--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,76 +612,76 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>30020-BG00- 780X300F-A   V</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="M2" t="n">
+        <v>780</v>
+      </c>
+      <c r="N2" t="n">
         <v>300</v>
       </c>
-      <c r="I2" t="n">
-        <v>285</v>
-      </c>
-      <c r="J2" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" t="n">
-        <v>870</v>
-      </c>
-      <c r="N2" t="n">
-        <v>95</v>
-      </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -690,25 +690,25 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB2" s="3" t="n"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/5/7）</t>
         </is>
       </c>
       <c r="AD2" s="3" t="n"/>
@@ -972,44 +972,44 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y5-14</t>
+          <t>Y5-6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8200</v>
+        <v>2000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8200</v>
+        <v>2000</v>
       </c>
       <c r="I5" t="n">
-        <v>16400</v>
+        <v>4000</v>
       </c>
       <c r="J5" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="L5" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M5" t="n">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="N5" t="n">
         <v>200</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1118,7 +1118,7 @@
         <v>4000</v>
       </c>
       <c r="J6" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n"/>
@@ -1212,50 +1212,50 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y5-6</t>
+          <t>A5-2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H7" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="I7" t="n">
-        <v>4000</v>
+        <v>2100</v>
       </c>
       <c r="J7" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>820</v>
+        <v>1080</v>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>46154</v>
@@ -1268,20 +1268,20 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>870</v>
+        <v>1080</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n"/>
@@ -1332,50 +1332,50 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>18000</v>
+        <v>400</v>
       </c>
       <c r="J8" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M8" t="n">
-        <v>780</v>
+        <v>680</v>
       </c>
       <c r="N8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>46154</v>
@@ -1393,15 +1393,15 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>780</v>
+        <v>680</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n"/>
@@ -1452,50 +1452,50 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A5-2</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="J9" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="M9" t="n">
-        <v>1080</v>
+        <v>680</v>
       </c>
       <c r="N9" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>46154</v>
@@ -1508,20 +1508,20 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>1080</v>
+        <v>680</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB9" s="3" t="n"/>
@@ -1572,76 +1572,76 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A5-2</t>
+          <t>Y5-2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2100</v>
+        <v>9000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2100</v>
+        <v>9000</v>
       </c>
       <c r="I10" t="n">
-        <v>2100</v>
+        <v>18000</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>1080</v>
+        <v>780</v>
       </c>
       <c r="N10" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>1080</v>
+        <v>780</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1657,18 +1657,18 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB10" s="3" t="n"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/8）</t>
         </is>
       </c>
       <c r="AD10" s="3" t="n"/>
@@ -1692,7 +1692,7 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>Y5-3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1706,30 +1706,30 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>2200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>200</v>
+        <v>2200</v>
       </c>
       <c r="I11" t="n">
-        <v>400</v>
+        <v>4400</v>
       </c>
       <c r="J11" t="n">
         <v>19</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -1738,10 +1738,10 @@
         <v>4</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>46149</v>
@@ -1753,11 +1753,11 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>Y5-3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1826,30 +1826,30 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>2200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>200</v>
+        <v>2200</v>
       </c>
       <c r="I12" t="n">
-        <v>400</v>
+        <v>4400</v>
       </c>
       <c r="J12" t="n">
         <v>25.65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M12" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="N12" t="n">
         <v>200</v>
@@ -1858,10 +1858,10 @@
         <v>4</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>46149</v>
@@ -1873,11 +1873,11 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>V5-3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1946,45 +1946,45 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9000</v>
+        <v>300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9000</v>
+        <v>300</v>
       </c>
       <c r="I13" t="n">
-        <v>18000</v>
+        <v>600</v>
       </c>
       <c r="J13" t="n">
         <v>23.75</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1993,11 +1993,11 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       <c r="AB13" s="3" t="n"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>（2026/5/8）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD13" s="3" t="n"/>
@@ -2052,56 +2052,56 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2200</v>
+        <v>400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2200</v>
+        <v>400</v>
       </c>
       <c r="I14" t="n">
-        <v>4400</v>
+        <v>800</v>
       </c>
       <c r="J14" t="n">
         <v>19</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M14" t="n">
-        <v>870</v>
+        <v>1030</v>
       </c>
       <c r="N14" t="n">
         <v>200</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>46149</v>
@@ -2113,15 +2113,15 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>870</v>
+        <v>1030</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2172,7 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2186,62 +2186,62 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="I15" t="n">
-        <v>4400</v>
+        <v>3200</v>
       </c>
       <c r="J15" t="n">
         <v>25.65</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M15" t="n">
-        <v>870</v>
+        <v>935</v>
       </c>
       <c r="N15" t="n">
         <v>200</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>46149</v>
+        <v>46143</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>870</v>
+        <v>935</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       <c r="AB15" s="3" t="n"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/1）</t>
         </is>
       </c>
       <c r="AD15" s="3" t="n"/>
@@ -2292,59 +2292,59 @@
       <c r="B16" s="3" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="I16" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="J16" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M16" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="N16" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2353,15 +2353,15 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2377,18 +2377,18 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB16" s="3" t="n"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD16" s="3" t="n"/>
@@ -2412,56 +2412,56 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="I17" t="n">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="J17" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M17" t="n">
-        <v>1440</v>
+        <v>1030</v>
       </c>
       <c r="N17" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>46149</v>
@@ -2473,15 +2473,15 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>1440</v>
+        <v>1030</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB17" s="3" t="n"/>
@@ -2532,41 +2532,41 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>V5-3</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>300</v>
+        <v>8600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>300</v>
+        <v>8600</v>
       </c>
       <c r="I18" t="n">
-        <v>600</v>
+        <v>8600</v>
       </c>
       <c r="J18" t="n">
         <v>23.75</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M18" t="n">
         <v>1000</v>
@@ -2575,13 +2575,13 @@
         <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="R18" s="2" t="n">
         <v>46153</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2666,45 +2666,45 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="I19" t="n">
-        <v>800</v>
+        <v>6000</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M19" t="n">
-        <v>1030</v>
+        <v>1300</v>
       </c>
       <c r="N19" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2713,15 +2713,15 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>1030</v>
+        <v>1300</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="AB19" s="3" t="n"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD19" s="3" t="n"/>
@@ -2772,76 +2772,76 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Y5-8</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="I20" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="J20" t="n">
-        <v>25.65</v>
+        <v>9.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M20" t="n">
-        <v>935</v>
+        <v>1300</v>
       </c>
       <c r="N20" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>935</v>
+        <v>1300</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2857,18 +2857,18 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB20" s="3" t="n"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD20" s="3" t="n"/>
@@ -2892,7 +2892,7 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2906,23 +2906,23 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="I21" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J21" t="n">
         <v>23.75</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="L21" s="3" t="n">
@@ -2932,28 +2932,25 @@
         <v>1000</v>
       </c>
       <c r="N21" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46157</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -2961,7 +2958,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3012,7 +3009,7 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3026,62 +3023,62 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="I22" t="n">
-        <v>800</v>
+        <v>12000</v>
       </c>
       <c r="J22" t="n">
         <v>23.75</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M22" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="N22" t="n">
         <v>200</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3108,7 +3105,7 @@
       <c r="AB22" s="3" t="n"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/13）</t>
         </is>
       </c>
       <c r="AD22" s="3" t="n"/>
@@ -3132,12 +3129,12 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3146,23 +3143,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="I23" t="n">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="J23" t="n">
         <v>23.75</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
@@ -3172,28 +3169,25 @@
         <v>1000</v>
       </c>
       <c r="N23" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46157</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R23" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U23" t="n">
@@ -3201,7 +3195,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3217,7 +3211,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3252,44 +3246,44 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>Y5-11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I24" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="J24" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M24" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="N24" t="n">
         <v>300</v>
@@ -3298,30 +3292,30 @@
         <v>2</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="Q24" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="R24" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="R24" s="2" t="n">
-        <v>46153</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U24" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3337,18 +3331,18 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB24" s="3" t="n"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD24" s="3" t="n"/>
@@ -3372,44 +3366,44 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I25" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="J25" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L25" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M25" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="N25" t="n">
         <v>300</v>
@@ -3418,30 +3412,30 @@
         <v>2</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3457,18 +3451,18 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB25" s="3" t="n"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD25" s="3" t="n"/>
@@ -3492,17 +3486,17 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Y5-7</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3515,53 +3509,53 @@
         <v>6000</v>
       </c>
       <c r="I26" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="J26" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M26" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="N26" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3577,18 +3571,18 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB26" s="3" t="n"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD26" s="3" t="n"/>
@@ -3612,44 +3606,44 @@
       <c r="B27" s="3" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Y5-11</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I27" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="J27" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M27" t="n">
-        <v>780</v>
+        <v>1300</v>
       </c>
       <c r="N27" t="n">
         <v>300</v>
@@ -3658,30 +3652,30 @@
         <v>2</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>780</v>
+        <v>1300</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3697,18 +3691,18 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB27" s="3" t="n"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD27" s="3" t="n"/>
@@ -3732,76 +3726,76 @@
       <c r="B28" s="3" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Y5-12</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="I28" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="J28" t="n">
         <v>23.75</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M28" t="n">
-        <v>780</v>
+        <v>450</v>
       </c>
       <c r="N28" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>780</v>
+        <v>960</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3817,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3828,7 +3822,7 @@
       <c r="AB28" s="3" t="n"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD28" s="3" t="n"/>
@@ -3852,50 +3846,50 @@
       <c r="B29" s="3" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="I29" t="n">
         <v>6000</v>
       </c>
       <c r="J29" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M29" t="n">
-        <v>1300</v>
+        <v>550</v>
       </c>
       <c r="N29" t="n">
         <v>300</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>46162</v>
@@ -3904,7 +3898,7 @@
         <v>46162</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3913,15 +3907,15 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>1300</v>
+        <v>1110</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3937,18 +3931,18 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB29" s="3" t="n"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD29" s="3" t="n"/>
@@ -3972,17 +3966,17 @@
       <c r="B30" s="3" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3995,24 +3989,24 @@
         <v>6000</v>
       </c>
       <c r="I30" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="J30" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M30" t="n">
-        <v>1300</v>
+        <v>450</v>
       </c>
       <c r="N30" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
@@ -4024,7 +4018,7 @@
         <v>46162</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -4033,15 +4027,15 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>1300</v>
+        <v>960</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4057,18 +4051,18 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB30" s="3" t="n"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD30" s="3" t="n"/>
@@ -4212,53 +4206,50 @@
       <c r="B32" s="3" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-13</t>
+          <t>Y5-25</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="I32" t="n">
-        <v>10200</v>
+        <v>12600</v>
       </c>
       <c r="J32" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>22022-8A00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M32" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="N32" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>46163</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>46163</v>
@@ -4273,15 +4264,15 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>22044-AA00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4297,12 +4288,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB32" s="3" t="n"/>
@@ -4326,19 +4317,18 @@
       <c r="AH32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4347,45 +4337,45 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4000</v>
+        <v>5100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4000</v>
+        <v>5100</v>
       </c>
       <c r="I33" t="n">
-        <v>4000</v>
+        <v>10200</v>
       </c>
       <c r="J33" t="n">
         <v>23.75</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M33" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="N33" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -4394,15 +4384,15 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4418,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4429,7 +4419,7 @@
       <c r="AB33" s="3" t="n"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AD33" s="3" t="n"/>
@@ -4447,80 +4437,79 @@
       <c r="AH33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>19</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="M34" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N34" t="n">
         <v>300</v>
       </c>
-      <c r="I34" t="n">
-        <v>285</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="M34" t="n">
-        <v>870</v>
-      </c>
-      <c r="N34" t="n">
-        <v>95</v>
-      </c>
       <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>46150</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4536,18 +4525,18 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB34" s="3" t="n"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD34" s="3" t="n"/>
@@ -4565,83 +4554,79 @@
       <c r="AH34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="I35" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="J35" t="n">
         <v>9.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M35" t="n">
-        <v>740</v>
+        <v>1440</v>
       </c>
       <c r="N35" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="P35" s="2" t="n">
-        <v>46162</v>
-      </c>
       <c r="Q35" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>750</v>
+        <v>1440</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4657,7 +4642,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4668,7 +4653,7 @@
       <c r="AB35" s="3" t="n"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD35" s="3" t="n"/>
@@ -4684,6 +4669,2588 @@
         </is>
       </c>
       <c r="AH35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y5-21</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M36" t="n">
+        <v>870</v>
+      </c>
+      <c r="N36" t="n">
+        <v>200</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>870</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="n"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>（2026/5/18）</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="n"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="n"/>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Y5-23</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I37" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M37" t="n">
+        <v>870</v>
+      </c>
+      <c r="N37" t="n">
+        <v>200</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>870</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="n"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>（2026/5/19）</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="n"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="n"/>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Y5-22</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M38" t="n">
+        <v>870</v>
+      </c>
+      <c r="N38" t="n">
+        <v>200</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>870</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="n"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>（2026/5/20）</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="n"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="n"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Y5-15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>30033-BY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M39" t="n">
+        <v>640</v>
+      </c>
+      <c r="N39" t="n">
+        <v>200</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>30066-AY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>640</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>スライス+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>（2026/5/18）</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="n"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="n"/>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>W5-6</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N40" t="n">
+        <v>300</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>（19）</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="n"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>（2026/5/19）</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="n"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="n"/>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>W5-6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N41" t="n">
+        <v>300</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="n"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>（2026/5/19）</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="n"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="n"/>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y5-27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I42" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M42" t="n">
+        <v>870</v>
+      </c>
+      <c r="N42" t="n">
+        <v>200</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>870</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="n"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>（2026/5/21）</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="n"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="n"/>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y5-16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>30033-BY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M43" t="n">
+        <v>640</v>
+      </c>
+      <c r="N43" t="n">
+        <v>200</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>30066-AY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>640</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>スライス+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="n"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>（2026/5/20）</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="n"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="n"/>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y5-24</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M44" t="n">
+        <v>870</v>
+      </c>
+      <c r="N44" t="n">
+        <v>200</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>870</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="n"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>（2026/5/22）</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="n"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="n"/>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Y5-17</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>30020-BY00- 640X250F-A   C</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M45" t="n">
+        <v>640</v>
+      </c>
+      <c r="N45" t="n">
+        <v>250</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>30040-AY00- 640X250F-A   C</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>640</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>スライス+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="n"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>（2026/5/25）</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="n"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="n"/>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>W5-7</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>19</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N46" t="n">
+        <v>300</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>（19）</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="n"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>（2026/5/22）</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="n"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="n"/>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>W5-7</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J47" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N47" t="n">
+        <v>300</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="n"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>（2026/5/22）</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="n"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="n"/>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y5-26</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M48" t="n">
+        <v>680</v>
+      </c>
+      <c r="N48" t="n">
+        <v>200</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>680</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="n"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="n"/>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="n"/>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Y5-28</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J49" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M49" t="n">
+        <v>870</v>
+      </c>
+      <c r="N49" t="n">
+        <v>200</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>870</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>（25.65）</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="n"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>（2026/5/25）</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="n"/>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="n"/>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Y5-20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J50" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M50" t="n">
+        <v>550</v>
+      </c>
+      <c r="N50" t="n">
+        <v>300</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>1110</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>スリット+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="n"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="n"/>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="n"/>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>W5-8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J51" t="n">
+        <v>19</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N51" t="n">
+        <v>300</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>（19）</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="n"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="n"/>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="n"/>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>W5-8</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1440</v>
+      </c>
+      <c r="N52" t="n">
+        <v>300</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>1440</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="n"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="n"/>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="n"/>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>V5-2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>30030-BG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N53" t="n">
+        <v>100</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>30060-AG00-1000X200F-A   C</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>分割,スライス</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>分割+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="n"/>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>（2026/5/11）</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="n"/>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="n"/>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Y5-20</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M54" t="n">
+        <v>550</v>
+      </c>
+      <c r="N54" t="n">
+        <v>300</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>1110</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="n"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="n"/>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="n"/>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>JR260501</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>300</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>300</v>
+      </c>
+      <c r="I55" t="n">
+        <v>285</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M55" t="n">
+        <v>870</v>
+      </c>
+      <c r="N55" t="n">
+        <v>95</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>FEL4004AY-10WD-1000X100</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="n"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>（2026/5/1）</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="n"/>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="n"/>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Y5-19</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M56" t="n">
+        <v>550</v>
+      </c>
+      <c r="N56" t="n">
+        <v>300</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>1110</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="n"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>（2026/5/14）</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="n"/>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="n"/>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Y5-10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3600</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="M57" t="n">
+        <v>740</v>
+      </c>
+      <c r="N57" t="n">
+        <v>200</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>750</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="n"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>（2026/5/13）</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="n"/>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="n"/>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,59 +612,59 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>W5-9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9000</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>4500</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>4500</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
-        <v>18000</v>
+        <v>200</v>
       </c>
       <c r="J2" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>15025-JW07-1550X 30F-A   V</t>
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>780</v>
+        <v>1550</v>
       </c>
       <c r="N2" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>15025-AW07-1600X200F-A   V</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>780</v>
+        <v>1600</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -690,25 +690,25 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB2" s="3" t="n"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD2" s="3" t="n"/>
@@ -732,68 +732,68 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H3" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="I3" t="n">
-        <v>285</v>
+        <v>4000</v>
       </c>
       <c r="J3" t="n">
         <v>23.75</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N3" t="n">
         <v>100</v>
       </c>
-      <c r="M3" t="n">
-        <v>870</v>
-      </c>
-      <c r="N3" t="n">
-        <v>95</v>
-      </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -810,14 +810,14 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="AB3" s="3" t="n"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD3" s="3" t="n"/>
@@ -852,59 +852,59 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Y5-5</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H4" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="I4" t="n">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="J4" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M4" t="n">
-        <v>680</v>
+        <v>1300</v>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -913,15 +913,15 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>680</v>
+        <v>1300</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -930,25 +930,25 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB4" s="3" t="n"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD4" s="3" t="n"/>
@@ -972,59 +972,59 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y5-6</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="I5" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="J5" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M5" t="n">
-        <v>820</v>
+        <v>1300</v>
       </c>
       <c r="N5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1033,15 +1033,15 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>870</v>
+        <v>1300</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1057,18 +1057,18 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD5" s="3" t="n"/>
@@ -1092,76 +1092,76 @@
       <c r="B6" s="3" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Y5-6</t>
+          <t>Y5-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="I6" t="n">
         <v>4000</v>
       </c>
       <c r="J6" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1177,18 +1177,18 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD6" s="3" t="n"/>
@@ -1212,76 +1212,76 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A5-2</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>2100</v>
+        <v>800</v>
       </c>
       <c r="J7" t="n">
         <v>19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="M7" t="n">
-        <v>1080</v>
+        <v>1030</v>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>1080</v>
+        <v>1030</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,59 +1332,59 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I8" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J8" t="n">
         <v>19</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M8" t="n">
-        <v>680</v>
+        <v>1550</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1393,15 +1393,15 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>680</v>
+        <v>1550</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="AB8" s="3" t="n"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD8" s="3" t="n"/>
@@ -1452,59 +1452,59 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I9" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="J9" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M9" t="n">
-        <v>680</v>
+        <v>1550</v>
       </c>
       <c r="N9" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1513,15 +1513,15 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>680</v>
+        <v>1550</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,18 +1537,18 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB9" s="3" t="n"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD9" s="3" t="n"/>
@@ -1572,7 +1572,7 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1586,45 +1586,45 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>18000</v>
+        <v>800</v>
       </c>
       <c r="J10" t="n">
         <v>23.75</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M10" t="n">
-        <v>780</v>
+        <v>1030</v>
       </c>
       <c r="N10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1633,15 +1633,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>780</v>
+        <v>1030</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       <c r="AB10" s="3" t="n"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>（2026/5/8）</t>
+          <t>（2026/5/7）</t>
         </is>
       </c>
       <c r="AD10" s="3" t="n"/>
@@ -1692,59 +1692,59 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2200</v>
+        <v>8600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2200</v>
+        <v>8600</v>
       </c>
       <c r="I11" t="n">
-        <v>4400</v>
+        <v>8600</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="N11" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1753,15 +1753,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1777,18 +1777,18 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB11" s="3" t="n"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD11" s="3" t="n"/>
@@ -1812,59 +1812,59 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="I12" t="n">
-        <v>4400</v>
+        <v>500</v>
       </c>
       <c r="J12" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M12" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1873,15 +1873,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1897,18 +1897,18 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB12" s="3" t="n"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD12" s="3" t="n"/>
@@ -1932,56 +1932,56 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>V5-3</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I13" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="J13" t="n">
         <v>23.75</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M13" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="N13" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>46153</v>
@@ -1993,15 +1993,15 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,44 +2052,44 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="I14" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="J14" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M14" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="N14" t="n">
         <v>200</v>
@@ -2098,30 +2098,30 @@
         <v>2</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2137,18 +2137,18 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB14" s="3" t="n"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD14" s="3" t="n"/>
@@ -2172,59 +2172,59 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y5-8</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="I15" t="n">
-        <v>3200</v>
+        <v>12000</v>
       </c>
       <c r="J15" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M15" t="n">
-        <v>935</v>
+        <v>1000</v>
       </c>
       <c r="N15" t="n">
         <v>200</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2233,15 +2233,15 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>935</v>
+        <v>1000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2257,18 +2257,18 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB15" s="3" t="n"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/5/13）</t>
         </is>
       </c>
       <c r="AD15" s="3" t="n"/>
@@ -2292,37 +2292,37 @@
       <c r="B16" s="3" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="I16" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J16" t="n">
         <v>23.75</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
@@ -2332,28 +2332,28 @@
         <v>1000</v>
       </c>
       <c r="N16" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2412,7 +2412,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>Y5-11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2426,62 +2426,62 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>400</v>
+        <v>9000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>400</v>
+        <v>9000</v>
       </c>
       <c r="I17" t="n">
-        <v>800</v>
+        <v>18000</v>
       </c>
       <c r="J17" t="n">
         <v>23.75</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M17" t="n">
-        <v>1030</v>
+        <v>780</v>
       </c>
       <c r="N17" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>1030</v>
+        <v>780</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       <c r="AB17" s="3" t="n"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>（2026/5/7）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD17" s="3" t="n"/>
@@ -2532,76 +2532,76 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8600</v>
+        <v>9000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8600</v>
+        <v>9000</v>
       </c>
       <c r="I18" t="n">
-        <v>8600</v>
+        <v>18000</v>
       </c>
       <c r="J18" t="n">
         <v>23.75</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M18" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="N18" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P18" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="R18" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="Q18" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>46153</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,7 +2628,7 @@
       <c r="AB18" s="3" t="n"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD18" s="3" t="n"/>
@@ -2652,7 +2652,7 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2666,16 +2666,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H19" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="I19" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -2698,13 +2698,13 @@
         <v>2</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       <c r="AB19" s="3" t="n"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/12）</t>
         </is>
       </c>
       <c r="AD19" s="3" t="n"/>
@@ -2772,7 +2772,7 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2786,16 +2786,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="I20" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="J20" t="n">
         <v>9.5</v>
@@ -2818,13 +2818,13 @@
         <v>2</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       <c r="AB20" s="3" t="n"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/12）</t>
         </is>
       </c>
       <c r="AD20" s="3" t="n"/>
@@ -2892,73 +2892,76 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>V5-4</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I21" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="J21" t="n">
         <v>23.75</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30020-BY00-1000X200F-A   C</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M21" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="N21" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
+      <c r="P21" s="2" t="n">
+        <v>46162</v>
+      </c>
       <c r="Q21" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>30040-AY00-1000X200F-A   C</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>スライス,巻返し</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2974,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,7 +2988,7 @@
       <c r="AB21" s="3" t="n"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD21" s="3" t="n"/>
@@ -3009,76 +3012,76 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Y5-7</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I22" t="n">
         <v>6000</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I22" t="n">
-        <v>12000</v>
       </c>
       <c r="J22" t="n">
         <v>23.75</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="N22" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3094,7 +3097,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3105,7 +3108,7 @@
       <c r="AB22" s="3" t="n"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD22" s="3" t="n"/>
@@ -3129,73 +3132,76 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>V5-4</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="I23" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="J23" t="n">
         <v>23.75</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30020-BY00-1000X200F-A   C</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M23" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="N23" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
       </c>
+      <c r="P23" s="2" t="n">
+        <v>46162</v>
+      </c>
       <c r="Q23" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>30040-AY00-1000X200F-A   C</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>スライス,巻返し</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3211,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3222,7 +3228,7 @@
       <c r="AB23" s="3" t="n"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD23" s="3" t="n"/>
@@ -3246,59 +3252,59 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Y5-11</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="I24" t="n">
-        <v>18000</v>
+        <v>3600</v>
       </c>
       <c r="J24" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M24" t="n">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="N24" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O24" t="n">
         <v>2</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3307,15 +3313,15 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="U24" t="n">
-        <v>780</v>
+        <v>750</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3331,18 +3337,18 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB24" s="3" t="n"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/13）</t>
         </is>
       </c>
       <c r="AD24" s="3" t="n"/>
@@ -3366,76 +3372,76 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Y5-12</t>
+          <t>Y5-25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="I25" t="n">
-        <v>18000</v>
+        <v>12600</v>
       </c>
       <c r="J25" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>22022-8A00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="L25" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M25" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="N25" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>22044-AA00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3451,18 +3457,18 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB25" s="3" t="n"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AD25" s="3" t="n"/>
@@ -3486,44 +3492,44 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
       <c r="I26" t="n">
-        <v>6000</v>
+        <v>10200</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M26" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="N26" t="n">
         <v>300</v>
@@ -3532,13 +3538,13 @@
         <v>2</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3547,15 +3553,15 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3571,18 +3577,18 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB26" s="3" t="n"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AD26" s="3" t="n"/>
@@ -3606,44 +3612,44 @@
       <c r="B27" s="3" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="J27" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M27" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="N27" t="n">
         <v>300</v>
@@ -3651,14 +3657,11 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="P27" s="2" t="n">
-        <v>46162</v>
-      </c>
       <c r="Q27" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3667,11 +3670,11 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3691,18 +3694,18 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB27" s="3" t="n"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD27" s="3" t="n"/>
@@ -3726,59 +3729,56 @@
       <c r="B28" s="3" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="I28" t="n">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="J28" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M28" t="n">
-        <v>450</v>
+        <v>1440</v>
       </c>
       <c r="N28" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" s="2" t="n">
-        <v>46162</v>
-      </c>
       <c r="Q28" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3787,15 +3787,15 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3811,18 +3811,18 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB28" s="3" t="n"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AD28" s="3" t="n"/>
@@ -3846,59 +3846,59 @@
       <c r="B29" s="3" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Y5-19</t>
+          <t>Y5-21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="I29" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="J29" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M29" t="n">
-        <v>550</v>
+        <v>870</v>
       </c>
       <c r="N29" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3907,15 +3907,15 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>1110</v>
+        <v>870</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3931,18 +3931,18 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB29" s="3" t="n"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AD29" s="3" t="n"/>
@@ -3966,59 +3966,59 @@
       <c r="B30" s="3" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>Y5-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I30" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="J30" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M30" t="n">
-        <v>450</v>
+        <v>870</v>
       </c>
       <c r="N30" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -4027,15 +4027,15 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>960</v>
+        <v>870</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4051,18 +4051,18 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB30" s="3" t="n"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AD30" s="3" t="n"/>
@@ -4086,59 +4086,59 @@
       <c r="B31" s="3" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3600</v>
+        <v>200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3600</v>
+        <v>200</v>
       </c>
       <c r="I31" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="J31" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="N31" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -4147,15 +4147,15 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4171,18 +4171,18 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB31" s="3" t="n"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/12）</t>
         </is>
       </c>
       <c r="AD31" s="3" t="n"/>
@@ -4206,7 +4206,7 @@
       <c r="B32" s="3" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-25</t>
+          <t>Y5-22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4220,42 +4220,45 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6300</v>
+        <v>9000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6300</v>
+        <v>9000</v>
       </c>
       <c r="I32" t="n">
-        <v>12600</v>
+        <v>18000</v>
       </c>
       <c r="J32" t="n">
         <v>25.65</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22022-8A00-1050X210F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M32" t="n">
-        <v>1050</v>
+        <v>870</v>
       </c>
       <c r="N32" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O32" t="n">
-        <v>2.2</v>
+        <v>4</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>46167</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -4264,11 +4267,11 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>22044-AA00-1050X210F-A   C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>1050</v>
+        <v>870</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -4299,7 +4302,7 @@
       <c r="AB32" s="3" t="n"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/20）</t>
         </is>
       </c>
       <c r="AD32" s="3" t="n"/>
@@ -4323,7 +4326,7 @@
       <c r="B33" s="3" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y5-13</t>
+          <t>Y5-15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4337,58 +4340,58 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="I33" t="n">
-        <v>10200</v>
+        <v>16000</v>
       </c>
       <c r="J33" t="n">
         <v>23.75</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M33" t="n">
-        <v>780</v>
+        <v>640</v>
       </c>
       <c r="N33" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="R33" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>780</v>
+        <v>640</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4443,7 +4446,7 @@
       <c r="B34" s="3" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4489,10 +4492,10 @@
         <v>2</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -4536,7 +4539,7 @@
       <c r="AB34" s="3" t="n"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AD34" s="3" t="n"/>
@@ -4560,7 +4563,7 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4606,10 +4609,10 @@
         <v>2</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4653,7 +4656,7 @@
       <c r="AB35" s="3" t="n"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AD35" s="3" t="n"/>
@@ -4677,7 +4680,7 @@
       <c r="B36" s="3" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Y5-21</t>
+          <t>Y5-27</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4722,11 +4725,14 @@
       <c r="O36" t="n">
         <v>4</v>
       </c>
+      <c r="P36" s="2" t="n">
+        <v>46169</v>
+      </c>
       <c r="Q36" s="2" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -4770,7 +4776,7 @@
       <c r="AB36" s="3" t="n"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/21）</t>
         </is>
       </c>
       <c r="AD36" s="3" t="n"/>
@@ -4794,73 +4800,76 @@
       <c r="B37" s="3" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Y5-23</t>
+          <t>Y5-16</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="I37" t="n">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="J37" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="L37" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M37" t="n">
-        <v>870</v>
+        <v>640</v>
       </c>
       <c r="N37" t="n">
         <v>200</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3.3</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46169</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>870</v>
+        <v>640</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4876,18 +4885,18 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB37" s="3" t="n"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/20）</t>
         </is>
       </c>
       <c r="AD37" s="3" t="n"/>
@@ -4911,7 +4920,7 @@
       <c r="B38" s="3" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Y5-22</t>
+          <t>Y5-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4941,7 +4950,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L38" s="3" t="n">
@@ -4956,11 +4965,14 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
+      <c r="P38" s="2" t="n">
+        <v>46170</v>
+      </c>
       <c r="Q38" s="2" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4969,7 +4981,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U38" t="n">
@@ -5004,7 +5016,7 @@
       <c r="AB38" s="3" t="n"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AD38" s="3" t="n"/>
@@ -5028,7 +5040,7 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Y5-15</t>
+          <t>Y5-17</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5042,42 +5054,45 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="I39" t="n">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="J39" t="n">
         <v>23.75</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M39" t="n">
         <v>640</v>
       </c>
       <c r="N39" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46170</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -5086,7 +5101,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="U39" t="n">
@@ -5121,7 +5136,7 @@
       <c r="AB39" s="3" t="n"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AD39" s="3" t="n"/>
@@ -5145,7 +5160,7 @@
       <c r="B40" s="3" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>W5-7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5191,10 +5206,10 @@
         <v>2</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -5238,7 +5253,7 @@
       <c r="AB40" s="3" t="n"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AD40" s="3" t="n"/>
@@ -5262,7 +5277,7 @@
       <c r="B41" s="3" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>W5-7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5308,10 +5323,10 @@
         <v>2</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -5355,7 +5370,7 @@
       <c r="AB41" s="3" t="n"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AD41" s="3" t="n"/>
@@ -5379,7 +5394,7 @@
       <c r="B42" s="3" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Y5-27</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,30 +5408,30 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="I42" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="J42" t="n">
         <v>25.65</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="L42" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M42" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="N42" t="n">
         <v>200</v>
@@ -5424,11 +5439,14 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
+      <c r="P42" s="2" t="n">
+        <v>46171</v>
+      </c>
       <c r="Q42" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -5437,11 +5455,11 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -5472,7 +5490,7 @@
       <c r="AB42" s="3" t="n"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>（2026/5/21）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AD42" s="3" t="n"/>
@@ -5496,56 +5514,59 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Y5-16</t>
+          <t>Y5-28</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="I43" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="J43" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L43" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M43" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="N43" t="n">
         <v>200</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>4</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -5554,15 +5575,15 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5578,18 +5599,18 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AB43" s="3" t="n"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AD43" s="3" t="n"/>
@@ -5613,56 +5634,59 @@
       <c r="B44" s="3" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y5-24</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I44" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="J44" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M44" t="n">
-        <v>870</v>
+        <v>550</v>
       </c>
       <c r="N44" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -5671,15 +5695,15 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>870</v>
+        <v>1110</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5695,18 +5719,18 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB44" s="3" t="n"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AD44" s="3" t="n"/>
@@ -5730,56 +5754,56 @@
       <c r="B45" s="3" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y5-17</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="I45" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="J45" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M45" t="n">
-        <v>640</v>
+        <v>1440</v>
       </c>
       <c r="N45" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>46170</v>
+        <v>46177</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -5788,15 +5812,15 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>640</v>
+        <v>1440</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5812,18 +5836,18 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AB45" s="3" t="n"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AD45" s="3" t="n"/>
@@ -5847,17 +5871,17 @@
       <c r="B46" s="3" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>W5-7</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5873,7 +5897,7 @@
         <v>9000</v>
       </c>
       <c r="J46" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5893,10 +5917,10 @@
         <v>2</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -5929,18 +5953,18 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB46" s="3" t="n"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AD46" s="3" t="n"/>
@@ -5958,62 +5982,66 @@
       <c r="AH46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>W5-7</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H47" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="I47" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="J47" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M47" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="N47" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46157</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -6022,15 +6050,15 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6039,25 +6067,25 @@
         </is>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB47" s="3" t="n"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD47" s="3" t="n"/>
@@ -6075,79 +6103,83 @@
       <c r="AH47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>Y5-30</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>7000</v>
+        <v>400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>7000</v>
+        <v>400</v>
       </c>
       <c r="I48" t="n">
-        <v>14000</v>
+        <v>400</v>
       </c>
       <c r="J48" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M48" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="N48" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46164</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>46168</v>
+        <v>46154</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6163,18 +6195,18 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AB48" s="3" t="n"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/12）</t>
         </is>
       </c>
       <c r="AD48" s="3" t="n"/>
@@ -6192,62 +6224,63 @@
       <c r="AH48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="n"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>9000</v>
+        <v>250</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>9000</v>
+        <v>250</v>
       </c>
       <c r="I49" t="n">
-        <v>18000</v>
-      </c>
-      <c r="J49" t="n">
-        <v>25.65</v>
+        <v>250</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M49" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="N49" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>2.5</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46157</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -6256,15 +6289,15 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6280,18 +6313,18 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AB49" s="3" t="n"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD49" s="3" t="n"/>
@@ -6309,18 +6342,19 @@
       <c r="AH49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="n"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6329,42 +6363,42 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="I50" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J50" t="n">
-        <v>23.75</v>
+        <v>500</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M50" t="n">
-        <v>550</v>
+        <v>1550</v>
       </c>
       <c r="N50" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2.5</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46157</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>46168</v>
+        <v>46153</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -6373,15 +6407,15 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>1110</v>
+        <v>1550</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6397,18 +6431,18 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AB50" s="3" t="n"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/11）</t>
         </is>
       </c>
       <c r="AD50" s="3" t="n"/>
@@ -6426,62 +6460,63 @@
       <c r="AH50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="n"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I51" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J51" t="n">
-        <v>19</v>
+        <v>6000</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M51" t="n">
-        <v>1440</v>
+        <v>550</v>
       </c>
       <c r="N51" t="n">
         <v>300</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46162</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>46177</v>
+        <v>46162</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -6490,15 +6525,15 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>1440</v>
+        <v>1110</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6514,18 +6549,18 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AB51" s="3" t="n"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/14）</t>
         </is>
       </c>
       <c r="AD51" s="3" t="n"/>
@@ -6543,59 +6578,60 @@
       <c r="AH51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="n"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="I52" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J52" t="n">
-        <v>9.5</v>
+        <v>12000</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L52" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M52" t="n">
-        <v>1440</v>
+        <v>550</v>
       </c>
       <c r="N52" t="n">
         <v>300</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="R52" s="2" t="n">
         <v>46168</v>
@@ -6607,15 +6643,15 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U52" t="n">
-        <v>1440</v>
+        <v>1110</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6631,12 +6667,12 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AB52" s="3" t="n"/>
@@ -6667,7 +6703,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6677,66 +6713,66 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="I53" t="n">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="J53" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="L53" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="M53" t="n">
+        <v>740</v>
+      </c>
+      <c r="N53" t="n">
         <v>200</v>
       </c>
-      <c r="M53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N53" t="n">
-        <v>100</v>
-      </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6752,18 +6788,18 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>分割+エンボス　湖南</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AB53" s="3" t="n"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/13）</t>
         </is>
       </c>
       <c r="AD53" s="3" t="n"/>
@@ -6779,478 +6815,6 @@
         </is>
       </c>
       <c r="AH53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Y5-20</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>欠点表示</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I54" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="M54" t="n">
-        <v>550</v>
-      </c>
-      <c r="N54" t="n">
-        <v>300</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>1110</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>欠点表示,スリット</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>欠点表示+スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AB54" s="3" t="n"/>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>（2026/5/26）</t>
-        </is>
-      </c>
-      <c r="AD54" s="3" t="n"/>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AF54" s="3" t="n"/>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AH54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>JR260501</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>梱包</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>300</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>300</v>
-      </c>
-      <c r="I55" t="n">
-        <v>285</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="M55" t="n">
-        <v>870</v>
-      </c>
-      <c r="N55" t="n">
-        <v>95</v>
-      </c>
-      <c r="O55" t="n">
-        <v>4</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>FEL4004AY-10WD-1000X100</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SEC,梱包,スリット</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>梱包+スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AB55" s="3" t="n"/>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>（2026/5/1）</t>
-        </is>
-      </c>
-      <c r="AD55" s="3" t="n"/>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AF55" s="3" t="n"/>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AH55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Y5-19</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>欠点表示</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I56" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="M56" t="n">
-        <v>550</v>
-      </c>
-      <c r="N56" t="n">
-        <v>300</v>
-      </c>
-      <c r="O56" t="n">
-        <v>3</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>1110</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>欠点表示,スリット</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>欠点表示+スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AB56" s="3" t="n"/>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>（2026/5/14）</t>
-        </is>
-      </c>
-      <c r="AD56" s="3" t="n"/>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AF56" s="3" t="n"/>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AH56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Y5-10</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>分割</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>エンボス　湖南</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J57" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="M57" t="n">
-        <v>740</v>
-      </c>
-      <c r="N57" t="n">
-        <v>200</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>750</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>分割,エンボス</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>分割+エンボス　湖南</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>（9.5）</t>
-        </is>
-      </c>
-      <c r="AB57" s="3" t="n"/>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>（2026/5/13）</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="n"/>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AF57" s="3" t="n"/>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AH57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,44 +617,44 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4200</v>
+        <v>9000</v>
       </c>
       <c r="G2" t="n">
-        <v>3600</v>
+        <v>1500</v>
       </c>
       <c r="H2" t="n">
-        <v>3600</v>
+        <v>1500</v>
       </c>
       <c r="I2" t="n">
-        <v>4200</v>
+        <v>18000</v>
       </c>
       <c r="J2" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L2" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M2" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="N2" t="n">
         <v>300</v>
@@ -663,33 +663,33 @@
         <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U2" s="3" t="n">
         <v>300</v>
       </c>
       <c r="V2" t="n">
-        <v>1300</v>
+        <v>780</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -698,25 +698,25 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>600</v>
+        <v>7500</v>
       </c>
       <c r="Z2" t="n">
-        <v>600</v>
+        <v>15000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>（2026/5/12）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AE2" s="3" t="n"/>
@@ -740,47 +740,47 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" t="n">
         <v>3600</v>
       </c>
-      <c r="H3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4200</v>
-      </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>1300</v>
+        <v>740</v>
       </c>
       <c r="N3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
@@ -792,27 +792,27 @@
         <v>46162</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>1300</v>
+        <v>750</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>600</v>
+        <v>2600</v>
       </c>
       <c r="Z3" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>（2026/5/12）</t>
+          <t>（2026/5/13）</t>
         </is>
       </c>
       <c r="AE3" s="3" t="n"/>
@@ -863,79 +863,79 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V5-4</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="H4" t="n">
-        <v>8000</v>
+        <v>3900</v>
       </c>
       <c r="I4" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="J4" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30020-BY00-1000X200F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M4" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>30040-AY00-1000X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V4" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>スライス,巻返し</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC4" s="3" t="n"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>（2026/5/11）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AE4" s="3" t="n"/>
@@ -986,59 +986,59 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="I5" t="n">
-        <v>2000</v>
+        <v>8100</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15025-NR28-1550X250F-ABK0J</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M5" t="n">
-        <v>1550</v>
+        <v>1440</v>
       </c>
       <c r="N5" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1047,18 +1047,18 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15025-SR28-1550X250F-ABK0J</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U5" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="V5" t="n">
-        <v>1550</v>
+        <v>1440</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>EC,巻返し</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1074,18 +1074,18 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AC5" s="3" t="n"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/15）</t>
         </is>
       </c>
       <c r="AE5" s="3" t="n"/>
@@ -1109,76 +1109,79 @@
       <c r="B6" s="3" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>193</v>
+        <v>6000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>200</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>12000</v>
       </c>
       <c r="J6" t="n">
         <v>23.75</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15024-XXXX-1600X 10F-A   B</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="M6" t="n">
-        <v>1600</v>
+        <v>450</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>46162</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15024-SRHW-1860X193F-A   B</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="U6" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="V6" t="n">
-        <v>1860</v>
+        <v>960</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>分割,スリット</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1194,7 +1197,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1229,79 +1232,79 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y5-11</t>
+          <t>W5-15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9000</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>18000</v>
+        <v>80</v>
       </c>
       <c r="J7" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>15015-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="M7" t="n">
-        <v>780</v>
+        <v>1550</v>
       </c>
       <c r="N7" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>15015-AP67-1550X400F-A   K</t>
         </is>
       </c>
       <c r="U7" s="3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>780</v>
+        <v>1550</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1317,18 +1320,18 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE7" s="3" t="n"/>
@@ -1352,79 +1355,79 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Y5-12</t>
+          <t>Y5-25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="I8" t="n">
-        <v>18000</v>
+        <v>12600</v>
       </c>
       <c r="J8" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>22022-8A00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="M8" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="N8" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P8" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="R8" s="2" t="n">
         <v>46161</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>46157</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>22044-AA00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="U8" s="3" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="V8" t="n">
-        <v>780</v>
+        <v>1050</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1440,18 +1443,18 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC8" s="3" t="n"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE8" s="3" t="n"/>
@@ -1475,7 +1478,7 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>W5-15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1489,45 +1492,45 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3000</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="I9" t="n">
-        <v>12000</v>
+        <v>80</v>
       </c>
       <c r="J9" t="n">
         <v>23.75</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>15015-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="M9" t="n">
-        <v>450</v>
+        <v>1550</v>
       </c>
       <c r="N9" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1536,18 +1539,18 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>15015-AP67-1550X400F-A   K</t>
         </is>
       </c>
       <c r="U9" s="3" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>960</v>
+        <v>1550</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1574,7 +1577,7 @@
       <c r="AC9" s="3" t="n"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE9" s="3" t="n"/>
@@ -1598,59 +1601,59 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I10" t="n">
         <v>6000</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>12000</v>
       </c>
       <c r="J10" t="n">
         <v>23.75</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="N10" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1659,18 +1662,18 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U10" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="V10" t="n">
-        <v>960</v>
+        <v>1110</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1686,7 +1689,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1697,7 +1700,7 @@
       <c r="AC10" s="3" t="n"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE10" s="3" t="n"/>
@@ -1721,79 +1724,79 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3600</v>
+        <v>1400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3600</v>
+        <v>1400</v>
       </c>
       <c r="I11" t="n">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="J11" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>0R040-8Y0B- 830X200F-ABG1C</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>740</v>
+        <v>830</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U11" s="3" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="V11" t="n">
-        <v>750</v>
+        <v>870</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1809,18 +1812,18 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE11" s="3" t="n"/>
@@ -1844,7 +1847,7 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Y5-25</t>
+          <t>Y5-32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1858,36 +1861,36 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6300</v>
+        <v>1400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6300</v>
+        <v>1400</v>
       </c>
       <c r="I12" t="n">
-        <v>12600</v>
+        <v>2800</v>
       </c>
       <c r="J12" t="n">
         <v>25.65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22022-8A00-1050X210F-A   C</t>
+          <t>0R040-8Y0B- 830X200F-ABG1C</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="M12" t="n">
-        <v>1050</v>
+        <v>830</v>
       </c>
       <c r="N12" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>46163</v>
@@ -1905,18 +1908,18 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>22044-AA00-1050X210F-A   C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U12" s="3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="V12" t="n">
-        <v>1050</v>
+        <v>870</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1967,50 +1970,50 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Y5-19</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="I13" t="n">
-        <v>6000</v>
+        <v>10200</v>
       </c>
       <c r="J13" t="n">
         <v>23.75</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M13" t="n">
-        <v>550</v>
+        <v>780</v>
       </c>
       <c r="N13" t="n">
         <v>300</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>46163</v>
@@ -2019,7 +2022,7 @@
         <v>46163</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2028,18 +2031,18 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="U13" s="3" t="n">
         <v>300</v>
       </c>
       <c r="V13" t="n">
-        <v>1110</v>
+        <v>780</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2055,7 +2058,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2066,7 +2069,7 @@
       <c r="AC13" s="3" t="n"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE13" s="3" t="n"/>
@@ -2090,50 +2093,50 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Y5-32</t>
+          <t>Y5-36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="I14" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="J14" t="n">
         <v>23.75</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 830X200F-ABG1C</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>830</v>
+        <v>1000</v>
       </c>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>46163</v>
@@ -2146,23 +2149,23 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="U14" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V14" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2178,7 +2181,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2213,59 +2216,56 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y5-32</t>
+          <t>W5-11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="I15" t="n">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="J15" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 830X200F-ABG1C</t>
+          <t>20020-JP17-1440X300F-A   Q</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M15" t="n">
-        <v>830</v>
+        <v>1440</v>
       </c>
       <c r="N15" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>46163</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2274,18 +2274,18 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>20020-AP17-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U15" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V15" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2301,18 +2301,18 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE15" s="3" t="n"/>
@@ -2336,56 +2336,56 @@
       <c r="B16" s="3" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Y5-13</t>
+          <t>Y5-21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5100</v>
+        <v>9000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5100</v>
+        <v>9000</v>
       </c>
       <c r="I16" t="n">
-        <v>10200</v>
+        <v>18000</v>
       </c>
       <c r="J16" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M16" t="n">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="N16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>46160</v>
@@ -2397,18 +2397,18 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="U16" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V16" t="n">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC16" s="3" t="n"/>
@@ -2459,17 +2459,17 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>Y5-23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2482,33 +2482,36 @@
         <v>9000</v>
       </c>
       <c r="I17" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>25.65</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M17" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="N17" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>46164</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2517,18 +2520,18 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U17" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V17" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2544,18 +2547,18 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC17" s="3" t="n"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE17" s="3" t="n"/>
@@ -2579,17 +2582,17 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>Y5-22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2602,33 +2605,36 @@
         <v>9000</v>
       </c>
       <c r="I18" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="J18" t="n">
-        <v>9.5</v>
+        <v>25.65</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M18" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="N18" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46167</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2637,18 +2643,18 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="U18" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V18" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2664,18 +2670,18 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC18" s="3" t="n"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>（2026/5/15）</t>
+          <t>（2026/5/20）</t>
         </is>
       </c>
       <c r="AE18" s="3" t="n"/>
@@ -2699,76 +2705,79 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>W5-11</t>
+          <t>JR260502</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="I19" t="n">
-        <v>1500</v>
+        <v>760</v>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>25.65</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20020-JP17-1440X300F-A   Q</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="N19" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>46167</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20020-AP17-1440X300F-A   P</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="U19" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V19" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2784,12 +2793,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC19" s="3" t="n"/>
@@ -2819,79 +2828,79 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Y5-21</t>
+          <t>JR260502</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>9000</v>
+        <v>760</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>9000</v>
+        <v>760</v>
       </c>
       <c r="I20" t="n">
-        <v>18000</v>
+        <v>760</v>
       </c>
       <c r="J20" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="M20" t="n">
         <v>870</v>
       </c>
       <c r="N20" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="U20" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V20" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2907,18 +2916,18 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC20" s="3" t="n"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE20" s="3" t="n"/>
@@ -2942,79 +2951,79 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Y5-23</t>
+          <t>V5-5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="I21" t="n">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30050-AS60-1000X100F-A   C</t>
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="N21" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30050-AS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="U21" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V21" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3030,12 +3039,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC21" s="3" t="n"/>
@@ -3065,59 +3074,59 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Y5-22</t>
+          <t>V5-6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="I22" t="n">
-        <v>18000</v>
+        <v>400</v>
       </c>
       <c r="J22" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>30020-BG20-1050X200F-AGA0U</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M22" t="n">
-        <v>870</v>
+        <v>1050</v>
       </c>
       <c r="N22" t="n">
         <v>200</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3126,18 +3135,18 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>30040-AG20-1050X200F-AGA0U</t>
         </is>
       </c>
       <c r="U22" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V22" t="n">
-        <v>870</v>
+        <v>1050</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3153,18 +3162,18 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC22" s="3" t="n"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/21）</t>
         </is>
       </c>
       <c r="AE22" s="3" t="n"/>
@@ -3188,59 +3197,59 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JR260502</t>
+          <t>Y5-15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="I23" t="n">
-        <v>760</v>
+        <v>16000</v>
       </c>
       <c r="J23" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="M23" t="n">
-        <v>870</v>
+        <v>640</v>
       </c>
       <c r="N23" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3249,18 +3258,18 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="U23" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V23" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3276,18 +3285,18 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC23" s="3" t="n"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE23" s="3" t="n"/>
@@ -3311,79 +3320,79 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Y5-31</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="I24" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="J24" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M24" t="n">
-        <v>820</v>
+        <v>1440</v>
       </c>
       <c r="N24" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U24" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V24" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3399,18 +3408,18 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC24" s="3" t="n"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE24" s="3" t="n"/>
@@ -3434,79 +3443,79 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JR260502</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>760</v>
+        <v>9000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>760</v>
+        <v>9000</v>
       </c>
       <c r="I25" t="n">
-        <v>760</v>
+        <v>9000</v>
       </c>
       <c r="J25" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="M25" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="N25" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U25" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V25" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3522,18 +3531,18 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AC25" s="3" t="n"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/18）</t>
         </is>
       </c>
       <c r="AE25" s="3" t="n"/>
@@ -3557,76 +3566,79 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>V5-5</t>
+          <t>Y5-27</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="J26" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30050-AS60-1000X100F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M26" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>46169</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>30050-AS60-1000X200F-A   C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="U26" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V26" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3642,18 +3654,18 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC26" s="3" t="n"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/21）</t>
         </is>
       </c>
       <c r="AE26" s="3" t="n"/>
@@ -3677,7 +3689,7 @@
       <c r="B27" s="3" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>V5-6</t>
+          <t>Y5-16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3691,58 +3703,61 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="I27" t="n">
-        <v>400</v>
+        <v>16000</v>
       </c>
       <c r="J27" t="n">
         <v>23.75</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30020-BG20-1050X200F-AGA0U</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M27" t="n">
-        <v>1050</v>
+        <v>640</v>
       </c>
       <c r="N27" t="n">
         <v>200</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3.3</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46169</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>30040-AG20-1050X200F-AGA0U</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="U27" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V27" t="n">
-        <v>1050</v>
+        <v>640</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3773,7 +3788,7 @@
       <c r="AC27" s="3" t="n"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>（2026/5/21）</t>
+          <t>（2026/5/20）</t>
         </is>
       </c>
       <c r="AE27" s="3" t="n"/>
@@ -3797,79 +3812,79 @@
       <c r="B28" s="3" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Y5-15</t>
+          <t>Y5-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="I28" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="J28" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M28" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="N28" t="n">
         <v>200</v>
       </c>
       <c r="O28" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U28" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V28" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3885,18 +3900,18 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC28" s="3" t="n"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>（2026/5/18）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE28" s="3" t="n"/>
@@ -3920,76 +3935,79 @@
       <c r="B29" s="3" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>Y5-34</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="I29" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J29" t="n">
-        <v>19</v>
+        <v>25.65</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M29" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="N29" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46170</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="U29" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V29" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -4005,18 +4023,18 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC29" s="3" t="n"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AE29" s="3" t="n"/>
@@ -4040,56 +4058,59 @@
       <c r="B30" s="3" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>V5-7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="I30" t="n">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="J30" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M30" t="n">
-        <v>1440</v>
+        <v>1030</v>
       </c>
       <c r="N30" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
+      <c r="P30" s="2" t="n">
+        <v>46170</v>
+      </c>
       <c r="Q30" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -4098,18 +4119,18 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="U30" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V30" t="n">
-        <v>1440</v>
+        <v>1030</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4125,18 +4146,18 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC30" s="3" t="n"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AE30" s="3" t="n"/>
@@ -4160,59 +4181,59 @@
       <c r="B31" s="3" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Y5-27</t>
+          <t>Y5-17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="I31" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="J31" t="n">
-        <v>25.65</v>
+        <v>23.75</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M31" t="n">
-        <v>870</v>
+        <v>640</v>
       </c>
       <c r="N31" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -4221,18 +4242,18 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="U31" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="V31" t="n">
-        <v>870</v>
+        <v>640</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4248,18 +4269,18 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC31" s="3" t="n"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（2026/5/21）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AE31" s="3" t="n"/>
@@ -4283,79 +4304,79 @@
       <c r="B32" s="3" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-16</t>
+          <t>V5-9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8000</v>
+        <v>1600</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>8000</v>
+        <v>1600</v>
       </c>
       <c r="I32" t="n">
-        <v>16000</v>
+        <v>1600</v>
       </c>
       <c r="J32" t="n">
         <v>23.75</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30060-AG00-1030X100F-A   C</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M32" t="n">
-        <v>640</v>
+        <v>1030</v>
       </c>
       <c r="N32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O32" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30060-AG00-1030X200F-A   C</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V32" t="n">
-        <v>640</v>
+        <v>1030</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4371,7 +4392,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4382,7 +4403,7 @@
       <c r="AC32" s="3" t="n"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AE32" s="3" t="n"/>
@@ -4406,59 +4427,56 @@
       <c r="B33" s="3" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y5-24</t>
+          <t>W5-12</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I33" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="J33" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M33" t="n">
-        <v>870</v>
+        <v>1300</v>
       </c>
       <c r="N33" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46170</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -4467,18 +4485,18 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>15020-AX5R-1440X300F-A   Z</t>
         </is>
       </c>
       <c r="U33" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V33" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4494,18 +4512,18 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC33" s="3" t="n"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE33" s="3" t="n"/>
@@ -4529,76 +4547,76 @@
       <c r="B34" s="3" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Y5-34</t>
+          <t>W5-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="I34" t="n">
         <v>6000</v>
       </c>
       <c r="J34" t="n">
-        <v>25.65</v>
+        <v>9.5</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M34" t="n">
-        <v>680</v>
+        <v>1300</v>
       </c>
       <c r="N34" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   Z</t>
         </is>
       </c>
       <c r="U34" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V34" t="n">
-        <v>680</v>
+        <v>1440</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4614,18 +4632,18 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AC34" s="3" t="n"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE34" s="3" t="n"/>
@@ -4649,59 +4667,59 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Y5-17</t>
+          <t>W5-14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>10000</v>
+        <v>90</v>
       </c>
       <c r="J35" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>10010-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>250</v>
+        <v>22.75</v>
       </c>
       <c r="M35" t="n">
-        <v>640</v>
+        <v>1550</v>
       </c>
       <c r="N35" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4710,18 +4728,18 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>10010-AP67-1550X 91F-A   P</t>
         </is>
       </c>
       <c r="U35" s="3" t="n">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="V35" t="n">
-        <v>640</v>
+        <v>1550</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4737,18 +4755,18 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC35" s="3" t="n"/>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE35" s="3" t="n"/>
@@ -4772,50 +4790,50 @@
       <c r="B36" s="3" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>W5-16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7000</v>
+        <v>20</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7000</v>
+        <v>180</v>
       </c>
       <c r="I36" t="n">
-        <v>14000</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>10025-JR28-1550X 20F-A   G</t>
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="M36" t="n">
-        <v>680</v>
+        <v>1550</v>
       </c>
       <c r="N36" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>46171</v>
@@ -4824,7 +4842,7 @@
         <v>46171</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -4833,18 +4851,18 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>10025-SR28-1650X180F-A   B</t>
         </is>
       </c>
       <c r="U36" s="3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="V36" t="n">
-        <v>680</v>
+        <v>1650</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4860,18 +4878,18 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC36" s="3" t="n"/>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE36" s="3" t="n"/>
@@ -4895,50 +4913,50 @@
       <c r="B37" s="3" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9000</v>
+        <v>20</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9000</v>
+        <v>271</v>
       </c>
       <c r="I37" t="n">
-        <v>18000</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>25.65</v>
+        <v>19</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15020-JW07-1550X 20F-A   V</t>
         </is>
       </c>
       <c r="L37" s="3" t="n">
-        <v>200</v>
+        <v>20.84615384615385</v>
       </c>
       <c r="M37" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="N37" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>46171</v>
@@ -4947,27 +4965,27 @@
         <v>46171</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="U37" s="3" t="n">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="V37" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4983,18 +5001,18 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>（25.65）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC37" s="3" t="n"/>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE37" s="3" t="n"/>
@@ -5018,50 +5036,50 @@
       <c r="B38" s="3" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="I38" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="J38" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M38" t="n">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="N38" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>46171</v>
@@ -5079,18 +5097,18 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="U38" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V38" t="n">
-        <v>1110</v>
+        <v>680</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5106,12 +5124,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC38" s="3" t="n"/>
@@ -5141,50 +5159,53 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>V5-7</t>
+          <t>Y5-28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>400</v>
+        <v>9000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>400</v>
+        <v>9000</v>
       </c>
       <c r="I39" t="n">
-        <v>800</v>
+        <v>18000</v>
       </c>
       <c r="J39" t="n">
-        <v>23.75</v>
+        <v>25.65</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30020-BG00-1030X200F-ABK0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="L39" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M39" t="n">
-        <v>1030</v>
+        <v>870</v>
       </c>
       <c r="N39" t="n">
         <v>200</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>46171</v>
@@ -5199,18 +5220,18 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="U39" s="3" t="n">
         <v>200</v>
       </c>
       <c r="V39" t="n">
-        <v>1030</v>
+        <v>870</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5226,12 +5247,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC39" s="3" t="n"/>
@@ -5261,53 +5282,56 @@
       <c r="B40" s="3" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>Y5-35</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="I40" t="n">
-        <v>9000</v>
+        <v>3200</v>
       </c>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>25.65</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M40" t="n">
-        <v>1440</v>
+        <v>935</v>
       </c>
       <c r="N40" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O40" t="n">
         <v>2</v>
       </c>
+      <c r="P40" s="2" t="n">
+        <v>46171</v>
+      </c>
       <c r="Q40" s="2" t="n">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="R40" s="2" t="n">
         <v>46168</v>
@@ -5319,18 +5343,18 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="U40" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V40" t="n">
-        <v>1440</v>
+        <v>935</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -5346,12 +5370,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（25.65）</t>
         </is>
       </c>
       <c r="AC40" s="3" t="n"/>
@@ -5381,44 +5405,44 @@
       <c r="B41" s="3" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>W5-12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I41" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J41" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="L41" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M41" t="n">
-        <v>1440</v>
+        <v>1300</v>
       </c>
       <c r="N41" t="n">
         <v>300</v>
@@ -5427,10 +5451,10 @@
         <v>2</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -5439,7 +5463,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   Z</t>
         </is>
       </c>
       <c r="U41" s="3" t="n">
@@ -5450,7 +5474,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5466,18 +5490,18 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC41" s="3" t="n"/>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/19）</t>
         </is>
       </c>
       <c r="AE41" s="3" t="n"/>
@@ -5501,56 +5525,59 @@
       <c r="B42" s="3" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>W5-16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1400</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1400</v>
+        <v>180</v>
       </c>
       <c r="I42" t="n">
-        <v>1400</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>10025-JR28-1550X 20F-A   G</t>
         </is>
       </c>
       <c r="L42" s="3" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="M42" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="N42" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2.5</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>46181</v>
+        <v>46171</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -5559,18 +5586,18 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>10025-SR28-1650X180F-A   B</t>
         </is>
       </c>
       <c r="U42" s="3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="V42" t="n">
-        <v>1000</v>
+        <v>1650</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5586,18 +5613,18 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC42" s="3" t="n"/>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE42" s="3" t="n"/>
@@ -5621,76 +5648,79 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>7200</v>
+        <v>6000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>7200</v>
+        <v>6000</v>
       </c>
       <c r="I43" t="n">
-        <v>7200</v>
+        <v>12000</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="L43" s="3" t="n">
         <v>300</v>
       </c>
       <c r="M43" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="N43" t="n">
         <v>300</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="U43" s="3" t="n">
         <v>300</v>
       </c>
       <c r="V43" t="n">
-        <v>770</v>
+        <v>1110</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5706,18 +5736,18 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC43" s="3" t="n"/>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AE43" s="3" t="n"/>
@@ -5741,76 +5771,79 @@
       <c r="B44" s="3" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>W5-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>300</v>
+        <v>91</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>7200</v>
+        <v>90</v>
       </c>
       <c r="J44" t="n">
-        <v>9.5</v>
+        <v>23.75</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>10010-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="M44" t="n">
-        <v>770</v>
+        <v>1550</v>
       </c>
       <c r="N44" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>10010-AP67-1550X 91F-A   P</t>
         </is>
       </c>
       <c r="U44" s="3" t="n">
-        <v>300</v>
+        <v>91</v>
       </c>
       <c r="V44" t="n">
-        <v>770</v>
+        <v>1550</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5826,18 +5859,18 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC44" s="3" t="n"/>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE44" s="3" t="n"/>
@@ -5861,73 +5894,79 @@
       <c r="B45" s="3" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>W5-12</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6000</v>
+        <v>271</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="I45" t="n">
-        <v>6000</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>23.75</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JW07-1550X 20F-A   V</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="M45" t="n">
-        <v>1300</v>
+        <v>1550</v>
       </c>
       <c r="N45" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="O45" t="n">
         <v>2</v>
       </c>
+      <c r="P45" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>46171</v>
+      </c>
       <c r="R45" s="2" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   Z</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="U45" s="3" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="V45" t="n">
-        <v>1440</v>
+        <v>1550</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5943,18 +5982,18 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>（19）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC45" s="3" t="n"/>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AE45" s="3" t="n"/>
@@ -5972,19 +6011,18 @@
       <c r="AI45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5993,42 +6031,42 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="I46" t="n">
-        <v>2000</v>
+        <v>9000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>19</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>15025-NR28-1550X250F-ABK0J</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M46" t="n">
-        <v>1550</v>
+        <v>1440</v>
       </c>
       <c r="N46" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>46161</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -6037,18 +6075,18 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>15025-SR28-1550X250F-ABK0J</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U46" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="V46" t="n">
-        <v>1550</v>
+        <v>1440</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>EC,巻返し</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -6064,18 +6102,18 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>巻返し+EC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC46" s="3" t="n"/>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AE46" s="3" t="n"/>
@@ -6093,83 +6131,82 @@
       <c r="AI46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>193</v>
+        <v>9000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>200</v>
+        <v>9000</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>9000</v>
       </c>
       <c r="J47" t="n">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15024-XXXX-1600X 10F-A   B</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="M47" t="n">
-        <v>1600</v>
+        <v>1440</v>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="O47" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15024-SRHW-1860X193F-A   B</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="U47" s="3" t="n">
-        <v>193</v>
+        <v>300</v>
       </c>
       <c r="V47" t="n">
-        <v>1860</v>
+        <v>1440</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>分割,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -6185,18 +6222,18 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>（23.75）</t>
+          <t>（9.5）</t>
         </is>
       </c>
       <c r="AC47" s="3" t="n"/>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AE47" s="3" t="n"/>
@@ -6214,83 +6251,82 @@
       <c r="AI47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y5-19</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="I48" t="n">
-        <v>6000</v>
+        <v>2000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>19</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M48" t="n">
-        <v>550</v>
+        <v>1180</v>
       </c>
       <c r="N48" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>46163</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="U48" s="3" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="V48" t="n">
-        <v>1110</v>
+        <v>1250</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -6306,18 +6342,18 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC48" s="3" t="n"/>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>（2026/5/14）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AE48" s="3" t="n"/>
@@ -6335,19 +6371,18 @@
       <c r="AI48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JR260502</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6356,42 +6391,42 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="I49" t="n">
-        <v>760</v>
+        <v>2000</v>
+      </c>
+      <c r="J49" t="n">
+        <v>23.75</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="M49" t="n">
-        <v>870</v>
+        <v>1180</v>
       </c>
       <c r="N49" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>46167</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -6400,18 +6435,18 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="U49" s="3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="V49" t="n">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -6427,18 +6462,18 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（23.75）</t>
         </is>
       </c>
       <c r="AC49" s="3" t="n"/>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>（2026/5/19）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AE49" s="3" t="n"/>
@@ -6456,63 +6491,65 @@
       <c r="AI49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>12000</v>
+        <v>1400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>12000</v>
+        <v>1400</v>
       </c>
       <c r="I50" t="n">
-        <v>12000</v>
+        <v>1400</v>
+      </c>
+      <c r="J50" t="n">
+        <v>19</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M50" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="N50" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -6521,18 +6558,18 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="U50" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V50" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6548,18 +6585,18 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC50" s="3" t="n"/>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AE50" s="3" t="n"/>
@@ -6577,66 +6614,62 @@
       <c r="AI50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>W5-13</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="I51" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="J51" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>15020-JX5R- 770X300F-A   R</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M51" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="N51" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
       </c>
-      <c r="P51" s="2" t="n">
-        <v>46162</v>
-      </c>
       <c r="Q51" s="2" t="n">
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -6645,18 +6678,18 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>15020-AX5R- 770X300F-A   P</t>
         </is>
       </c>
       <c r="U51" s="3" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V51" t="n">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6672,18 +6705,18 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>（9.5）</t>
+          <t>（19）</t>
         </is>
       </c>
       <c r="AC51" s="3" t="n"/>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>（2026/5/13）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AE51" s="3" t="n"/>
@@ -6699,6 +6732,985 @@
         </is>
       </c>
       <c r="AI51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>W5-13</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>15020-JX5R- 770X300F-A   R</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M52" t="n">
+        <v>770</v>
+      </c>
+      <c r="N52" t="n">
+        <v>300</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>15020-AX5R- 770X300F-A   P</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="V52" t="n">
+        <v>770</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="n"/>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>（2026/6/3）</t>
+        </is>
+      </c>
+      <c r="AE52" s="3" t="n"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="n"/>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Y5-36</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>30030-BG00-1000X100F-ABK0C</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N53" t="n">
+        <v>100</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>30060-AG00-1000X200F-ABK0C</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>分割,スライス</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>分割+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="n"/>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>（2026/5/18）</t>
+        </is>
+      </c>
+      <c r="AE53" s="3" t="n"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="n"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>W5-15</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>400</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>400</v>
+      </c>
+      <c r="I54" t="n">
+        <v>80</v>
+      </c>
+      <c r="J54" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>15015-JP67-1550X 20F-A   P</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1550</v>
+      </c>
+      <c r="N54" t="n">
+        <v>20</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>15015-AP67-1550X400F-A   K</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1550</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>分割,スリット,EC</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>分割+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="n"/>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>（2026/5/18）</t>
+        </is>
+      </c>
+      <c r="AE54" s="3" t="n"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="n"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Y5-19</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M55" t="n">
+        <v>550</v>
+      </c>
+      <c r="N55" t="n">
+        <v>300</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1110</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="n"/>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>（2026/5/18）</t>
+        </is>
+      </c>
+      <c r="AE55" s="3" t="n"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="n"/>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JR260502</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>800</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>800</v>
+      </c>
+      <c r="I56" t="n">
+        <v>760</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>40040-R10W- 870X 95</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="M56" t="n">
+        <v>870</v>
+      </c>
+      <c r="N56" t="n">
+        <v>95</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>FEL4004AY-10WD-1000X100</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="n"/>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>（2026/5/19）</t>
+        </is>
+      </c>
+      <c r="AE56" s="3" t="n"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="n"/>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>W5-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>180</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>180</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>10025-JR28-1550X 20F-A   G</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1550</v>
+      </c>
+      <c r="N57" t="n">
+        <v>20</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>10025-SR28-1650X180F-A   B</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1650</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>分割,スリット,EC</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>分割+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>（23.75）</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="n"/>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>（2026/5/22）</t>
+        </is>
+      </c>
+      <c r="AE57" s="3" t="n"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="n"/>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Y5-20</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="M58" t="n">
+        <v>550</v>
+      </c>
+      <c r="N58" t="n">
+        <v>300</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1110</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="n"/>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>（2026/5/26）</t>
+        </is>
+      </c>
+      <c r="AE58" s="3" t="n"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="n"/>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Y5-10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3600</v>
+      </c>
+      <c r="J59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M59" t="n">
+        <v>740</v>
+      </c>
+      <c r="N59" t="n">
+        <v>200</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="V59" t="n">
+        <v>750</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
+        <v>2600</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>（9.5）</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="n"/>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>（2026/5/13）</t>
+        </is>
+      </c>
+      <c r="AE59" s="3" t="n"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="n"/>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI59" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AL65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,71 +611,6 @@
           <t>AI特別指定_解析</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>」グローバルコメント解析】</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>参照用・段階2で自動記録</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -680,91 +619,85 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>Y5-16</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79412</v>
+        <v>79393</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2700</v>
+        <v>8000</v>
       </c>
       <c r="H2" t="n">
-        <v>600</v>
+        <v>2600</v>
       </c>
       <c r="I2" t="n">
-        <v>600</v>
+        <v>2600</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>2700</v>
+        <v>16000</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O2" t="n">
-        <v>1440</v>
+        <v>640</v>
       </c>
       <c r="P2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026/05/27</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026/05/27</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
+        <v>3.3</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>46162</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X2" t="n">
-        <v>1440</v>
+        <v>640</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -773,19 +706,19 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>2100</v>
+        <v>5400</v>
       </c>
       <c r="AB2" t="n">
-        <v>2100</v>
+        <v>10800</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -808,27 +741,6 @@
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>※二重適用についで</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>配台への反映はメインシート「グローバルコメント」からのみ行ゝれした。このAX〜AY列は読み坖られません。編集しても次回実行まで配台に効しません。原文はメイン欄を参照してください。</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -837,91 +749,85 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y5-16</t>
+          <t>Y5-24</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79393</v>
+        <v>79402</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H3" t="n">
-        <v>2600</v>
+        <v>4600</v>
       </c>
       <c r="I3" t="n">
-        <v>2600</v>
+        <v>4600</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>200</v>
       </c>
       <c r="O3" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="P3" t="n">
         <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026/05/27</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026/05/27</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>200</v>
       </c>
       <c r="X3" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -930,25 +836,25 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="AB3" t="n">
-        <v>10800</v>
+        <v>8800</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -965,27 +871,6 @@
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>計画基準日時</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,91 +879,85 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Y5-24</t>
+          <t>W5-13</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79402</v>
+        <v>79641</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9000</v>
+        <v>7200</v>
       </c>
       <c r="H4" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4600</v>
+        <v>7200</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>7200</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15020-JX5R- 770X300F-A   R</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O4" t="n">
-        <v>870</v>
+        <v>770</v>
       </c>
       <c r="P4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>46162</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>15020-AX5R- 770X300F-A   P</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X4" t="n">
-        <v>870</v>
+        <v>770</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1087,25 +966,25 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/20）</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1122,27 +1001,6 @@
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>工場休業日</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,71 +1009,65 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>Y5-34</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79641</v>
+        <v>79583</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>7200</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O5" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="P5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1224,18 +1076,18 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X5" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1251,18 +1103,18 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1279,27 +1131,6 @@
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>スキル覝件を無視</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,91 +1139,85 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Y5-34</t>
+          <t>V5-7</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79583</v>
+        <v>79604</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-A   C</t>
+          <t>30020-BG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="N6" t="n">
         <v>200</v>
       </c>
       <c r="O6" t="n">
-        <v>680</v>
+        <v>1030</v>
       </c>
       <c r="P6" t="n">
         <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>46167</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-A   C</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>200</v>
       </c>
       <c r="X6" t="n">
-        <v>680</v>
+        <v>1030</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1408,18 +1233,18 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1436,27 +1261,6 @@
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>need人数1固定</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1465,11 +1269,11 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V5-7</t>
+          <t>Y5-17</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79604</v>
+        <v>79395</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1482,54 +1286,48 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>800</v>
+        <v>10000</v>
       </c>
       <c r="L7" t="n">
         <v>25</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30020-BG00-1030X200F-ABK0C</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O7" t="n">
-        <v>1030</v>
+        <v>640</v>
       </c>
       <c r="P7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
+      <c r="R7" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>46167</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1538,14 +1336,14 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X7" t="n">
-        <v>1030</v>
+        <v>640</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1593,27 +1391,6 @@
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>配台制限の撤廃</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1622,71 +1399,65 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Y5-17</t>
+          <t>V5-9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79395</v>
+        <v>79688</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5000</v>
+        <v>1600</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5000</v>
+        <v>1600</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>10000</v>
+        <v>1600</v>
       </c>
       <c r="L8" t="n">
         <v>25</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>30060-AG00-1030X100F-A   C</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>640</v>
+        <v>1030</v>
       </c>
       <c r="P8" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1695,18 +1466,18 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>30060-AG00-1030X200F-A   C</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="X8" t="n">
-        <v>640</v>
+        <v>1030</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1722,7 +1493,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1733,7 +1504,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1750,27 +1521,6 @@
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>グローバルOP指定</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1779,71 +1529,65 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V5-9</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79688</v>
+        <v>79706</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I9" t="n">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X100F-A   C</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O9" t="n">
-        <v>1030</v>
+        <v>1180</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1852,18 +1596,18 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X200F-A   C</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X9" t="n">
-        <v>1030</v>
+        <v>1250</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1879,18 +1623,18 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr"/>
@@ -1907,27 +1651,6 @@
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>日付×工程フォーム指定</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1936,11 +1659,11 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C5-1</t>
+          <t>W5-14</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79706</v>
+        <v>79683</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1953,54 +1676,48 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4000</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>4000</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>4000</v>
+        <v>91</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2000</v>
+        <v>90</v>
       </c>
       <c r="L10" t="n">
         <v>20</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20010-H600-1180X250F-AWH1C</t>
+          <t>10010-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
-        <v>1180</v>
+        <v>1550</v>
       </c>
       <c r="P10" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+      <c r="R10" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2009,18 +1726,18 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>20010-B600-1250X250F-AWH1C</t>
+          <t>10010-AP67-1550X 91F-A   P</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="X10" t="n">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>スリット,EC</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2064,27 +1781,6 @@
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>グローバル速度ルール</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2093,11 +1789,11 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W5-14</t>
+          <t>W5-16</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79683</v>
+        <v>79686</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2116,20 +1812,20 @@
         <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="L11" t="n">
         <v>20</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10010-JP67-1550X 20F-A   P</t>
+          <t>10025-JR28-1550X 20F-A   G</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2142,22 +1838,16 @@
         <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2166,18 +1856,18 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10010-AP67-1550X 91F-A   P</t>
+          <t>10025-SR28-1650X180F-A   B</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="X11" t="n">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2221,27 +1911,6 @@
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>未適用メモ(AI)</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2250,11 +1919,11 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79686</v>
+        <v>79687</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2273,20 +1942,20 @@
         <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
         <v>20</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>15020-JW07-1550X 20F-A   V</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2299,42 +1968,36 @@
         <v>20</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="X12" t="n">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2378,27 +2041,6 @@
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>AI覝約</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2407,91 +2049,85 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79687</v>
+        <v>79404</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>7000</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>271</v>
+        <v>7000</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>14000</v>
       </c>
       <c r="L13" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="O13" t="n">
-        <v>1550</v>
+        <v>680</v>
       </c>
       <c r="P13" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="X13" t="n">
-        <v>1550</v>
+        <v>680</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2507,18 +2143,18 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
@@ -2535,19 +2171,6 @@
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2556,11 +2179,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>Y5-28</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79404</v>
+        <v>79408</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2573,33 +2196,33 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I14" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="J14" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K14" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="L14" t="n">
         <v>27</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>200</v>
       </c>
       <c r="O14" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P14" t="n">
         <v>200</v>
@@ -2607,20 +2230,14 @@
       <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+      <c r="R14" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>46167</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2629,14 +2246,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>200</v>
       </c>
       <c r="X14" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -2667,7 +2284,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr"/>
@@ -2684,19 +2301,6 @@
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2705,11 +2309,11 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>Y5-35</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79408</v>
+        <v>79676</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2722,54 +2326,48 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="J15" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>18000</v>
+        <v>3200</v>
       </c>
       <c r="L15" t="n">
         <v>27</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>200</v>
       </c>
       <c r="O15" t="n">
-        <v>870</v>
+        <v>935</v>
       </c>
       <c r="P15" t="n">
         <v>200</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2778,14 +2376,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>200</v>
       </c>
       <c r="X15" t="n">
-        <v>870</v>
+        <v>935</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -2816,7 +2414,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
@@ -2833,19 +2431,6 @@
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2854,11 +2439,11 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Y5-35</t>
+          <t>Y5-38</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79676</v>
+        <v>79823</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2871,70 +2456,64 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="L16" t="n">
         <v>27</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>0R040-8Y0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>200</v>
       </c>
       <c r="O16" t="n">
-        <v>935</v>
+        <v>850</v>
       </c>
       <c r="P16" t="n">
         <v>200</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>50080-AY0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="W16" t="n">
         <v>200</v>
       </c>
       <c r="X16" t="n">
-        <v>935</v>
+        <v>850</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2965,7 +2544,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr"/>
@@ -2982,19 +2561,6 @@
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3003,11 +2569,11 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Y5-38</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79823</v>
+        <v>79913</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3029,45 +2595,39 @@
         <v>2000</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>4000</v>
+        <v>1933</v>
       </c>
       <c r="L17" t="n">
         <v>27</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 850X200F-AGA1C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O17" t="n">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="P17" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3076,18 +2636,18 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>50080-AY0B- 850X200F-AGA1C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X17" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -3131,19 +2691,6 @@
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3152,91 +2699,85 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>79913</v>
+        <v>79398</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="J18" t="n">
         <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>1933</v>
+        <v>12000</v>
       </c>
       <c r="L18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="O18" t="n">
-        <v>870</v>
+        <v>550</v>
       </c>
       <c r="P18" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3252,18 +2793,18 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
@@ -3280,19 +2821,6 @@
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3301,11 +2829,11 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79398</v>
+        <v>79913</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3318,74 +2846,68 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6000</v>
+        <v>1943</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="J19" t="n">
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>12000</v>
+        <v>1933</v>
       </c>
       <c r="L19" t="n">
         <v>25</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="O19" t="n">
-        <v>550</v>
+        <v>870</v>
       </c>
       <c r="P19" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X19" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -3412,7 +2934,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
@@ -3429,19 +2951,6 @@
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3450,15 +2959,15 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79913</v>
+        <v>79687</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3467,54 +2976,48 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1943</v>
+        <v>271</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="I20" t="n">
-        <v>2000</v>
+        <v>271</v>
       </c>
       <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>20</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1933</v>
       </c>
       <c r="L20" t="n">
         <v>25</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>15020-JW07-1550X 20F-A   V</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="P20" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+      <c r="R20" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3523,18 +3026,18 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3550,7 +3053,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3561,7 +3064,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr"/>
@@ -3578,19 +3081,6 @@
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3599,71 +3089,65 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>PN06-01</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79687</v>
+        <v>79935</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>271</v>
+        <v>2000</v>
       </c>
       <c r="H21" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>271</v>
+        <v>2000</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="L21" t="n">
         <v>25</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="P21" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+      <c r="R21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3672,18 +3156,18 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="X21" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3699,7 +3183,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3710,7 +3194,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr"/>
@@ -3727,19 +3211,6 @@
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3748,15 +3219,15 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79935</v>
+        <v>79821</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3765,54 +3236,48 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>2000</v>
+        <v>2850</v>
       </c>
       <c r="L22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N22" t="n">
         <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>1000</v>
+        <v>316</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3821,7 +3286,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -3832,7 +3297,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3848,12 +3313,12 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>EC+SEC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3876,19 +3341,6 @@
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3905,16 +3357,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3929,7 +3381,7 @@
         <v>2850</v>
       </c>
       <c r="L23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3948,20 +3400,14 @@
       <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R23" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3997,12 +3443,12 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -4025,19 +3471,6 @@
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4046,91 +3479,83 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79821</v>
+        <v>79414</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>950</v>
+        <v>9000</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>2850</v>
+        <v>9000</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O24" t="n">
-        <v>316</v>
+        <v>1440</v>
       </c>
       <c r="P24" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -4146,18 +3571,18 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr"/>
@@ -4174,19 +3599,6 @@
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4203,12 +3615,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4227,7 +3639,7 @@
         <v>9000</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -4247,15 +3659,11 @@
         <v>2</v>
       </c>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+      <c r="S25" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4291,12 +3699,12 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -4319,19 +3727,6 @@
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4340,87 +3735,85 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79414</v>
+        <v>79926</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9000</v>
+        <v>3995</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>9000</v>
+        <v>4085</v>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>3880</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="O26" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="P26" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+      <c r="R26" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="X26" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4436,18 +3829,18 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr"/>
@@ -4464,19 +3857,6 @@
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4493,31 +3873,31 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3995</v>
+        <v>3880</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4085</v>
+        <v>3895</v>
       </c>
       <c r="J27" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
         <v>3880</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -4536,20 +3916,14 @@
       <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R27" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4585,12 +3959,12 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -4613,19 +3987,6 @@
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4634,71 +3995,65 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79926</v>
+        <v>79754</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3880</v>
+        <v>1155</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3895</v>
+        <v>1155</v>
       </c>
       <c r="J28" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>3880</v>
+        <v>2310</v>
       </c>
       <c r="L28" t="n">
         <v>25</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="O28" t="n">
-        <v>870</v>
+        <v>1080</v>
       </c>
       <c r="P28" t="n">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4707,18 +4062,18 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4734,7 +4089,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4745,7 +4100,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr"/>
@@ -4762,19 +4117,6 @@
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4783,11 +4125,11 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79754</v>
+        <v>79996</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4800,74 +4142,68 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1155</v>
+        <v>3200</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1155</v>
+        <v>3200</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>2310</v>
+        <v>6400</v>
       </c>
       <c r="L29" t="n">
         <v>25</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="O29" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="P29" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="X29" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4911,19 +4247,6 @@
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4932,11 +4255,11 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>Y6-1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79996</v>
+        <v>79867</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4949,63 +4272,57 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
-        <v>6400</v>
+        <v>4800</v>
       </c>
       <c r="L30" t="n">
         <v>25</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O30" t="n">
         <v>1000</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -5016,7 +4333,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -5043,7 +4360,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -5060,19 +4377,6 @@
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5081,71 +4385,63 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Y6-1</t>
+          <t>Y5-39</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>79867</v>
+        <v>79825</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>4800</v>
+        <v>200</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N31" t="n">
         <v>200</v>
       </c>
       <c r="O31" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P31" t="n">
         <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5154,18 +4450,18 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W31" t="n">
         <v>200</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -5181,18 +4477,18 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr"/>
@@ -5209,19 +4505,6 @@
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5230,11 +4513,11 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-39</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79825</v>
+        <v>79826</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5247,19 +4530,19 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
@@ -5281,36 +4564,34 @@
       <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+      <c r="R32" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X32" t="n">
         <v>750</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -5354,19 +4635,6 @@
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5375,11 +4643,11 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>Y5-41</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79826</v>
+        <v>79827</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5392,26 +4660,26 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L33" t="n">
         <v>10</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5424,42 +4692,36 @@
         <v>200</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X33" t="n">
         <v>750</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -5503,19 +4765,6 @@
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5524,71 +4773,65 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Y5-41</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>79827</v>
+        <v>79754</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>200</v>
+        <v>2310</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>200</v>
+        <v>2310</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>200</v>
+        <v>2310</v>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="O34" t="n">
-        <v>740</v>
+        <v>1080</v>
       </c>
       <c r="P34" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5597,18 +4840,18 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="X34" t="n">
-        <v>750</v>
+        <v>1080</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -5624,18 +4867,18 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr"/>
@@ -5652,19 +4895,6 @@
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5673,71 +4903,65 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>Y6-2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>79754</v>
+        <v>79868</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2310</v>
+        <v>2800</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2310</v>
+        <v>2800</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>2310</v>
+        <v>5600</v>
       </c>
       <c r="L35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O35" t="n">
-        <v>1080</v>
+        <v>640</v>
       </c>
       <c r="P35" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>3.3</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5746,18 +4970,18 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="X35" t="n">
-        <v>1080</v>
+        <v>640</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -5773,12 +4997,12 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -5801,19 +5025,6 @@
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5822,11 +5033,11 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Y6-2</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>79868</v>
+        <v>79822</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5839,54 +5050,46 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>5600</v>
+        <v>4000</v>
       </c>
       <c r="L36" t="n">
         <v>25</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N36" t="n">
         <v>200</v>
       </c>
       <c r="O36" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="P36" t="n">
         <v>200</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5895,14 +5098,14 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>200</v>
       </c>
       <c r="X36" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -5950,19 +5153,6 @@
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5971,87 +5161,83 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79822</v>
+        <v>79994</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J37" t="n">
         <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="L37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>30100-VG00-1000X 50F-A   C</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O37" t="n">
         <v>1000</v>
       </c>
       <c r="P37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+      <c r="S37" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30100-NG00-1000X 50F-A   C</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -6067,18 +5253,18 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr"/>
@@ -6095,19 +5281,6 @@
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6116,67 +5289,65 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>79994</v>
+        <v>79605</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="L38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X 50F-A   C</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O38" t="n">
         <v>1000</v>
       </c>
       <c r="P38" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6185,18 +5356,18 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X 50F-A   C</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -6212,12 +5383,12 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -6240,19 +5411,6 @@
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6261,91 +5419,83 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>79605</v>
+        <v>79989</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="L39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N39" t="n">
         <v>200</v>
       </c>
       <c r="O39" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P39" t="n">
         <v>200</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -6361,18 +5511,18 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr"/>
@@ -6389,90 +5539,73 @@
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>Y6-6</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>79994</v>
+        <v>79874</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>500</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="L40" t="n">
+        <v>27</v>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X 50F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O40" t="n">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="P40" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6481,18 +5614,18 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X 50F-A   C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -6508,18 +5641,18 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>巻返し+エンボス　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr"/>
@@ -6536,19 +5669,6 @@
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6557,87 +5677,85 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>Y6-7</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>79989</v>
+        <v>79875</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>1200</v>
+        <v>7600</v>
       </c>
       <c r="L41" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N41" t="n">
         <v>200</v>
       </c>
       <c r="O41" t="n">
-        <v>740</v>
+        <v>870</v>
       </c>
       <c r="P41" t="n">
         <v>200</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X41" t="n">
-        <v>750</v>
+        <v>870</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -6653,12 +5771,12 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -6681,19 +5799,6 @@
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6702,11 +5807,11 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Y6-6</t>
+          <t>Y6-8</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>79874</v>
+        <v>79876</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -6719,33 +5824,33 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="L42" t="n">
         <v>27</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N42" t="n">
         <v>200</v>
       </c>
       <c r="O42" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P42" t="n">
         <v>200</v>
@@ -6753,20 +5858,14 @@
       <c r="Q42" t="n">
         <v>4</v>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R42" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6775,14 +5874,14 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W42" t="n">
         <v>200</v>
       </c>
       <c r="X42" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -6830,19 +5929,6 @@
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6851,43 +5937,43 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Y6-7</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>79875</v>
+        <v>79871</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>7600</v>
+        <v>6400</v>
       </c>
       <c r="L43" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6902,20 +5988,14 @@
       <c r="Q43" t="n">
         <v>4</v>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R43" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6924,7 +6004,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -6935,7 +6015,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -6951,18 +6031,18 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr"/>
@@ -6979,19 +6059,6 @@
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7000,11 +6067,11 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y6-8</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>79876</v>
+        <v>79871</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -7017,19 +6084,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
-        <v>1600</v>
+        <v>6400</v>
       </c>
       <c r="L44" t="n">
         <v>27</v>
@@ -7051,20 +6118,14 @@
       <c r="Q44" t="n">
         <v>4</v>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R44" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7073,7 +6134,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -7084,7 +6145,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -7111,7 +6172,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr"/>
@@ -7128,19 +6189,6 @@
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7149,11 +6197,11 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>79871</v>
+        <v>79872</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -7166,26 +6214,26 @@
         </is>
       </c>
       <c r="G45" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K45" t="n">
         <v>3200</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J45" t="n">
-        <v>16</v>
-      </c>
-      <c r="K45" t="n">
-        <v>6400</v>
       </c>
       <c r="L45" t="n">
         <v>20</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7200,20 +6248,14 @@
       <c r="Q45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R45" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7222,7 +6264,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -7277,19 +6319,6 @@
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7298,11 +6327,11 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79871</v>
+        <v>79872</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -7315,26 +6344,26 @@
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" t="n">
         <v>3200</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J46" t="n">
-        <v>16</v>
-      </c>
-      <c r="K46" t="n">
-        <v>6400</v>
       </c>
       <c r="L46" t="n">
         <v>27</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7349,20 +6378,14 @@
       <c r="Q46" t="n">
         <v>4</v>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R46" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7371,7 +6394,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7426,19 +6449,6 @@
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
-      <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7447,11 +6457,11 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -7464,33 +6474,33 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="L47" t="n">
         <v>20</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N47" t="n">
         <v>200</v>
       </c>
       <c r="O47" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P47" t="n">
         <v>200</v>
@@ -7498,20 +6508,14 @@
       <c r="Q47" t="n">
         <v>4</v>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R47" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7520,14 +6524,14 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W47" t="n">
         <v>200</v>
       </c>
       <c r="X47" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -7575,19 +6579,6 @@
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7596,11 +6587,11 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -7613,33 +6604,33 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="J48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="L48" t="n">
         <v>27</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>200</v>
       </c>
       <c r="O48" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P48" t="n">
         <v>200</v>
@@ -7647,20 +6638,14 @@
       <c r="Q48" t="n">
         <v>4</v>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R48" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7669,14 +6654,14 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>200</v>
       </c>
       <c r="X48" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -7724,19 +6709,6 @@
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7745,91 +6717,85 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>79873</v>
+        <v>79927</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>600</v>
+        <v>29400</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>600</v>
+        <v>29400</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="K49" t="n">
-        <v>1200</v>
+        <v>29400</v>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O49" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="P49" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X49" t="n">
-        <v>680</v>
+        <v>1050</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -7845,18 +6811,18 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr"/>
@@ -7873,19 +6839,6 @@
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7894,71 +6847,63 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79873</v>
+        <v>79987</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L50" t="n">
+        <v>25</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>300</v>
+      </c>
+      <c r="O50" t="n">
+        <v>550</v>
+      </c>
+      <c r="P50" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q50" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L50" t="n">
-        <v>27</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>200</v>
-      </c>
-      <c r="O50" t="n">
-        <v>680</v>
-      </c>
-      <c r="P50" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7967,18 +6912,18 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X50" t="n">
-        <v>680</v>
+        <v>1110</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -7994,18 +6939,18 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr"/>
@@ -8022,19 +6967,6 @@
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8043,11 +6975,11 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79927</v>
+        <v>79985</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -8060,74 +6992,66 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>29400</v>
+        <v>5400</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>29400</v>
+        <v>5400</v>
       </c>
       <c r="J51" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>29400</v>
+        <v>10800</v>
       </c>
       <c r="L51" t="n">
         <v>25</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>300</v>
       </c>
       <c r="O51" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P51" t="n">
         <v>300</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>2026/06/12</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026/06/12</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>300</v>
       </c>
       <c r="X51" t="n">
-        <v>1050</v>
+        <v>1110</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -8154,7 +7078,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr"/>
@@ -8171,19 +7095,6 @@
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8192,15 +7103,15 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>V6-2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79987</v>
+        <v>79995</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8209,50 +7120,48 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="L52" t="n">
         <v>25</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P52" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="R52" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="S52" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>46184</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8261,18 +7170,18 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X52" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -8288,7 +7197,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8299,7 +7208,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/11）</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr"/>
@@ -8316,19 +7225,6 @@
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr"/>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8337,87 +7233,85 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>Y5-42</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79985</v>
+        <v>79828</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="J53" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>10800</v>
+        <v>1200</v>
       </c>
       <c r="L53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O53" t="n">
-        <v>550</v>
+        <v>740</v>
       </c>
       <c r="P53" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R53" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S53" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X53" t="n">
-        <v>1110</v>
+        <v>750</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -8433,18 +7327,18 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
@@ -8461,32 +7355,21 @@
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>V6-2</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79995</v>
+        <v>79996</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -8495,30 +7378,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>10000</v>
+        <v>6400</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>10000</v>
+        <v>6400</v>
       </c>
       <c r="J54" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="K54" t="n">
-        <v>10000</v>
+        <v>6400</v>
       </c>
       <c r="L54" t="n">
         <v>25</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8531,22 +7414,16 @@
         <v>100</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>2026/06/17</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>2026/06/17</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R54" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S54" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T54" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8566,7 +7443,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -8582,7 +7459,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8593,7 +7470,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>（2026/6/11）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr"/>
@@ -8610,112 +7487,91 @@
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79828</v>
+        <v>79985</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1200</v>
+        <v>10800</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1200</v>
+        <v>10800</v>
       </c>
       <c r="J55" t="n">
+        <v>36</v>
+      </c>
+      <c r="K55" t="n">
+        <v>10800</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>300</v>
+      </c>
+      <c r="O55" t="n">
+        <v>550</v>
+      </c>
+      <c r="P55" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q55" t="n">
         <v>3</v>
       </c>
-      <c r="K55" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L55" t="n">
-        <v>10</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>200</v>
-      </c>
-      <c r="O55" t="n">
-        <v>740</v>
-      </c>
-      <c r="P55" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T55" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X55" t="n">
-        <v>750</v>
+        <v>1110</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -8731,18 +7587,18 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr"/>
@@ -8759,19 +7615,6 @@
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -8782,71 +7625,61 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79996</v>
+        <v>79987</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6400</v>
+        <v>12000</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>6400</v>
+        <v>12000</v>
       </c>
       <c r="J56" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>6400</v>
-      </c>
-      <c r="L56" t="n">
-        <v>25</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O56" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P56" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q56" t="n">
         <v>3</v>
       </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8855,18 +7688,18 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -8882,18 +7715,18 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr"/>
@@ -8910,19 +7743,6 @@
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -8933,11 +7753,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>79985</v>
+        <v>79398</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -8950,19 +7770,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="J57" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
@@ -8982,16 +7802,14 @@
       <c r="Q57" t="n">
         <v>3</v>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+      <c r="R57" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S57" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T57" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9038,7 +7856,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr"/>
@@ -9055,19 +7873,6 @@
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="inlineStr"/>
-      <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="inlineStr"/>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr"/>
-      <c r="AV57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr"/>
-      <c r="AX57" t="inlineStr"/>
-      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -9078,15 +7883,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>79987</v>
+        <v>79913</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9095,68 +7900,66 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="J58" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>12000</v>
+        <v>1933</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="O58" t="n">
-        <v>550</v>
+        <v>870</v>
       </c>
       <c r="P58" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R58" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S58" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T58" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X58" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -9172,7 +7975,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9183,7 +7986,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr"/>
@@ -9200,19 +8003,6 @@
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
-      <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr"/>
-      <c r="AV58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr"/>
-      <c r="AX58" t="inlineStr"/>
-      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -9223,15 +8013,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79398</v>
+        <v>79821</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9240,72 +8030,66 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="J59" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>12000</v>
+        <v>2850</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>550</v>
+        <v>316</v>
       </c>
       <c r="P59" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R59" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S59" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T59" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X59" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -9321,7 +8105,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9332,7 +8116,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr"/>
@@ -9349,19 +8133,6 @@
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="inlineStr"/>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
-      <c r="AV59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr"/>
-      <c r="AX59" t="inlineStr"/>
-      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -9372,11 +8143,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>79913</v>
+        <v>79926</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -9389,24 +8160,24 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2000</v>
+        <v>4085</v>
       </c>
       <c r="J60" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K60" t="n">
-        <v>1933</v>
+        <v>3880</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9421,20 +8192,14 @@
       <c r="Q60" t="n">
         <v>2</v>
       </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+      <c r="R60" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S60" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T60" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9443,11 +8208,11 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -9481,7 +8246,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr"/>
@@ -9498,19 +8263,6 @@
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="inlineStr"/>
-      <c r="AR60" t="inlineStr"/>
-      <c r="AS60" t="inlineStr"/>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="inlineStr"/>
-      <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
-      <c r="AX60" t="inlineStr"/>
-      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -9521,11 +8273,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>PN06-01</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>79821</v>
+        <v>79935</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -9534,56 +8286,50 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>2850</v>
+        <v>2000</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>316</v>
+        <v>1000</v>
       </c>
       <c r="P61" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R61" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S61" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T61" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9592,7 +8338,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -9603,7 +8349,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -9619,7 +8365,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>梱包+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9647,19 +8393,6 @@
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
-      <c r="AR61" t="inlineStr"/>
-      <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="inlineStr"/>
-      <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -9670,69 +8403,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>79926</v>
+        <v>79989</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>4085</v>
+        <v>1200</v>
       </c>
       <c r="J62" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>3880</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>1200</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10</v>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O62" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P62" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T62" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9741,18 +8468,18 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W62" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -9768,18 +8495,18 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>分割+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr"/>
@@ -9796,19 +8523,6 @@
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="inlineStr"/>
-      <c r="AQ62" t="inlineStr"/>
-      <c r="AR62" t="inlineStr"/>
-      <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr"/>
-      <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -9819,89 +8533,81 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>79935</v>
+        <v>79994</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>30100-VG00-1000X 50F-A   C</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O63" t="n">
         <v>1000</v>
       </c>
       <c r="P63" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T63" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>30100-NG00-1000X 50F-A   C</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -9917,7 +8623,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>梱包+SEC機　湖南</t>
+          <t>巻返し+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9928,7 +8634,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr"/>
@@ -9945,19 +8651,6 @@
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="inlineStr"/>
-      <c r="AS63" t="inlineStr"/>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AU63" t="inlineStr"/>
-      <c r="AV63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr"/>
-      <c r="AX63" t="inlineStr"/>
-      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -9968,11 +8661,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>79989</v>
+        <v>79826</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -9985,19 +8678,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="L64" t="n">
         <v>10</v>
@@ -10019,20 +8712,18 @@
       <c r="Q64" t="n">
         <v>2</v>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R64" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S64" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T64" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -10075,7 +8766,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr"/>
@@ -10092,19 +8783,6 @@
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
-      <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="inlineStr"/>
-      <c r="AR64" t="inlineStr"/>
-      <c r="AS64" t="inlineStr"/>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AU64" t="inlineStr"/>
-      <c r="AV64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr"/>
-      <c r="AX64" t="inlineStr"/>
-      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -10115,11 +8793,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>Y5-42</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>79826</v>
+        <v>79828</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -10132,19 +8810,19 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="L65" t="n">
         <v>10</v>
@@ -10166,24 +8844,18 @@
       <c r="Q65" t="n">
         <v>2</v>
       </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+      <c r="R65" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S65" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T65" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -10243,170 +8915,6 @@
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr"/>
-      <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="inlineStr"/>
-      <c r="AS65" t="inlineStr"/>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr"/>
-      <c r="AV65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr"/>
-      <c r="AX65" t="inlineStr"/>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Y5-42</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>79828</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>分割</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>エンボス　湖南</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L66" t="n">
-        <v>10</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>200</v>
-      </c>
-      <c r="O66" t="n">
-        <v>740</v>
-      </c>
-      <c r="P66" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
-        </is>
-      </c>
-      <c r="W66" t="n">
-        <v>400</v>
-      </c>
-      <c r="X66" t="n">
-        <v>750</v>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>分割,エンボス</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>分割+エンボス　湖南</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>（10）</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>（2026/6/3）</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="inlineStr"/>
-      <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="inlineStr"/>
-      <c r="AV66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr"/>
-      <c r="AX66" t="inlineStr"/>
-      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL65"/>
+  <dimension ref="A1:AL75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,62 +619,62 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Y5-16</t>
+          <t>W5-13</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79393</v>
+        <v>79641</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8000</v>
+        <v>7200</v>
       </c>
       <c r="H2" t="n">
-        <v>2600</v>
+        <v>3900</v>
       </c>
       <c r="I2" t="n">
-        <v>2600</v>
+        <v>3900</v>
       </c>
       <c r="J2" t="n">
         <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>16000</v>
+        <v>7200</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>15020-JX5R- 770X300F-A   R</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O2" t="n">
-        <v>640</v>
+        <v>770</v>
       </c>
       <c r="P2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>46162</v>
@@ -686,18 +686,18 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>15020-AX5R- 770X300F-A   P</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X2" t="n">
-        <v>640</v>
+        <v>770</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>5400</v>
+        <v>3300</v>
       </c>
       <c r="AB2" t="n">
-        <v>10800</v>
+        <v>3300</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -749,11 +749,11 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y5-24</t>
+          <t>Y5-28</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79402</v>
+        <v>79408</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -769,13 +769,13 @@
         <v>9000</v>
       </c>
       <c r="H3" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="I3" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
         <v>18000</v>
@@ -801,13 +801,13 @@
         <v>4</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="AB3" t="n">
-        <v>8800</v>
+        <v>9200</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/25）</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -879,56 +879,56 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>Y5-34</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79641</v>
+        <v>79583</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>7200</v>
+        <v>6000</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O4" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="P4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>46170</v>
@@ -937,7 +937,7 @@
         <v>46170</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -946,18 +946,18 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X4" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -973,18 +973,18 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1009,56 +1009,56 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y5-34</t>
+          <t>V5-9</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79583</v>
+        <v>79688</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-A   C</t>
+          <t>30060-AG00-1030X100F-A   C</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>680</v>
+        <v>1030</v>
       </c>
       <c r="P5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>46170</v>
@@ -1071,23 +1071,23 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-A   C</t>
+          <t>30060-AG00-1030X200F-A   C</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>200</v>
       </c>
       <c r="X5" t="n">
-        <v>680</v>
+        <v>1030</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1139,65 +1139,65 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V5-7</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79604</v>
+        <v>79706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I6" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30020-BG00-1030X200F-ABK0C</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O6" t="n">
-        <v>1030</v>
+        <v>1180</v>
       </c>
       <c r="P6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1206,18 +1206,18 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X6" t="n">
-        <v>1030</v>
+        <v>1250</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1233,18 +1233,18 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1269,65 +1269,65 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y5-17</t>
+          <t>W5-14</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79395</v>
+        <v>79683</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>5000</v>
+        <v>91</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" t="n">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>25</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>10010-JP67-1550X 20F-A   P</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>640</v>
+        <v>1550</v>
       </c>
       <c r="P7" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1336,18 +1336,18 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>10010-AP67-1550X 91F-A   P</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="X7" t="n">
-        <v>640</v>
+        <v>1550</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1363,18 +1363,18 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -1399,65 +1399,65 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V5-9</t>
+          <t>W5-16</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79688</v>
+        <v>79686</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1600</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>1600</v>
+        <v>180</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1600</v>
+        <v>183</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X100F-A   C</t>
+          <t>10025-JR28-1550X 20F-A   G</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>1030</v>
+        <v>1550</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X200F-A   C</t>
+          <t>10025-SR28-1650X180F-A   B</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="X8" t="n">
-        <v>1030</v>
+        <v>1650</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>分割,スリット,EC</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1493,18 +1493,18 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1529,56 +1529,56 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C5-1</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79706</v>
+        <v>79687</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4000</v>
+        <v>271</v>
       </c>
       <c r="H9" t="n">
-        <v>4000</v>
+        <v>271</v>
       </c>
       <c r="I9" t="n">
-        <v>4000</v>
+        <v>271</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2000</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>15020-JW07-1550X 20F-A   V</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>20</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>20010-H600-1180X250F-AWH1C</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>250</v>
-      </c>
       <c r="O9" t="n">
-        <v>1180</v>
+        <v>1550</v>
       </c>
       <c r="P9" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>46171</v>
@@ -1591,23 +1591,23 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>20010-B600-1250X250F-AWH1C</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="X9" t="n">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>スリット,EC</t>
+          <t>分割,EC</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -1659,11 +1659,11 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>W5-14</t>
+          <t>W5-17</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79683</v>
+        <v>79687</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
         <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
         <v>20</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10010-JP67-1550X 20F-A   P</t>
+          <t>15020-JW07-1550X 20F-A   V</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1708,7 +1708,7 @@
         <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" s="1" t="n">
         <v>46171</v>
@@ -1721,16 +1721,16 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>10010-AP67-1550X 91F-A   P</t>
+          <t>15020-AW07-1550X271F-A   V</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="X10" t="n">
         <v>1550</v>
@@ -1789,56 +1789,56 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79686</v>
+        <v>79404</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>7000</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>180</v>
+        <v>7000</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>183</v>
+        <v>14000</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="O11" t="n">
-        <v>1550</v>
+        <v>680</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>46171</v>
@@ -1847,7 +1847,7 @@
         <v>46171</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1856,18 +1856,18 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="X11" t="n">
-        <v>1650</v>
+        <v>680</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1883,18 +1883,18 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr"/>
@@ -1919,53 +1919,53 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>Y5-35</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79687</v>
+        <v>79676</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>1600</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>271</v>
+        <v>1600</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>3200</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="O12" t="n">
-        <v>1550</v>
+        <v>935</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="Q12" t="n">
         <v>2</v>
@@ -1977,27 +1977,27 @@
         <v>46171</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="X12" t="n">
-        <v>1550</v>
+        <v>935</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2013,18 +2013,18 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr"/>
@@ -2049,11 +2049,11 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>Y5-38</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79404</v>
+        <v>79823</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2066,33 +2066,33 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="L13" t="n">
         <v>27</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>200</v>
       </c>
       <c r="O13" t="n">
-        <v>680</v>
+        <v>850</v>
       </c>
       <c r="P13" t="n">
         <v>200</v>
@@ -2107,23 +2107,23 @@
         <v>46171</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>200</v>
       </c>
       <c r="X13" t="n">
-        <v>680</v>
+        <v>850</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
@@ -2179,11 +2179,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79408</v>
+        <v>79913</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2196,39 +2196,39 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="H14" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J14" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>18000</v>
+        <v>1933</v>
       </c>
       <c r="L14" t="n">
         <v>27</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O14" t="n">
         <v>870</v>
       </c>
       <c r="P14" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>46171</v>
@@ -2237,27 +2237,27 @@
         <v>46171</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X14" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2284,7 +2284,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr"/>
@@ -2309,53 +2309,53 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y5-35</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79676</v>
+        <v>79913</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1600</v>
+        <v>1943</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>3200</v>
+        <v>1933</v>
       </c>
       <c r="L15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O15" t="n">
-        <v>935</v>
+        <v>870</v>
       </c>
       <c r="P15" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
@@ -2367,27 +2367,27 @@
         <v>46171</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X15" t="n">
-        <v>935</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2403,18 +2403,18 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
@@ -2439,56 +2439,56 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Y5-38</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79823</v>
+        <v>79398</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="L16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 850X200F-AGA1C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O16" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
       <c r="P16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>46171</v>
@@ -2497,27 +2497,27 @@
         <v>46171</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>50080-AY0B- 850X200F-AGA1C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X16" t="n">
-        <v>850</v>
+        <v>1110</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2533,18 +2533,18 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr"/>
@@ -2569,15 +2569,15 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>PN06-01</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79913</v>
+        <v>79935</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2598,36 +2598,36 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>1933</v>
+        <v>2000</v>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="P17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2663,18 +2663,18 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr"/>
@@ -2699,85 +2699,83 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>PN06-02</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>79398</v>
+        <v>80058</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6000</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>6000</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>12000</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
         <v>25</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P18" t="n">
-        <v>300</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X18" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2793,7 +2791,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2804,7 +2802,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
@@ -2829,65 +2827,65 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79913</v>
+        <v>79821</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1943</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>1933</v>
+        <v>2850</v>
       </c>
       <c r="L19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>870</v>
+        <v>316</v>
       </c>
       <c r="P19" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2896,7 +2894,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -2923,18 +2921,18 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
@@ -2959,15 +2957,15 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79687</v>
+        <v>79821</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2976,48 +2974,48 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>271</v>
+        <v>950</v>
       </c>
       <c r="H20" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>271</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>2850</v>
       </c>
       <c r="L20" t="n">
         <v>25</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O20" t="n">
-        <v>1550</v>
+        <v>316</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>46164</v>
+        <v>46174</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3026,18 +3024,18 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="X20" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3053,7 +3051,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3064,7 +3062,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr"/>
@@ -3089,15 +3087,15 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79935</v>
+        <v>79926</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3106,45 +3104,45 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2000</v>
+        <v>3995</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2000</v>
+        <v>4085</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K21" t="n">
-        <v>2000</v>
+        <v>3880</v>
       </c>
       <c r="L21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O21" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>46174</v>
@@ -3156,18 +3154,18 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3183,12 +3181,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>EC+SEC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -3219,62 +3217,62 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79821</v>
+        <v>79926</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3880</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3895</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>2850</v>
+        <v>3880</v>
       </c>
       <c r="L22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O22" t="n">
-        <v>316</v>
+        <v>870</v>
       </c>
       <c r="P22" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>46174</v>
@@ -3286,11 +3284,11 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -3313,12 +3311,12 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3349,65 +3347,65 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79821</v>
+        <v>79754</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>950</v>
+        <v>1155</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>1155</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>2850</v>
+        <v>2310</v>
       </c>
       <c r="L23" t="n">
         <v>25</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="O23" t="n">
-        <v>316</v>
+        <v>1080</v>
       </c>
       <c r="P23" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3416,18 +3414,18 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3443,7 +3441,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3454,7 +3452,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr"/>
@@ -3479,83 +3477,85 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79414</v>
+        <v>79754</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9000</v>
+        <v>2310</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>9000</v>
+        <v>2310</v>
       </c>
       <c r="J24" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>9000</v>
+        <v>2310</v>
       </c>
       <c r="L24" t="n">
         <v>20</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="O24" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="P24" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>46178</v>
+      </c>
       <c r="S24" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>300</v>
+        <v>105</v>
       </c>
       <c r="X24" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3582,7 +3582,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr"/>
@@ -3607,63 +3607,65 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79414</v>
+        <v>79996</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9000</v>
+        <v>3200</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>9000</v>
+        <v>3200</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>9000</v>
+        <v>6400</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O25" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="P25" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>46178</v>
+      </c>
       <c r="S25" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3672,18 +3674,18 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X25" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3699,18 +3701,18 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr"/>
@@ -3735,56 +3737,56 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>Y6-1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79926</v>
+        <v>79867</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3995</v>
+        <v>2400</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4085</v>
+        <v>2400</v>
       </c>
       <c r="J26" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>3880</v>
+        <v>4800</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O26" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="P26" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>46178</v>
@@ -3802,18 +3804,18 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3829,12 +3831,12 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -3865,65 +3867,63 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>Y5-39</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79926</v>
+        <v>79825</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3880</v>
+        <v>200</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3895</v>
+        <v>200</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>3880</v>
+        <v>200</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O27" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P27" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R27" s="1" t="n">
-        <v>46178</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3932,18 +3932,18 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3959,18 +3959,18 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr"/>
@@ -3995,56 +3995,56 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79754</v>
+        <v>79826</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1155</v>
+        <v>800</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1155</v>
+        <v>800</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>2310</v>
+        <v>800</v>
       </c>
       <c r="L28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O28" t="n">
-        <v>1080</v>
+        <v>740</v>
       </c>
       <c r="P28" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>46178</v>
@@ -4053,27 +4053,27 @@
         <v>46178</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>105</v>
+        <v>400</v>
       </c>
       <c r="X28" t="n">
-        <v>1080</v>
+        <v>750</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4089,18 +4089,18 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr"/>
@@ -4125,56 +4125,56 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>Y5-41</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79996</v>
+        <v>79827</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3200</v>
+        <v>200</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3200</v>
+        <v>200</v>
       </c>
       <c r="J29" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>6400</v>
+        <v>200</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O29" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>46178</v>
@@ -4183,27 +4183,27 @@
         <v>46178</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W29" t="n">
         <v>200</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4219,18 +4219,18 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr"/>
@@ -4255,11 +4255,11 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Y6-1</t>
+          <t>Y6-2</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4272,48 +4272,48 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>4800</v>
+        <v>5600</v>
       </c>
       <c r="L30" t="n">
         <v>25</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N30" t="n">
         <v>200</v>
       </c>
       <c r="O30" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="P30" t="n">
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="W30" t="n">
         <v>200</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -4385,20 +4385,20 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Y5-39</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>79825</v>
+        <v>80056</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4411,57 +4411,57 @@
         <v>200</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>200</v>
       </c>
-      <c r="L31" t="n">
-        <v>10</v>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>740</v>
+        <v>900</v>
       </c>
       <c r="P31" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>46181</v>
+      </c>
       <c r="S31" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X31" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>巻返し+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4513,62 +4513,62 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79826</v>
+        <v>80056</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O32" t="n">
-        <v>740</v>
+        <v>900</v>
       </c>
       <c r="P32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>46176</v>
@@ -4580,18 +4580,18 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="X32" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4643,65 +4643,65 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y5-41</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79827</v>
+        <v>79822</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N33" t="n">
         <v>200</v>
       </c>
       <c r="O33" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P33" t="n">
         <v>200</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -4710,18 +4710,18 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W33" t="n">
         <v>200</v>
       </c>
       <c r="X33" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4737,18 +4737,18 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr"/>
@@ -4773,85 +4773,85 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>79754</v>
+        <v>79994</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2310</v>
+        <v>500</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2310</v>
+        <v>500</v>
       </c>
       <c r="J34" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>2310</v>
+        <v>500</v>
       </c>
       <c r="L34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="O34" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="P34" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="X34" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4867,18 +4867,18 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr"/>
@@ -4903,56 +4903,56 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Y6-2</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>79868</v>
+        <v>79605</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>5600</v>
+        <v>1400</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N35" t="n">
         <v>200</v>
       </c>
       <c r="O35" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="P35" t="n">
         <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R35" s="1" t="n">
         <v>46181</v>
@@ -4961,27 +4961,27 @@
         <v>46181</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>200</v>
       </c>
       <c r="X35" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4997,18 +4997,18 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr"/>
@@ -5033,20 +5033,20 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>T6-3</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>79822</v>
+        <v>80061</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5062,54 +5062,56 @@
         <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>30050-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="N36" t="n">
         <v>200</v>
       </c>
       <c r="O36" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="P36" t="n">
         <v>200</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>46182</v>
+      </c>
       <c r="S36" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30050-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>200</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5125,18 +5127,18 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr"/>
@@ -5161,63 +5163,65 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>T6-4</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79994</v>
+        <v>80063</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X 50F-A   C</t>
+          <t>30060-JG00-1000X100F-A   Q</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O37" t="n">
         <v>1000</v>
       </c>
       <c r="P37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>46182</v>
+      </c>
       <c r="S37" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5226,18 +5230,18 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X 50F-A   C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5253,18 +5257,18 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr"/>
@@ -5289,65 +5293,65 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>79605</v>
+        <v>80064</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="L38" t="n">
         <v>20</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N38" t="n">
         <v>200</v>
       </c>
       <c r="O38" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="P38" t="n">
         <v>200</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5356,18 +5360,18 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>200</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5383,7 +5387,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -5394,7 +5398,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr"/>
@@ -5419,50 +5423,50 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>79989</v>
+        <v>80064</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N39" t="n">
         <v>200</v>
       </c>
       <c r="O39" t="n">
-        <v>740</v>
+        <v>1050</v>
       </c>
       <c r="P39" t="n">
         <v>200</v>
@@ -5470,32 +5474,34 @@
       <c r="Q39" t="n">
         <v>2</v>
       </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" s="1" t="n">
+        <v>46182</v>
+      </c>
       <c r="S39" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X39" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5511,18 +5517,18 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr"/>
@@ -5547,85 +5553,85 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Y6-6</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>79874</v>
+        <v>79989</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="L40" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N40" t="n">
         <v>200</v>
       </c>
       <c r="O40" t="n">
-        <v>680</v>
+        <v>740</v>
       </c>
       <c r="P40" t="n">
         <v>200</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X40" t="n">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5641,12 +5647,12 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5677,85 +5683,85 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Y6-7</t>
+          <t>Y6-11</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>79875</v>
+        <v>80060</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>7600</v>
+        <v>2000</v>
       </c>
       <c r="L41" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N41" t="n">
         <v>200</v>
       </c>
       <c r="O41" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="P41" t="n">
         <v>200</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W41" t="n">
         <v>200</v>
       </c>
       <c r="X41" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5771,18 +5777,18 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr"/>
@@ -5807,11 +5813,11 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Y6-8</t>
+          <t>Y6-6</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>79876</v>
+        <v>79874</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5824,33 +5830,33 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="L42" t="n">
         <v>27</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N42" t="n">
         <v>200</v>
       </c>
       <c r="O42" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P42" t="n">
         <v>200</v>
@@ -5865,7 +5871,7 @@
         <v>46184</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5874,14 +5880,14 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W42" t="n">
         <v>200</v>
       </c>
       <c r="X42" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -5912,7 +5918,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr"/>
@@ -5937,43 +5943,43 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-7</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>79871</v>
+        <v>79875</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="J43" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>6400</v>
+        <v>7600</v>
       </c>
       <c r="L43" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -5999,12 +6005,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -6015,7 +6021,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -6031,12 +6037,12 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -6067,11 +6073,11 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-8</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>79871</v>
+        <v>79876</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -6084,19 +6090,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3200</v>
+        <v>800</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3200</v>
+        <v>800</v>
       </c>
       <c r="J44" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>6400</v>
+        <v>1600</v>
       </c>
       <c r="L44" t="n">
         <v>27</v>
@@ -6129,12 +6135,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -6145,7 +6151,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -6197,11 +6203,11 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>79872</v>
+        <v>79871</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -6214,26 +6220,26 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>3200</v>
+        <v>6400</v>
       </c>
       <c r="L45" t="n">
         <v>20</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6255,16 +6261,16 @@
         <v>46184</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -6302,7 +6308,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr"/>
@@ -6327,11 +6333,11 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79872</v>
+        <v>79871</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6344,26 +6350,26 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>3200</v>
+        <v>6400</v>
       </c>
       <c r="L46" t="n">
         <v>27</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -6385,16 +6391,16 @@
         <v>46184</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -6432,7 +6438,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr"/>
@@ -6457,11 +6463,11 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79873</v>
+        <v>79872</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -6474,33 +6480,33 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="L47" t="n">
         <v>20</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N47" t="n">
         <v>200</v>
       </c>
       <c r="O47" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P47" t="n">
         <v>200</v>
@@ -6515,23 +6521,23 @@
         <v>46184</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W47" t="n">
         <v>200</v>
       </c>
       <c r="X47" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -6562,7 +6568,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr"/>
@@ -6587,11 +6593,11 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>79873</v>
+        <v>79872</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6604,33 +6610,33 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="L48" t="n">
         <v>27</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>200</v>
       </c>
       <c r="O48" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P48" t="n">
         <v>200</v>
@@ -6645,23 +6651,23 @@
         <v>46184</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>200</v>
       </c>
       <c r="X48" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -6692,7 +6698,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr"/>
@@ -6717,85 +6723,85 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>79927</v>
+        <v>79873</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>29400</v>
+        <v>600</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>29400</v>
+        <v>600</v>
       </c>
       <c r="J49" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>29400</v>
+        <v>1200</v>
       </c>
       <c r="L49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O49" t="n">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="P49" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X49" t="n">
-        <v>1050</v>
+        <v>680</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -6811,18 +6817,18 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr"/>
@@ -6847,63 +6853,65 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79987</v>
+        <v>79873</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>12000</v>
+        <v>1200</v>
       </c>
       <c r="L50" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O50" t="n">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="P50" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
-      </c>
-      <c r="R50" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <v>46184</v>
+      </c>
       <c r="S50" s="1" t="n">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -6912,18 +6920,18 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X50" t="n">
-        <v>1110</v>
+        <v>680</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6939,18 +6947,18 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr"/>
@@ -6975,11 +6983,11 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79985</v>
+        <v>79927</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -6992,66 +7000,68 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5400</v>
+        <v>29400</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>5400</v>
+        <v>29400</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="K51" t="n">
-        <v>10800</v>
+        <v>29400</v>
       </c>
       <c r="L51" t="n">
         <v>25</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>300</v>
       </c>
       <c r="O51" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P51" t="n">
         <v>300</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="R51" s="1" t="n">
+        <v>46185</v>
+      </c>
       <c r="S51" s="1" t="n">
-        <v>46189</v>
+        <v>46185</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>300</v>
       </c>
       <c r="X51" t="n">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -7078,7 +7088,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr"/>
@@ -7103,15 +7113,15 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>V6-2</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79995</v>
+        <v>79987</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7120,48 +7130,48 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L52" t="n">
         <v>25</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O52" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P52" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7170,18 +7180,18 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -7197,7 +7207,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -7208,7 +7218,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>（2026/6/11）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr"/>
@@ -7233,85 +7243,85 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79828</v>
+        <v>80065</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O53" t="n">
-        <v>740</v>
+        <v>1440</v>
       </c>
       <c r="P53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q53" t="n">
         <v>2</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X53" t="n">
-        <v>750</v>
+        <v>1440</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7327,18 +7337,18 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
@@ -7357,73 +7367,71 @@
       <c r="AL53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79996</v>
+        <v>80065</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="J54" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="L54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O54" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="P54" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -7432,18 +7440,18 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -7459,18 +7467,18 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr"/>
@@ -7489,12 +7497,10 @@
       <c r="AL54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>Y6-10</t>
@@ -7505,7 +7511,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7514,21 +7520,23 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>10800</v>
+        <v>5400</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>10800</v>
+        <v>5400</v>
       </c>
       <c r="J55" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
         <v>10800</v>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>25</v>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>30030-AP66- 550X300F-ABK0M</t>
@@ -7546,7 +7554,9 @@
       <c r="Q55" t="n">
         <v>3</v>
       </c>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" s="1" t="n">
+        <v>46189</v>
+      </c>
       <c r="S55" s="1" t="n">
         <v>46189</v>
       </c>
@@ -7587,12 +7597,12 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -7617,23 +7627,21 @@
       <c r="AL55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>V6-2</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79987</v>
+        <v>79995</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7642,44 +7650,48 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="J56" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="L56" t="n">
+        <v>25</v>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P56" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
-      </c>
-      <c r="R56" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="R56" s="1" t="n">
+        <v>46190</v>
+      </c>
       <c r="S56" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -7688,18 +7700,18 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X56" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7715,18 +7727,18 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/11）</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr"/>
@@ -7745,23 +7757,21 @@
       <c r="AL56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>79398</v>
+        <v>80067</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7770,46 +7780,48 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="J57" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>6000</v>
+      </c>
+      <c r="L57" t="n">
+        <v>25</v>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>300</v>
       </c>
       <c r="O57" t="n">
-        <v>550</v>
+        <v>1300</v>
       </c>
       <c r="P57" t="n">
         <v>300</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -7818,18 +7830,18 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W57" t="n">
         <v>300</v>
       </c>
       <c r="X57" t="n">
-        <v>1110</v>
+        <v>1440</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -7845,18 +7857,18 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr"/>
@@ -7875,91 +7887,91 @@
       <c r="AL57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>79913</v>
+        <v>80067</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="J58" t="n">
         <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>1933</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
+        <v>6000</v>
+      </c>
+      <c r="L58" t="n">
+        <v>20</v>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="O58" t="n">
-        <v>870</v>
+        <v>1300</v>
       </c>
       <c r="P58" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="Q58" t="n">
         <v>2</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -7975,18 +7987,18 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr"/>
@@ -8005,91 +8017,91 @@
       <c r="AL58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79821</v>
+        <v>80067</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="J59" t="n">
+        <v>20</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L59" t="n">
         <v>10</v>
       </c>
-      <c r="K59" t="n">
-        <v>2850</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O59" t="n">
-        <v>316</v>
+        <v>1300</v>
       </c>
       <c r="P59" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46176</v>
+        <v>46191</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46176</v>
+        <v>46191</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8105,18 +8117,18 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr"/>
@@ -8135,91 +8147,91 @@
       <c r="AL59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>79926</v>
+        <v>80066</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>4085</v>
+        <v>9000</v>
       </c>
       <c r="J60" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>3880</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>9000</v>
+      </c>
+      <c r="L60" t="n">
+        <v>20</v>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="O60" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="P60" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="Q60" t="n">
         <v>2</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46178</v>
+        <v>46195</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46178</v>
+        <v>46195</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8235,18 +8247,18 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr"/>
@@ -8265,91 +8277,91 @@
       <c r="AL60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>79935</v>
+        <v>80066</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="J61" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>9000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10</v>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O61" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="P61" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q61" t="n">
         <v>2</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46176</v>
+        <v>46195</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46176</v>
+        <v>46195</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W61" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -8365,18 +8377,18 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>梱包+SEC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr"/>
@@ -8395,23 +8407,21 @@
       <c r="AL61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>Y5-42</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>79989</v>
+        <v>79828</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8454,12 +8464,14 @@
       <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="S62" s="1" t="n">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8495,7 +8507,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr"/>
@@ -8533,61 +8545,65 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>79994</v>
+        <v>79996</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>500</v>
+        <v>6400</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>500</v>
+        <v>6400</v>
       </c>
       <c r="J63" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K63" t="n">
-        <v>500</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>6400</v>
+      </c>
+      <c r="L63" t="n">
+        <v>25</v>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X 50F-A   C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
         <v>1000</v>
       </c>
       <c r="P63" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R63" s="1" t="n">
+        <v>46178</v>
+      </c>
       <c r="S63" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8596,18 +8612,18 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X 50F-A   C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8623,18 +8639,18 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>巻返し+エンボス　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr"/>
@@ -8661,65 +8677,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>79826</v>
+        <v>79398</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>800</v>
+        <v>12000</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>800</v>
+        <v>12000</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K64" t="n">
-        <v>800</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O64" t="n">
-        <v>740</v>
+        <v>550</v>
       </c>
       <c r="P64" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8728,18 +8742,18 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W64" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X64" t="n">
-        <v>750</v>
+        <v>1110</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8755,18 +8769,18 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr"/>
@@ -8793,65 +8807,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>79828</v>
+        <v>79913</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L65" t="n">
-        <v>10</v>
-      </c>
+        <v>1933</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O65" t="n">
-        <v>740</v>
+        <v>870</v>
       </c>
       <c r="P65" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8860,18 +8872,18 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W65" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="X65" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8887,18 +8899,18 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr"/>
@@ -8915,6 +8927,1312 @@
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>JR260601</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>79821</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J66" t="n">
+        <v>10</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2850</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>40040-R10W- 316X 95</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>100</v>
+      </c>
+      <c r="O66" t="n">
+        <v>316</v>
+      </c>
+      <c r="P66" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S66" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T66" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>FEL4004AY-10WD-1000X100</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>100</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>JR260602</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>79926</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4085</v>
+      </c>
+      <c r="J67" t="n">
+        <v>43</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3880</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>30020-A05W- 870X 97   LG</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>97</v>
+      </c>
+      <c r="O67" t="n">
+        <v>870</v>
+      </c>
+      <c r="P67" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T67" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+        </is>
+      </c>
+      <c r="W67" t="n">
+        <v>95</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T6-1</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>79994</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>巻返し</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>500</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>500</v>
+      </c>
+      <c r="L68" t="n">
+        <v>25</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>30100-VG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>50</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P68" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R68" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S68" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T68" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>30100-NG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="W68" t="n">
+        <v>100</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>エンボス,巻返し</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>巻返し+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>（25）</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>（2026/6/3）</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Y6-9</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>79987</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J69" t="n">
+        <v>40</v>
+      </c>
+      <c r="K69" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>300</v>
+      </c>
+      <c r="O69" t="n">
+        <v>550</v>
+      </c>
+      <c r="P69" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S69" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T69" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="W69" t="n">
+        <v>300</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1110</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>（2026/6/9）</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Y6-10</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>79985</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>欠点表示</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>10800</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J70" t="n">
+        <v>36</v>
+      </c>
+      <c r="K70" t="n">
+        <v>10800</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>300</v>
+      </c>
+      <c r="O70" t="n">
+        <v>550</v>
+      </c>
+      <c r="P70" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3</v>
+      </c>
+      <c r="R70" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="S70" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T70" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>30030-AP66-1110X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>300</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1110</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>欠点表示,スリット</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>欠点表示+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>（2026/6/10）</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PN06-01</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>79935</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J71" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>FEL3002BY05WDLG-EC</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>100</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P71" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R71" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S71" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T71" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
+        </is>
+      </c>
+      <c r="W71" t="n">
+        <v>100</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>梱包+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PN06-02</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>80058</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>100</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>100</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P72" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S72" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T72" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
+        </is>
+      </c>
+      <c r="W72" t="n">
+        <v>100</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>梱包+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Y5-40</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>79826</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>800</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>800</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>800</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>200</v>
+      </c>
+      <c r="O73" t="n">
+        <v>740</v>
+      </c>
+      <c r="P73" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R73" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S73" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T73" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>400</v>
+      </c>
+      <c r="X73" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>（2026/6/3）</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>T6-2</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>79989</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L74" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>200</v>
+      </c>
+      <c r="O74" t="n">
+        <v>740</v>
+      </c>
+      <c r="P74" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S74" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T74" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W74" t="n">
+        <v>400</v>
+      </c>
+      <c r="X74" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>（2026/6/5）</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Y5-42</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>79828</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L75" t="n">
+        <v>10</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>200</v>
+      </c>
+      <c r="O75" t="n">
+        <v>740</v>
+      </c>
+      <c r="P75" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2</v>
+      </c>
+      <c r="R75" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S75" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T75" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W75" t="n">
+        <v>400</v>
+      </c>
+      <c r="X75" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>（2026/6/3）</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -2747,7 +2747,9 @@
       <c r="P18" t="n">
         <v>100</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>20</v>
+      </c>
       <c r="R18" s="1" t="n">
         <v>46176</v>
       </c>
@@ -4393,7 +4395,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4416,7 +4418,9 @@
       <c r="K31" t="n">
         <v>200</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>50090-BY0B- 900X100F-ABKOC</t>
@@ -4477,12 +4481,12 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>巻返し+スライス機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4513,11 +4517,11 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>80056</v>
+        <v>79822</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4530,39 +4534,39 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O32" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="P32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R32" s="1" t="n">
         <v>46181</v>
@@ -4571,27 +4575,27 @@
         <v>46181</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X32" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4618,7 +4622,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr"/>
@@ -4643,56 +4647,56 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79822</v>
+        <v>79994</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>500</v>
+      </c>
+      <c r="L33" t="n">
         <v>10</v>
       </c>
-      <c r="K33" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L33" t="n">
-        <v>25</v>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O33" t="n">
         <v>1000</v>
       </c>
       <c r="P33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R33" s="1" t="n">
         <v>46181</v>
@@ -4701,27 +4705,27 @@
         <v>46181</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4737,18 +4741,18 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr"/>
@@ -4781,12 +4785,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4805,7 +4809,7 @@
         <v>500</v>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4867,12 +4871,12 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -8677,63 +8681,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>79398</v>
+        <v>80056</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>12000</v>
+        <v>200</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>12000</v>
+        <v>200</v>
       </c>
       <c r="J64" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>12000</v>
+        <v>200</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>550</v>
+        <v>900</v>
       </c>
       <c r="P64" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8742,18 +8746,18 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W64" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X64" t="n">
-        <v>1110</v>
+        <v>900</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8769,7 +8773,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>巻返し+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -8780,7 +8784,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr"/>
@@ -8807,15 +8811,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>79913</v>
+        <v>79398</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8824,37 +8828,37 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="J65" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>1933</v>
+        <v>12000</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="O65" t="n">
-        <v>870</v>
+        <v>550</v>
       </c>
       <c r="P65" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R65" s="1" t="n">
         <v>46171</v>
@@ -8863,27 +8867,27 @@
         <v>46171</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W65" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X65" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8899,7 +8903,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -8910,7 +8914,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr"/>
@@ -8937,11 +8941,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>79821</v>
+        <v>79913</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -8954,46 +8958,46 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>2850</v>
+        <v>1933</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O66" t="n">
-        <v>316</v>
+        <v>870</v>
       </c>
       <c r="P66" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -9002,7 +9006,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -9040,7 +9044,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr"/>
@@ -9067,11 +9071,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>79926</v>
+        <v>79821</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -9084,43 +9088,43 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>4085</v>
+        <v>1000</v>
       </c>
       <c r="J67" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="K67" t="n">
-        <v>3880</v>
+        <v>2850</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>870</v>
+        <v>316</v>
       </c>
       <c r="P67" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="T67" s="1" t="n">
         <v>46174</v>
@@ -9132,11 +9136,11 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -9197,15 +9201,15 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>79994</v>
+        <v>79926</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9214,68 +9218,66 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>500</v>
+        <v>4085</v>
       </c>
       <c r="J68" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="K68" t="n">
-        <v>500</v>
-      </c>
-      <c r="L68" t="n">
-        <v>25</v>
-      </c>
+        <v>3880</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="O68" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P68" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="T68" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W68" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -9291,18 +9293,18 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr"/>
@@ -9765,7 +9767,9 @@
       <c r="P72" t="n">
         <v>100</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>20</v>
+      </c>
       <c r="R72" s="1" t="n">
         <v>46176</v>
       </c>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL75"/>
+  <dimension ref="A1:AL80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,7 +1029,7 @@
         <v>1600</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I5" t="n">
         <v>1600</v>
@@ -2459,7 +2459,7 @@
         <v>6000</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I16" t="n">
         <v>6000</v>
@@ -3089,56 +3089,56 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79926</v>
+        <v>80080</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3995</v>
+        <v>1750</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4085</v>
+        <v>1750</v>
       </c>
       <c r="J21" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>3880</v>
+        <v>600</v>
       </c>
       <c r="L21" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="O21" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="P21" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>46178</v>
@@ -3151,23 +3151,23 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -3227,31 +3227,31 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3880</v>
+        <v>3995</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3895</v>
+        <v>4085</v>
       </c>
       <c r="J22" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
         <v>3880</v>
       </c>
       <c r="L22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3349,56 +3349,56 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79754</v>
+        <v>79926</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1155</v>
+        <v>3880</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1155</v>
+        <v>3895</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>2310</v>
+        <v>3880</v>
       </c>
       <c r="L23" t="n">
         <v>25</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="O23" t="n">
-        <v>1080</v>
+        <v>870</v>
       </c>
       <c r="P23" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>46178</v>
@@ -3407,7 +3407,7 @@
         <v>46178</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3416,18 +3416,18 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="X23" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr"/>
@@ -3487,31 +3487,31 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2310</v>
+        <v>1155</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2310</v>
+        <v>1155</v>
       </c>
       <c r="J24" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>2310</v>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
@@ -3609,56 +3609,56 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79996</v>
+        <v>79754</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3200</v>
+        <v>2310</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3200</v>
+        <v>2310</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>6400</v>
+        <v>2310</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="O25" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>46178</v>
@@ -3671,23 +3671,23 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -3739,11 +3739,11 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Y6-1</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79867</v>
+        <v>79996</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3756,39 +3756,39 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>4800</v>
+        <v>6400</v>
       </c>
       <c r="L26" t="n">
         <v>25</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
         <v>1000</v>
       </c>
       <c r="P26" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>46178</v>
@@ -3797,16 +3797,16 @@
         <v>46178</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3844,7 +3844,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr"/>
@@ -3869,63 +3869,65 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Y5-39</t>
+          <t>Y6-1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79825</v>
+        <v>79867</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>200</v>
+        <v>4800</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N27" t="n">
         <v>200</v>
       </c>
       <c r="O27" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P27" t="n">
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>46178</v>
+      </c>
       <c r="S27" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3934,18 +3936,18 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="W27" t="n">
         <v>200</v>
       </c>
       <c r="X27" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3961,18 +3963,18 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr"/>
@@ -3997,11 +3999,11 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>Y5-39</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79826</v>
+        <v>79825</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4014,19 +4016,19 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -4055,27 +4057,27 @@
         <v>46178</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X28" t="n">
         <v>750</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4102,7 +4104,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr"/>
@@ -4127,11 +4129,11 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Y5-41</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79827</v>
+        <v>79826</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4144,26 +4146,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="L29" t="n">
         <v>10</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4176,7 +4178,7 @@
         <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>46178</v>
@@ -4185,27 +4187,27 @@
         <v>46178</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X29" t="n">
         <v>750</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4232,7 +4234,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr"/>
@@ -4257,65 +4259,65 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Y6-2</t>
+          <t>Y5-41</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79868</v>
+        <v>79827</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N30" t="n">
         <v>200</v>
       </c>
       <c r="O30" t="n">
-        <v>640</v>
+        <v>740</v>
       </c>
       <c r="P30" t="n">
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4324,18 +4326,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W30" t="n">
         <v>200</v>
       </c>
       <c r="X30" t="n">
-        <v>640</v>
+        <v>750</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4351,18 +4353,18 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -4387,65 +4389,65 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80056</v>
+        <v>80080</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>200</v>
+        <v>1750</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>200</v>
+        <v>1750</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="L31" t="n">
         <v>25</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O31" t="n">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4454,18 +4456,18 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X31" t="n">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4481,7 +4483,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -4492,7 +4494,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr"/>
@@ -4517,20 +4519,20 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>T6-3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79822</v>
+        <v>80061</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4546,27 +4548,27 @@
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>30050-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="N32" t="n">
         <v>200</v>
       </c>
       <c r="O32" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="P32" t="n">
         <v>200</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R32" s="1" t="n">
         <v>46181</v>
@@ -4575,27 +4577,27 @@
         <v>46181</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30050-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="W32" t="n">
         <v>200</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4611,18 +4613,18 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr"/>
@@ -4647,47 +4649,47 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>T6-4</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79994</v>
+        <v>80063</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>30060-JG00-1000X100F-A   Q</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O33" t="n">
         <v>1000</v>
@@ -4696,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R33" s="1" t="n">
         <v>46181</v>
@@ -4705,7 +4707,7 @@
         <v>46181</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -4714,7 +4716,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -4725,7 +4727,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4741,18 +4743,18 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr"/>
@@ -4777,56 +4779,56 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>79994</v>
+        <v>80064</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O34" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R34" s="1" t="n">
         <v>46181</v>
@@ -4835,7 +4837,7 @@
         <v>46181</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4844,18 +4846,18 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4871,18 +4873,18 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr"/>
@@ -4907,56 +4909,56 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>79605</v>
+        <v>80064</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="L35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N35" t="n">
         <v>200</v>
       </c>
       <c r="O35" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="P35" t="n">
         <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" s="1" t="n">
         <v>46181</v>
@@ -4965,7 +4967,7 @@
         <v>46181</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4974,18 +4976,18 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>200</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -5001,18 +5003,18 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr"/>
@@ -5037,85 +5039,85 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T6-3</t>
+          <t>Y6-2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>80061</v>
+        <v>79868</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>2000</v>
+        <v>5600</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30050-JG00-1030X200F-ABK0Q</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N36" t="n">
         <v>200</v>
       </c>
       <c r="O36" t="n">
-        <v>1030</v>
+        <v>640</v>
       </c>
       <c r="P36" t="n">
         <v>200</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>30050-AG00-1030X200F-ABK0C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>200</v>
       </c>
       <c r="X36" t="n">
-        <v>1030</v>
+        <v>640</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5131,18 +5133,18 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr"/>
@@ -5167,20 +5169,20 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T6-4</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>80063</v>
+        <v>80056</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5199,33 +5201,33 @@
         <v>200</v>
       </c>
       <c r="L37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30060-JG00-1000X100F-A   Q</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N37" t="n">
         <v>100</v>
       </c>
       <c r="O37" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P37" t="n">
         <v>100</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5234,18 +5236,18 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>100</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5261,18 +5263,18 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr"/>
@@ -5297,85 +5299,85 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>80064</v>
+        <v>79822</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N38" t="n">
         <v>200</v>
       </c>
       <c r="O38" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="P38" t="n">
         <v>200</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>200</v>
       </c>
       <c r="X38" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5391,18 +5393,18 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr"/>
@@ -5427,65 +5429,65 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>80064</v>
+        <v>79994</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O39" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="P39" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -5494,18 +5496,18 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X39" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5521,18 +5523,18 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr"/>
@@ -5557,85 +5559,85 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>79989</v>
+        <v>79994</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="L40" t="n">
+        <v>25</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>30100-VG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>50</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P40" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q40" t="n">
         <v>10</v>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>200</v>
-      </c>
-      <c r="O40" t="n">
-        <v>740</v>
-      </c>
-      <c r="P40" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
       <c r="R40" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="X40" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5651,18 +5653,18 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr"/>
@@ -5687,65 +5689,65 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Y6-11</t>
+          <t>T6-6</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80060</v>
+        <v>80094</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N41" t="n">
         <v>200</v>
       </c>
       <c r="O41" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P41" t="n">
         <v>200</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>46177</v>
+        <v>46143</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -5754,18 +5756,18 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W41" t="n">
         <v>200</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5781,18 +5783,18 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/5/1）</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr"/>
@@ -5817,65 +5819,65 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Y6-6</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>79874</v>
+        <v>79605</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="L42" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N42" t="n">
         <v>200</v>
       </c>
       <c r="O42" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="P42" t="n">
         <v>200</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46184</v>
+        <v>46181</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>46184</v>
+        <v>46181</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5884,18 +5886,18 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="W42" t="n">
         <v>200</v>
       </c>
       <c r="X42" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5911,18 +5913,18 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr"/>
@@ -5947,65 +5949,65 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Y6-7</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>79875</v>
+        <v>80081</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3800</v>
+        <v>600</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3800</v>
+        <v>600</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>7600</v>
+        <v>600</v>
       </c>
       <c r="L43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>20020-AP17-1410X300F-A   V</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O43" t="n">
-        <v>870</v>
+        <v>1410</v>
       </c>
       <c r="P43" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6014,18 +6016,18 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>20020-AP17-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X43" t="n">
-        <v>870</v>
+        <v>1440</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -6041,18 +6043,18 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr"/>
@@ -6077,65 +6079,65 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y6-8</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>79876</v>
+        <v>79989</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="L44" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N44" t="n">
         <v>200</v>
       </c>
       <c r="O44" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P44" t="n">
         <v>200</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6144,18 +6146,18 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X44" t="n">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -6171,18 +6173,18 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr"/>
@@ -6207,65 +6209,65 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-11</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>79871</v>
+        <v>80060</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>6400</v>
+        <v>2000</v>
       </c>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N45" t="n">
         <v>200</v>
       </c>
       <c r="O45" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="P45" t="n">
         <v>200</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6274,18 +6276,18 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W45" t="n">
         <v>200</v>
       </c>
       <c r="X45" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -6301,18 +6303,18 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr"/>
@@ -6337,11 +6339,11 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-6</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79871</v>
+        <v>79874</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6354,33 +6356,33 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3200</v>
+        <v>200</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3200</v>
+        <v>200</v>
       </c>
       <c r="J46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>6400</v>
+        <v>400</v>
       </c>
       <c r="L46" t="n">
         <v>27</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N46" t="n">
         <v>200</v>
       </c>
       <c r="O46" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P46" t="n">
         <v>200</v>
@@ -6395,27 +6397,27 @@
         <v>46184</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W46" t="n">
         <v>200</v>
       </c>
       <c r="X46" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6442,7 +6444,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr"/>
@@ -6467,39 +6469,39 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-7</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79872</v>
+        <v>79875</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1600</v>
+        <v>3800</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1600</v>
+        <v>3800</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>3200</v>
+        <v>7600</v>
       </c>
       <c r="L47" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -6525,7 +6527,7 @@
         <v>46184</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -6534,7 +6536,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -6545,7 +6547,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6561,18 +6563,18 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr"/>
@@ -6597,11 +6599,11 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-8</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>79872</v>
+        <v>79876</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6614,26 +6616,26 @@
         </is>
       </c>
       <c r="G48" t="n">
+        <v>800</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>800</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
         <v>1600</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1600</v>
-      </c>
-      <c r="J48" t="n">
-        <v>8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3200</v>
       </c>
       <c r="L48" t="n">
         <v>27</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -6655,7 +6657,7 @@
         <v>46184</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -6664,7 +6666,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -6675,7 +6677,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6702,7 +6704,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr"/>
@@ -6727,11 +6729,11 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>79873</v>
+        <v>79871</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6744,33 +6746,33 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>1200</v>
+        <v>6400</v>
       </c>
       <c r="L49" t="n">
         <v>20</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>200</v>
       </c>
       <c r="O49" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P49" t="n">
         <v>200</v>
@@ -6789,19 +6791,19 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W49" t="n">
         <v>200</v>
       </c>
       <c r="X49" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -6857,11 +6859,11 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79873</v>
+        <v>79871</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6874,33 +6876,33 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K50" t="n">
-        <v>1200</v>
+        <v>6400</v>
       </c>
       <c r="L50" t="n">
         <v>27</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N50" t="n">
         <v>200</v>
       </c>
       <c r="O50" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P50" t="n">
         <v>200</v>
@@ -6919,19 +6921,19 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W50" t="n">
         <v>200</v>
       </c>
       <c r="X50" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -6987,85 +6989,85 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79927</v>
+        <v>79872</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>29400</v>
+        <v>1600</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>29400</v>
+        <v>1600</v>
       </c>
       <c r="J51" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>29400</v>
+        <v>3200</v>
       </c>
       <c r="L51" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O51" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P51" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X51" t="n">
-        <v>1050</v>
+        <v>870</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -7081,18 +7083,18 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr"/>
@@ -7117,85 +7119,85 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79987</v>
+        <v>79872</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>12000</v>
+        <v>3200</v>
       </c>
       <c r="L52" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O52" t="n">
-        <v>550</v>
+        <v>870</v>
       </c>
       <c r="P52" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X52" t="n">
-        <v>1110</v>
+        <v>870</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -7211,18 +7213,18 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr"/>
@@ -7247,65 +7249,65 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>W6-3</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>80065</v>
+        <v>79873</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="L53" t="n">
         <v>20</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O53" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="P53" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7314,18 +7316,18 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X53" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7341,7 +7343,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -7352,7 +7354,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
@@ -7377,65 +7379,65 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>W6-3</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>80065</v>
+        <v>79873</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="L54" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O54" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="P54" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -7444,18 +7446,18 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X54" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -7471,18 +7473,18 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr"/>
@@ -7507,11 +7509,11 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79985</v>
+        <v>79927</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7524,68 +7526,68 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5400</v>
+        <v>29400</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>5400</v>
+        <v>29400</v>
       </c>
       <c r="J55" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="K55" t="n">
-        <v>10800</v>
+        <v>29400</v>
       </c>
       <c r="L55" t="n">
         <v>25</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="N55" t="n">
         <v>300</v>
       </c>
       <c r="O55" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P55" t="n">
         <v>300</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46189</v>
+        <v>46185</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>46189</v>
+        <v>46185</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="W55" t="n">
         <v>300</v>
       </c>
       <c r="X55" t="n">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7612,7 +7614,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr"/>
@@ -7637,15 +7639,15 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>V6-2</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79995</v>
+        <v>79987</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7654,48 +7656,48 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L56" t="n">
         <v>25</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O56" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P56" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -7704,18 +7706,18 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7731,7 +7733,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -7742,7 +7744,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>（2026/6/11）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr"/>
@@ -7767,20 +7769,20 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>80067</v>
+        <v>80065</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7799,18 +7801,18 @@
         <v>6000</v>
       </c>
       <c r="L57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>300</v>
       </c>
       <c r="O57" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="P57" t="n">
         <v>300</v>
@@ -7819,10 +7821,10 @@
         <v>2</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="T57" s="1" t="n">
         <v>46182</v>
@@ -7845,7 +7847,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -7861,12 +7863,12 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7897,20 +7899,20 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>80067</v>
+        <v>80065</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7929,18 +7931,18 @@
         <v>6000</v>
       </c>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>300</v>
       </c>
       <c r="O58" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="P58" t="n">
         <v>300</v>
@@ -7949,10 +7951,10 @@
         <v>2</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="T58" s="1" t="n">
         <v>46182</v>
@@ -7975,7 +7977,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -7991,12 +7993,12 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -8027,65 +8029,65 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>80067</v>
+        <v>79985</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="J59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="L59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N59" t="n">
         <v>300</v>
       </c>
       <c r="O59" t="n">
-        <v>1300</v>
+        <v>550</v>
       </c>
       <c r="P59" t="n">
         <v>300</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8094,18 +8096,18 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W59" t="n">
         <v>300</v>
       </c>
       <c r="X59" t="n">
-        <v>1440</v>
+        <v>1110</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8121,18 +8123,18 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr"/>
@@ -8157,65 +8159,65 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>W6-5</t>
+          <t>V6-2</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>80066</v>
+        <v>79995</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="J60" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="L60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="P60" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8224,18 +8226,18 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X60" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8251,18 +8253,18 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/11）</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr"/>
@@ -8287,50 +8289,50 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>W6-5</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>80066</v>
+        <v>80067</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J61" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>300</v>
       </c>
       <c r="O61" t="n">
-        <v>1440</v>
+        <v>1300</v>
       </c>
       <c r="P61" t="n">
         <v>300</v>
@@ -8339,13 +8341,13 @@
         <v>2</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8365,7 +8367,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -8381,18 +8383,18 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr"/>
@@ -8417,85 +8419,85 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>79828</v>
+        <v>80067</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="L62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O62" t="n">
-        <v>740</v>
+        <v>1300</v>
       </c>
       <c r="P62" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W62" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X62" t="n">
-        <v>750</v>
+        <v>1440</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -8511,18 +8513,18 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr"/>
@@ -8541,73 +8543,71 @@
       <c r="AL62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>79996</v>
+        <v>80067</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="J63" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="L63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O63" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="P63" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46178</v>
+        <v>46191</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46178</v>
+        <v>46191</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8616,18 +8616,18 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8643,18 +8643,18 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr"/>
@@ -8673,71 +8673,71 @@
       <c r="AL63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>80056</v>
+        <v>80066</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>200</v>
+        <v>9000</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>200</v>
+        <v>9000</v>
       </c>
       <c r="J64" t="n">
+        <v>30</v>
+      </c>
+      <c r="K64" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L64" t="n">
+        <v>20</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>300</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P64" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q64" t="n">
         <v>2</v>
       </c>
-      <c r="K64" t="n">
-        <v>200</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>100</v>
-      </c>
-      <c r="O64" t="n">
-        <v>900</v>
-      </c>
-      <c r="P64" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>9</v>
-      </c>
       <c r="R64" s="1" t="n">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8746,18 +8746,18 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W64" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X64" t="n">
-        <v>900</v>
+        <v>1440</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8773,18 +8773,18 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>巻返し+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr"/>
@@ -8803,71 +8803,71 @@
       <c r="AL64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>79398</v>
+        <v>80066</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="J65" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K65" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+        <v>9000</v>
+      </c>
+      <c r="L65" t="n">
+        <v>10</v>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N65" t="n">
         <v>300</v>
       </c>
       <c r="O65" t="n">
-        <v>550</v>
+        <v>1440</v>
       </c>
       <c r="P65" t="n">
         <v>300</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>46168</v>
+        <v>46183</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8876,18 +8876,18 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W65" t="n">
         <v>300</v>
       </c>
       <c r="X65" t="n">
-        <v>1110</v>
+        <v>1440</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8903,18 +8903,18 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr"/>
@@ -8933,71 +8933,71 @@
       <c r="AL65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>Y5-42</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>79913</v>
+        <v>79828</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="J66" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>1933</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
+        <v>1200</v>
+      </c>
+      <c r="L66" t="n">
+        <v>10</v>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O66" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P66" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -9006,18 +9006,18 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W66" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X66" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -9033,18 +9033,18 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr"/>
@@ -9071,83 +9071,85 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>79821</v>
+        <v>79996</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1000</v>
+        <v>6400</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>6400</v>
       </c>
       <c r="J67" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>2850</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
+        <v>6400</v>
+      </c>
+      <c r="L67" t="n">
+        <v>25</v>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>316</v>
+        <v>1000</v>
       </c>
       <c r="P67" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -9163,18 +9165,18 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr"/>
@@ -9201,83 +9203,83 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>79926</v>
+        <v>80056</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>4085</v>
+        <v>200</v>
       </c>
       <c r="J68" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>3880</v>
+        <v>200</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O68" t="n">
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="P68" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="T68" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W68" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="X68" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -9293,7 +9295,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>梱包+スリット機1　湖南</t>
+          <t>巻返し+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -9304,7 +9306,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr"/>
@@ -9331,11 +9333,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>79987</v>
+        <v>79398</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -9351,7 +9353,7 @@
         <v>12000</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I69" t="n">
         <v>12000</v>
@@ -9381,13 +9383,13 @@
         <v>3</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46188</v>
+        <v>46171</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46188</v>
+        <v>46171</v>
       </c>
       <c r="T69" s="1" t="n">
-        <v>46182</v>
+        <v>46168</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -9434,7 +9436,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr"/>
@@ -9461,15 +9463,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>79985</v>
+        <v>79913</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9478,66 +9480,66 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>10800</v>
+        <v>2000</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>10800</v>
+        <v>2000</v>
       </c>
       <c r="J70" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>10800</v>
+        <v>1933</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="O70" t="n">
-        <v>550</v>
+        <v>870</v>
       </c>
       <c r="P70" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46189</v>
+        <v>46171</v>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46189</v>
+        <v>46171</v>
       </c>
       <c r="T70" s="1" t="n">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W70" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X70" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -9553,7 +9555,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -9564,7 +9566,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr"/>
@@ -9591,11 +9593,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>79935</v>
+        <v>79821</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -9604,41 +9606,41 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K71" t="n">
-        <v>2000</v>
+        <v>2850</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N71" t="n">
         <v>100</v>
       </c>
       <c r="O71" t="n">
-        <v>1000</v>
+        <v>316</v>
       </c>
       <c r="P71" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R71" s="1" t="n">
         <v>46176</v>
@@ -9656,7 +9658,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W71" t="n">
@@ -9667,7 +9669,7 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -9683,7 +9685,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>梱包+SEC機　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -9721,83 +9723,83 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PN06-02</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>80058</v>
+        <v>80080</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>1750</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>100</v>
+        <v>1750</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O72" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="P72" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q72" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="R72" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="S72" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="T72" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W72" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X72" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9813,7 +9815,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>梱包+SEC機　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -9851,53 +9853,51 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>79826</v>
+        <v>79926</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>800</v>
+        <v>4085</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="K73" t="n">
-        <v>800</v>
-      </c>
-      <c r="L73" t="n">
-        <v>10</v>
-      </c>
+        <v>3880</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O73" t="n">
-        <v>740</v>
+        <v>870</v>
       </c>
       <c r="P73" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q73" t="n">
         <v>2</v>
@@ -9909,27 +9909,27 @@
         <v>46178</v>
       </c>
       <c r="T73" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="X73" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -9945,18 +9945,18 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>梱包+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr"/>
@@ -9983,85 +9983,83 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>79989</v>
+        <v>79987</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="J74" t="n">
+        <v>40</v>
+      </c>
+      <c r="K74" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>300</v>
+      </c>
+      <c r="O74" t="n">
+        <v>550</v>
+      </c>
+      <c r="P74" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q74" t="n">
         <v>3</v>
       </c>
-      <c r="K74" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L74" t="n">
-        <v>10</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>200</v>
-      </c>
-      <c r="O74" t="n">
-        <v>740</v>
-      </c>
-      <c r="P74" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>2</v>
-      </c>
       <c r="R74" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S74" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T74" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="S74" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="T74" s="1" t="n">
-        <v>46178</v>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W74" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X74" t="n">
-        <v>750</v>
+        <v>1110</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -10077,18 +10075,18 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr"/>
@@ -10115,85 +10113,83 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>79828</v>
+        <v>79985</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1200</v>
+        <v>10800</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1200</v>
+        <v>10800</v>
       </c>
       <c r="J75" t="n">
+        <v>36</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10800</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>30030-AP66- 550X300F-ABK0M</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>300</v>
+      </c>
+      <c r="O75" t="n">
+        <v>550</v>
+      </c>
+      <c r="P75" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q75" t="n">
         <v>3</v>
       </c>
-      <c r="K75" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L75" t="n">
-        <v>10</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>200</v>
-      </c>
-      <c r="O75" t="n">
-        <v>740</v>
-      </c>
-      <c r="P75" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>2</v>
-      </c>
       <c r="R75" s="1" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="T75" s="1" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W75" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X75" t="n">
-        <v>750</v>
+        <v>1110</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -10209,18 +10205,18 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>分割+エンボス　湖南</t>
+          <t>欠点表示+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr"/>
@@ -10237,6 +10233,662 @@
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PN06-01</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>79935</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J76" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>FEL3002BY05WDLG-EC</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>100</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P76" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2</v>
+      </c>
+      <c r="R76" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S76" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T76" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
+        </is>
+      </c>
+      <c r="W76" t="n">
+        <v>100</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>梱包+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PN06-02</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>80058</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>100</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>100</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>100</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>100</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P77" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>20</v>
+      </c>
+      <c r="R77" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S77" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T77" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>100</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>梱包+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Y5-40</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>79826</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>800</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>800</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>800</v>
+      </c>
+      <c r="L78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>200</v>
+      </c>
+      <c r="O78" t="n">
+        <v>740</v>
+      </c>
+      <c r="P78" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2</v>
+      </c>
+      <c r="R78" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T78" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>400</v>
+      </c>
+      <c r="X78" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>T6-2</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>79989</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L79" t="n">
+        <v>10</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>200</v>
+      </c>
+      <c r="O79" t="n">
+        <v>740</v>
+      </c>
+      <c r="P79" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2</v>
+      </c>
+      <c r="R79" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T79" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>400</v>
+      </c>
+      <c r="X79" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>（2026/6/5）</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Y5-42</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>79828</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L80" t="n">
+        <v>10</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>25020-FG00- 740X200F-AGR0M</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>200</v>
+      </c>
+      <c r="O80" t="n">
+        <v>740</v>
+      </c>
+      <c r="P80" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T80" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>25020-AG00- 750X400F-AGR0C</t>
+        </is>
+      </c>
+      <c r="W80" t="n">
+        <v>400</v>
+      </c>
+      <c r="X80" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>（2026/6/1）</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL80"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +607,71 @@
           <t>AI特別指定_解析</t>
         </is>
       </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Unnamed: 38</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Unnamed: 39</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Unnamed: 40</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Unnamed: 41</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 42</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Unnamed: 43</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Unnamed: 44</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 45</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 46</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 47</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 48</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>」グローバルコメント解析】</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>参照用・段階2で自動記録</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -619,85 +680,91 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79641</v>
+        <v>79404</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7200</v>
+        <v>7000</v>
       </c>
       <c r="H2" t="n">
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="I2" t="n">
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>7200</v>
+        <v>14000</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O2" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="P2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>46162</v>
+        <v>4</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X2" t="n">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -706,25 +773,25 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="AB2" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>（2026/5/20）</t>
+          <t>（2026/5/26）</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -741,6 +808,27 @@
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>※二重適用についで</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>配台への反映はメインシート「グローバルコメント」からのみ行ゝれした。このAX〜AY列は読み坖られません。編集しても次回実行まで配台に効しません。原文はメイン欄を参照してください。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -749,11 +837,11 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79408</v>
+        <v>79913</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -766,68 +854,74 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="H3" t="n">
-        <v>4400</v>
+        <v>1000</v>
       </c>
       <c r="I3" t="n">
-        <v>4400</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>18000</v>
+        <v>1933</v>
       </c>
       <c r="L3" t="n">
         <v>27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O3" t="n">
         <v>870</v>
       </c>
       <c r="P3" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>46167</v>
+        <v>2</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X3" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -836,10 +930,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>4600</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9200</v>
+        <v>776</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -854,7 +948,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>（2026/5/25）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -871,6 +965,27 @@
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>計画基準日時</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -879,65 +994,71 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Y5-34</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79583</v>
+        <v>79913</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3000</v>
+        <v>1943</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>6000</v>
+        <v>1933</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-A   C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O4" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P4" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>46168</v>
+        <v>2</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -946,18 +1067,18 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-A   C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X4" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -973,18 +1094,18 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1001,6 +1122,27 @@
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>工場休業日</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1009,65 +1151,71 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>V5-9</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79688</v>
+        <v>79706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="H5" t="n">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="I5" t="n">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X100F-A   C</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O5" t="n">
-        <v>1030</v>
+        <v>1180</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>46168</v>
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1076,18 +1224,18 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X200F-A   C</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X5" t="n">
-        <v>1030</v>
+        <v>1250</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1103,18 +1251,18 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/5/22）</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1131,93 +1279,122 @@
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>スキル覝件を無視</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C5-1</t>
+          <t>W5-22</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79706</v>
+        <v>80126</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4000</v>
+        <v>63</v>
       </c>
       <c r="H6" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4000</v>
+        <v>63</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20010-H600-1180X250F-AWH1C</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="O6" t="n">
-        <v>1180</v>
+        <v>1500</v>
       </c>
       <c r="P6" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>46164</v>
+        <v>1.1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>20010-B600-1250X250F-AWH1C</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="X6" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>スリット,EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1233,18 +1410,18 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/29）</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1261,6 +1438,27 @@
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>need人数1固定</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,85 +1467,91 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>W5-14</t>
+          <t>Y5-38</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79683</v>
+        <v>79823</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="I7" t="n">
-        <v>91</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>4000</v>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10010-JP67-1550X 20F-A   P</t>
+          <t>0R040-8Y0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="O7" t="n">
-        <v>1550</v>
+        <v>850</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>46164</v>
+        <v>4</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10010-AP67-1550X 91F-A   P</t>
+          <t>50080-AY0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="X7" t="n">
-        <v>1550</v>
+        <v>850</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1363,18 +1567,18 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -1391,6 +1595,27 @@
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>配台制限の撤廃</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,11 +1624,11 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>W6-7</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79686</v>
+        <v>80110</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1416,68 +1641,74 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
         <v>20</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="O8" t="n">
-        <v>1550</v>
+        <v>940</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="Q8" t="n">
         <v>2.5</v>
       </c>
-      <c r="R8" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>46164</v>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="X8" t="n">
-        <v>1650</v>
+        <v>940</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1504,7 +1735,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1521,6 +1752,27 @@
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>グローバルOP指定</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,65 +1781,71 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>PN06-01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79687</v>
+        <v>79935</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>271</v>
+        <v>2000</v>
       </c>
       <c r="H9" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>271</v>
+        <v>2000</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="P9" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>46164</v>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1596,18 +1854,18 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="X9" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1623,7 +1881,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1634,7 +1892,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr"/>
@@ -1651,6 +1909,27 @@
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>日付×工程フォーム指定</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,11 +1938,11 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>PN06-02</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79687</v>
+        <v>80058</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1672,52 +1951,58 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>100</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q10" t="n">
         <v>20</v>
       </c>
-      <c r="L10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1550</v>
-      </c>
-      <c r="P10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>46164</v>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1726,18 +2011,18 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="X10" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1753,18 +2038,18 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>（2026/5/22）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr"/>
@@ -1781,6 +2066,27 @@
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>グローバル速度ルール</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,85 +2095,91 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>W6-6</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79404</v>
+        <v>80108</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7000</v>
+        <v>1500</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7000</v>
+        <v>1500</v>
       </c>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>20020-AP17-1120X300F-A   P</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O11" t="n">
-        <v>680</v>
+        <v>1120</v>
       </c>
       <c r="P11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>46168</v>
+        <v>2</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>20020-AP17-1330X300F-A   P</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X11" t="n">
-        <v>680</v>
+        <v>1330</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1883,18 +2195,18 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr"/>
@@ -1911,6 +2223,27 @@
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>未適用メモ(AI)</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,11 +2252,11 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Y5-35</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79676</v>
+        <v>79821</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1936,68 +2269,74 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>3200</v>
+        <v>2850</v>
       </c>
       <c r="L12" t="n">
         <v>27</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>935</v>
+        <v>316</v>
       </c>
       <c r="P12" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>46168</v>
+        <v>4</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X12" t="n">
-        <v>935</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2024,7 +2363,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr"/>
@@ -2041,6 +2380,27 @@
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>AI覝約</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2049,65 +2409,71 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Y5-38</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79823</v>
+        <v>79821</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2000</v>
+        <v>950</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
         <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>4000</v>
+        <v>2850</v>
       </c>
       <c r="L13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 850X200F-AGA1C</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>850</v>
+        <v>316</v>
       </c>
       <c r="P13" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="R13" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>46170</v>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2116,18 +2482,18 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>50080-AY0B- 850X200F-AGA1C</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X13" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2143,18 +2509,18 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
@@ -2171,6 +2537,19 @@
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2179,85 +2558,91 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79913</v>
+        <v>80080</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>600</v>
+      </c>
+      <c r="L14" t="n">
         <v>20</v>
       </c>
-      <c r="K14" t="n">
-        <v>1933</v>
-      </c>
-      <c r="L14" t="n">
-        <v>27</v>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="O14" t="n">
-        <v>870</v>
+        <v>1550</v>
       </c>
       <c r="P14" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>46170</v>
+        <v>2.5</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2273,18 +2658,18 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr"/>
@@ -2301,6 +2686,19 @@
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2309,65 +2707,71 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79913</v>
+        <v>80100</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1943</v>
+        <v>500</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>250</v>
+      </c>
+      <c r="L15" t="n">
         <v>20</v>
       </c>
-      <c r="K15" t="n">
-        <v>1933</v>
-      </c>
-      <c r="L15" t="n">
-        <v>25</v>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="O15" t="n">
-        <v>870</v>
+        <v>1300</v>
       </c>
       <c r="P15" t="n">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="R15" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>46170</v>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2376,18 +2780,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2403,18 +2807,18 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
@@ -2431,6 +2835,19 @@
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2439,85 +2856,91 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79398</v>
+        <v>79754</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6000</v>
+        <v>1155</v>
       </c>
       <c r="H16" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>6000</v>
+        <v>1155</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>12000</v>
+        <v>2310</v>
       </c>
       <c r="L16" t="n">
         <v>25</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="O16" t="n">
-        <v>550</v>
+        <v>1080</v>
       </c>
       <c r="P16" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>46168</v>
+        <v>5</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>300</v>
+        <v>105</v>
       </c>
       <c r="X16" t="n">
-        <v>1110</v>
+        <v>1080</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2533,7 +2956,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2544,7 +2967,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr"/>
@@ -2561,6 +2984,19 @@
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2569,65 +3005,71 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79935</v>
+        <v>79754</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2000</v>
+        <v>2310</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2000</v>
+        <v>2310</v>
       </c>
       <c r="J17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2310</v>
+      </c>
+      <c r="L17" t="n">
         <v>20</v>
       </c>
-      <c r="K17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>25</v>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="O17" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>46174</v>
+        <v>5</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2636,18 +3078,18 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2663,18 +3105,18 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>EC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr"/>
@@ -2691,6 +3133,19 @@
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2699,65 +3154,71 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PN06-02</t>
+          <t>C6-1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80058</v>
+        <v>80116</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="L18" t="n">
         <v>25</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>0R040-8Y0B- 310X200G-A   C</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O18" t="n">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>46174</v>
+        <v>4</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2766,18 +3227,18 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2793,7 +3254,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>EC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2804,7 +3265,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
@@ -2821,6 +3282,19 @@
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2829,85 +3303,91 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79821</v>
+        <v>79996</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>2850</v>
+        <v>6400</v>
       </c>
       <c r="L19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>316</v>
+        <v>1000</v>
       </c>
       <c r="P19" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>46174</v>
+        <v>3</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2923,18 +3403,18 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
@@ -2951,6 +3431,19 @@
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2959,15 +3452,15 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79821</v>
+        <v>80080</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2976,68 +3469,74 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>950</v>
+        <v>1750</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>2850</v>
+        <v>600</v>
       </c>
       <c r="L20" t="n">
         <v>25</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O20" t="n">
-        <v>316</v>
+        <v>1550</v>
       </c>
       <c r="P20" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>46174</v>
+        <v>2.5</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3053,7 +3552,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3081,6 +3580,19 @@
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3089,85 +3601,91 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>Y6-1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80080</v>
+        <v>79867</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>600</v>
+        <v>4800</v>
       </c>
       <c r="L21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="O21" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="P21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>46174</v>
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="X21" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3183,12 +3701,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -3211,6 +3729,19 @@
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3219,65 +3750,71 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>Y5-39</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79926</v>
+        <v>79825</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3995</v>
+        <v>200</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4085</v>
+        <v>200</v>
       </c>
       <c r="J22" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>3880</v>
+        <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O22" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P22" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R22" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>46174</v>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3286,18 +3823,18 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3313,12 +3850,12 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3341,6 +3878,19 @@
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3349,85 +3899,91 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79926</v>
+        <v>79826</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3880</v>
+        <v>800</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3895</v>
+        <v>800</v>
       </c>
       <c r="J23" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>3880</v>
+        <v>800</v>
       </c>
       <c r="L23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O23" t="n">
-        <v>870</v>
+        <v>740</v>
       </c>
       <c r="P23" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="R23" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>46174</v>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3443,12 +3999,12 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -3471,6 +4027,19 @@
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3479,65 +4048,71 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>Y5-41</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79754</v>
+        <v>79827</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1155</v>
+        <v>200</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1155</v>
+        <v>200</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2310</v>
+        <v>200</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O24" t="n">
-        <v>1080</v>
+        <v>740</v>
       </c>
       <c r="P24" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>46175</v>
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3546,18 +4121,18 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="X24" t="n">
-        <v>1080</v>
+        <v>750</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3573,18 +4148,18 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr"/>
@@ -3601,6 +4176,19 @@
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3609,65 +4197,71 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79754</v>
+        <v>79926</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2310</v>
+        <v>3995</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2310</v>
+        <v>4085</v>
       </c>
       <c r="J25" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="K25" t="n">
-        <v>2310</v>
+        <v>3880</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="O25" t="n">
-        <v>1080</v>
+        <v>870</v>
       </c>
       <c r="P25" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>46175</v>
+        <v>2</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3676,18 +4270,18 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="X25" t="n">
-        <v>1080</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3703,18 +4297,18 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr"/>
@@ -3731,6 +4325,19 @@
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3739,85 +4346,91 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79996</v>
+        <v>79926</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3200</v>
+        <v>3880</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3200</v>
+        <v>3895</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>6400</v>
+        <v>3880</v>
       </c>
       <c r="L26" t="n">
         <v>25</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O26" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>46175</v>
+        <v>2</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3833,7 +4446,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3844,7 +4457,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr"/>
@@ -3861,6 +4474,19 @@
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3869,85 +4495,91 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Y6-1</t>
+          <t>T6-3</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79867</v>
+        <v>80061</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>4800</v>
+        <v>2000</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>30050-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="N27" t="n">
         <v>200</v>
       </c>
       <c r="O27" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="P27" t="n">
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>46174</v>
+        <v>5</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>30050-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="W27" t="n">
         <v>200</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3963,12 +4595,12 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -3991,6 +4623,19 @@
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3999,20 +4644,20 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Y5-39</t>
+          <t>T6-4</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79825</v>
+        <v>80063</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4025,59 +4670,65 @@
         <v>200</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>200</v>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30060-JG00-1000X100F-A   Q</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P28" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>46174</v>
+        <v>6</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X28" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4093,12 +4744,12 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
@@ -4121,6 +4772,19 @@
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4129,50 +4793,50 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79826</v>
+        <v>80064</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N29" t="n">
         <v>200</v>
       </c>
       <c r="O29" t="n">
-        <v>740</v>
+        <v>1050</v>
       </c>
       <c r="P29" t="n">
         <v>200</v>
@@ -4180,14 +4844,20 @@
       <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="R29" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>46174</v>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4196,18 +4866,18 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X29" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4223,12 +4893,12 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -4251,6 +4921,19 @@
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4259,20 +4942,20 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Y5-41</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79827</v>
+        <v>80064</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4288,56 +4971,62 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N30" t="n">
         <v>200</v>
       </c>
       <c r="O30" t="n">
-        <v>740</v>
+        <v>1050</v>
       </c>
       <c r="P30" t="n">
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>46176</v>
+        <v>2</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W30" t="n">
         <v>200</v>
       </c>
       <c r="X30" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4353,18 +5042,18 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -4381,6 +5070,19 @@
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4389,65 +5091,71 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80080</v>
+        <v>79994</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="O31" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="P31" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>46174</v>
+        <v>10</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4456,18 +5164,18 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="X31" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4483,18 +5191,18 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr"/>
@@ -4511,6 +5219,19 @@
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4519,65 +5240,71 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T6-3</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>80061</v>
+        <v>79994</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>500</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>30100-VG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>50</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P32" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q32" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L32" t="n">
-        <v>20</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>30050-JG00-1030X200F-ABK0Q</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>200</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1030</v>
-      </c>
-      <c r="P32" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>46174</v>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4586,18 +5313,18 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>30050-AG00-1030X200F-ABK0C</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X32" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4613,18 +5340,18 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr"/>
@@ -4641,6 +5368,19 @@
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4649,85 +5389,91 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T6-4</t>
+          <t>Y6-2</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80063</v>
+        <v>79868</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2800</v>
+      </c>
+      <c r="J33" t="n">
+        <v>14</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5600</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>30033-BY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
         <v>200</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="O33" t="n">
+        <v>640</v>
+      </c>
+      <c r="P33" t="n">
         <v>200</v>
       </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="Q33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>30066-AY00- 640X200F-AGA0C</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
         <v>200</v>
       </c>
-      <c r="L33" t="n">
-        <v>20</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>30060-JG00-1000X100F-A   Q</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>100</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P33" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6</v>
-      </c>
-      <c r="R33" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T33" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>30060-AG00-1000X100F-A   C</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>100</v>
-      </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4743,18 +5489,18 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr"/>
@@ -4771,6 +5517,19 @@
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4779,65 +5538,71 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>80064</v>
+        <v>80056</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O34" t="n">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="P34" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T34" s="1" t="n">
-        <v>46174</v>
+        <v>9</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4846,18 +5611,18 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X34" t="n">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4873,18 +5638,18 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr"/>
@@ -4901,6 +5666,19 @@
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4909,20 +5687,20 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>T6-6</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>80064</v>
+        <v>80094</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4938,56 +5716,62 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N35" t="n">
         <v>200</v>
       </c>
       <c r="O35" t="n">
-        <v>1050</v>
+        <v>740</v>
       </c>
       <c r="P35" t="n">
         <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T35" s="1" t="n">
-        <v>46174</v>
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>200</v>
       </c>
       <c r="X35" t="n">
-        <v>1050</v>
+        <v>750</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -5003,18 +5787,18 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/5/1）</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr"/>
@@ -5031,6 +5815,19 @@
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5039,85 +5836,91 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Y6-2</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>79868</v>
+        <v>79605</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>5600</v>
+        <v>1400</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N36" t="n">
         <v>200</v>
       </c>
       <c r="O36" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="P36" t="n">
         <v>200</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R36" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T36" s="1" t="n">
-        <v>46175</v>
+        <v>3</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>200</v>
       </c>
       <c r="X36" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5133,18 +5936,18 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr"/>
@@ -5161,6 +5964,19 @@
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5169,11 +5985,11 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>80056</v>
+        <v>79822</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5186,68 +6002,74 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="L37" t="n">
         <v>25</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O37" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
-      </c>
-      <c r="R37" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>46176</v>
+        <v>3</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X37" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5274,7 +6096,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr"/>
@@ -5291,6 +6113,19 @@
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5299,65 +6134,71 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>79822</v>
+        <v>80081</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="L38" t="n">
         <v>25</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>20020-AP17-1410X300F-A   V</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O38" t="n">
-        <v>1000</v>
+        <v>1410</v>
       </c>
       <c r="P38" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
-      </c>
-      <c r="R38" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>46175</v>
+        <v>2</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5366,18 +6207,18 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>20020-AP17-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5393,7 +6234,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -5421,6 +6262,19 @@
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5429,11 +6283,11 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>79994</v>
+        <v>79989</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5446,68 +6300,74 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="L39" t="n">
         <v>10</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O39" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P39" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
-      </c>
-      <c r="R39" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>46176</v>
+        <v>2</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5534,7 +6394,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr"/>
@@ -5551,6 +6411,19 @@
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5559,65 +6432,71 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>V6-4</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>79994</v>
+        <v>80129</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L40" t="n">
         <v>25</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>15020-BA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O40" t="n">
         <v>1000</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
-      </c>
-      <c r="R40" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>46176</v>
+        <v>2</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -5626,18 +6505,18 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>15040-AA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5653,7 +6532,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -5664,7 +6543,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr"/>
@@ -5681,6 +6560,19 @@
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5689,85 +6581,91 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T6-6</t>
+          <t>V6-5</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80094</v>
+        <v>80133</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>15020-BA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="O41" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>46143</v>
+        <v>2</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>15040-AA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="X41" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5783,18 +6681,18 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr"/>
@@ -5811,6 +6709,19 @@
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5819,43 +6730,43 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>V6-6</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>79605</v>
+        <v>80136</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="L42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>30025-BV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -5868,16 +6779,22 @@
         <v>200</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
-      </c>
-      <c r="R42" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T42" s="1" t="n">
-        <v>46176</v>
+        <v>2.5</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5886,7 +6803,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>30050-AV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -5897,7 +6814,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5913,18 +6830,18 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr"/>
@@ -5941,6 +6858,19 @@
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5949,85 +6879,91 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80081</v>
+        <v>80137</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L43" t="n">
         <v>25</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>20020-AP17-1410X300F-A   V</t>
+          <t>30025-BS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O43" t="n">
-        <v>1410</v>
+        <v>1000</v>
       </c>
       <c r="P43" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
-      </c>
-      <c r="R43" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>46175</v>
+        <v>2.5</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>20020-AP17-1440X300F-A   P</t>
+          <t>30050-AS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X43" t="n">
-        <v>1440</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -6043,7 +6979,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6054,7 +6990,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr"/>
@@ -6071,6 +7007,19 @@
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6079,65 +7028,71 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>Y6-11</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>79989</v>
+        <v>80060</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N44" t="n">
         <v>200</v>
       </c>
       <c r="O44" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P44" t="n">
         <v>200</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
-      </c>
-      <c r="R44" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>46178</v>
+        <v>3</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6146,18 +7101,18 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X44" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -6173,18 +7128,18 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr"/>
@@ -6201,6 +7156,19 @@
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6209,65 +7177,71 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y6-11</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>80060</v>
+        <v>79871</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>2000</v>
+        <v>6400</v>
       </c>
       <c r="L45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N45" t="n">
         <v>200</v>
       </c>
       <c r="O45" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P45" t="n">
         <v>200</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
-      </c>
-      <c r="R45" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>46177</v>
+        <v>4</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6276,18 +7250,18 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W45" t="n">
         <v>200</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -6303,18 +7277,18 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr"/>
@@ -6331,6 +7305,19 @@
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6339,11 +7326,11 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Y6-6</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79874</v>
+        <v>79871</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6356,33 +7343,33 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>200</v>
+        <v>3200</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>200</v>
+        <v>3200</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>400</v>
+        <v>6400</v>
       </c>
       <c r="L46" t="n">
         <v>27</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N46" t="n">
         <v>200</v>
       </c>
       <c r="O46" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P46" t="n">
         <v>200</v>
@@ -6390,34 +7377,40 @@
       <c r="Q46" t="n">
         <v>4</v>
       </c>
-      <c r="R46" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>46177</v>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W46" t="n">
         <v>200</v>
       </c>
       <c r="X46" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6444,7 +7437,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr"/>
@@ -6461,6 +7454,19 @@
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6469,39 +7475,39 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Y6-7</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79875</v>
+        <v>79872</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3800</v>
+        <v>1600</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>3800</v>
+        <v>1600</v>
       </c>
       <c r="J47" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>7600</v>
+        <v>3200</v>
       </c>
       <c r="L47" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -6520,14 +7526,20 @@
       <c r="Q47" t="n">
         <v>4</v>
       </c>
-      <c r="R47" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S47" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T47" s="1" t="n">
-        <v>46177</v>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -6536,7 +7548,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -6547,7 +7559,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6563,18 +7575,18 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr"/>
@@ -6591,6 +7603,19 @@
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6599,11 +7624,11 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y6-8</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>79876</v>
+        <v>79872</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6616,26 +7641,26 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="L48" t="n">
         <v>27</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -6650,14 +7675,20 @@
       <c r="Q48" t="n">
         <v>4</v>
       </c>
-      <c r="R48" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S48" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T48" s="1" t="n">
-        <v>46177</v>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -6666,7 +7697,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -6677,7 +7708,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6704,7 +7735,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr"/>
@@ -6721,6 +7752,19 @@
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6729,11 +7773,11 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>79871</v>
+        <v>79873</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6746,33 +7790,33 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="J49" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>6400</v>
+        <v>1200</v>
       </c>
       <c r="L49" t="n">
         <v>20</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>200</v>
       </c>
       <c r="O49" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P49" t="n">
         <v>200</v>
@@ -6780,30 +7824,36 @@
       <c r="Q49" t="n">
         <v>4</v>
       </c>
-      <c r="R49" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T49" s="1" t="n">
-        <v>46178</v>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W49" t="n">
         <v>200</v>
       </c>
       <c r="X49" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -6851,6 +7901,19 @@
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6859,11 +7922,11 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79871</v>
+        <v>79873</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6876,33 +7939,33 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="J50" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>6400</v>
+        <v>1200</v>
       </c>
       <c r="L50" t="n">
         <v>27</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N50" t="n">
         <v>200</v>
       </c>
       <c r="O50" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P50" t="n">
         <v>200</v>
@@ -6910,30 +7973,36 @@
       <c r="Q50" t="n">
         <v>4</v>
       </c>
-      <c r="R50" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S50" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T50" s="1" t="n">
-        <v>46178</v>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W50" t="n">
         <v>200</v>
       </c>
       <c r="X50" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -6981,6 +8050,19 @@
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6989,50 +8071,50 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-6</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79872</v>
+        <v>79874</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>200</v>
       </c>
       <c r="O51" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P51" t="n">
         <v>200</v>
@@ -7040,34 +8122,40 @@
       <c r="Q51" t="n">
         <v>4</v>
       </c>
-      <c r="R51" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S51" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T51" s="1" t="n">
-        <v>46178</v>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>200</v>
       </c>
       <c r="X51" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -7083,18 +8171,18 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr"/>
@@ -7111,6 +8199,19 @@
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7119,11 +8220,11 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-7</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79872</v>
+        <v>79875</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -7136,19 +8237,19 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1600</v>
+        <v>3800</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1600</v>
+        <v>3800</v>
       </c>
       <c r="J52" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>3200</v>
+        <v>7600</v>
       </c>
       <c r="L52" t="n">
         <v>27</v>
@@ -7170,14 +8271,20 @@
       <c r="Q52" t="n">
         <v>4</v>
       </c>
-      <c r="R52" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S52" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T52" s="1" t="n">
-        <v>46178</v>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7186,7 +8293,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -7197,7 +8304,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -7224,7 +8331,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr"/>
@@ -7241,6 +8348,19 @@
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7249,50 +8369,50 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-8</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79873</v>
+        <v>79876</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="L53" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N53" t="n">
         <v>200</v>
       </c>
       <c r="O53" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P53" t="n">
         <v>200</v>
@@ -7300,34 +8420,40 @@
       <c r="Q53" t="n">
         <v>4</v>
       </c>
-      <c r="R53" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S53" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T53" s="1" t="n">
-        <v>46178</v>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W53" t="n">
         <v>200</v>
       </c>
       <c r="X53" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7343,18 +8469,18 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
@@ -7371,6 +8497,19 @@
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7379,85 +8518,91 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79873</v>
+        <v>79927</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>600</v>
+        <v>29400</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>600</v>
+        <v>29400</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="K54" t="n">
-        <v>1200</v>
+        <v>29400</v>
       </c>
       <c r="L54" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O54" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="P54" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
-      </c>
-      <c r="R54" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="S54" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="T54" s="1" t="n">
-        <v>46178</v>
+        <v>2.5</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026/06/12</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2026/06/12</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X54" t="n">
-        <v>680</v>
+        <v>1050</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -7473,18 +8618,18 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr"/>
@@ -7501,6 +8646,19 @@
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7509,11 +8667,11 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79927</v>
+        <v>79987</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7526,68 +8684,74 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>29400</v>
+        <v>6000</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>29400</v>
+        <v>6000</v>
       </c>
       <c r="J55" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>29400</v>
+        <v>12000</v>
       </c>
       <c r="L55" t="n">
         <v>25</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N55" t="n">
         <v>300</v>
       </c>
       <c r="O55" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P55" t="n">
         <v>300</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R55" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="S55" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="T55" s="1" t="n">
-        <v>46174</v>
+        <v>3</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W55" t="n">
         <v>300</v>
       </c>
       <c r="X55" t="n">
-        <v>1050</v>
+        <v>1110</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7614,7 +8778,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr"/>
@@ -7631,6 +8795,19 @@
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7639,20 +8816,20 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>Y6-12</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79987</v>
+        <v>80128</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7665,7 +8842,7 @@
         <v>6000</v>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
         <v>12000</v>
@@ -7675,29 +8852,35 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O56" t="n">
-        <v>550</v>
+        <v>640</v>
       </c>
       <c r="P56" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
-      </c>
-      <c r="R56" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="S56" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="T56" s="1" t="n">
-        <v>46182</v>
+        <v>2</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -7706,18 +8889,18 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="X56" t="n">
-        <v>1110</v>
+        <v>640</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7733,7 +8916,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -7744,7 +8927,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr"/>
@@ -7761,6 +8944,19 @@
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7820,14 +9016,20 @@
       <c r="Q57" t="n">
         <v>2</v>
       </c>
-      <c r="R57" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="S57" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="T57" s="1" t="n">
-        <v>46182</v>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -7891,6 +9093,19 @@
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7950,14 +9165,20 @@
       <c r="Q58" t="n">
         <v>2</v>
       </c>
-      <c r="R58" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="S58" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="T58" s="1" t="n">
-        <v>46182</v>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -8021,6 +9242,19 @@
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8080,14 +9314,20 @@
       <c r="Q59" t="n">
         <v>3</v>
       </c>
-      <c r="R59" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="S59" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="T59" s="1" t="n">
-        <v>46183</v>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8151,6 +9391,19 @@
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8210,14 +9463,20 @@
       <c r="Q60" t="n">
         <v>6</v>
       </c>
-      <c r="R60" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="S60" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="T60" s="1" t="n">
-        <v>46184</v>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026/06/17</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2026/06/17</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8281,6 +9540,19 @@
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8340,14 +9612,20 @@
       <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R61" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="S61" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="T61" s="1" t="n">
-        <v>46182</v>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8411,6 +9689,19 @@
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8470,14 +9761,20 @@
       <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="R62" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="S62" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="T62" s="1" t="n">
-        <v>46182</v>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8541,6 +9838,19 @@
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8600,14 +9910,20 @@
       <c r="Q63" t="n">
         <v>2</v>
       </c>
-      <c r="R63" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="S63" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="T63" s="1" t="n">
-        <v>46182</v>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8671,6 +9987,19 @@
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8730,14 +10059,20 @@
       <c r="Q64" t="n">
         <v>2</v>
       </c>
-      <c r="R64" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="S64" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="T64" s="1" t="n">
-        <v>46183</v>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8801,6 +10136,19 @@
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8860,14 +10208,20 @@
       <c r="Q65" t="n">
         <v>2</v>
       </c>
-      <c r="R65" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="S65" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="T65" s="1" t="n">
-        <v>46183</v>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8931,6 +10285,19 @@
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8990,14 +10357,20 @@
       <c r="Q66" t="n">
         <v>2</v>
       </c>
-      <c r="R66" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="S66" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="T66" s="1" t="n">
-        <v>46174</v>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -9061,6 +10434,19 @@
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -9122,14 +10508,20 @@
       <c r="Q67" t="n">
         <v>3</v>
       </c>
-      <c r="R67" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S67" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T67" s="1" t="n">
-        <v>46175</v>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -9193,6 +10585,19 @@
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -9252,14 +10657,20 @@
       <c r="Q68" t="n">
         <v>9</v>
       </c>
-      <c r="R68" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="S68" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="T68" s="1" t="n">
-        <v>46176</v>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -9323,6 +10734,19 @@
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -9333,83 +10757,89 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>79398</v>
+        <v>80100</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>12000</v>
+        <v>250</v>
       </c>
       <c r="H69" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>12000</v>
+        <v>250</v>
       </c>
       <c r="J69" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>12000</v>
+        <v>250</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O69" t="n">
-        <v>550</v>
+        <v>1300</v>
       </c>
       <c r="P69" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
-      </c>
-      <c r="R69" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S69" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T69" s="1" t="n">
-        <v>46168</v>
+        <v>2</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="W69" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="X69" t="n">
-        <v>1110</v>
+        <v>1300</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -9425,7 +10855,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>欠点表示+スリット機1　湖南</t>
+          <t>巻返し+EC機　湖南</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -9436,7 +10866,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>（2026/5/26）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr"/>
@@ -9453,6 +10883,19 @@
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -9512,14 +10955,20 @@
       <c r="Q70" t="n">
         <v>2</v>
       </c>
-      <c r="R70" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="S70" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="T70" s="1" t="n">
-        <v>46170</v>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -9583,6 +11032,19 @@
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -9642,14 +11104,20 @@
       <c r="Q71" t="n">
         <v>4</v>
       </c>
-      <c r="R71" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S71" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T71" s="1" t="n">
-        <v>46174</v>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -9713,6 +11181,19 @@
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -9772,14 +11253,20 @@
       <c r="Q72" t="n">
         <v>2.5</v>
       </c>
-      <c r="R72" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S72" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T72" s="1" t="n">
-        <v>46174</v>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -9843,6 +11330,19 @@
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -9902,14 +11402,20 @@
       <c r="Q73" t="n">
         <v>2</v>
       </c>
-      <c r="R73" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S73" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T73" s="1" t="n">
-        <v>46174</v>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -9973,6 +11479,19 @@
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -10032,14 +11551,20 @@
       <c r="Q74" t="n">
         <v>3</v>
       </c>
-      <c r="R74" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="S74" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="T74" s="1" t="n">
-        <v>46182</v>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -10086,7 +11611,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr"/>
@@ -10103,6 +11628,19 @@
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -10162,14 +11700,20 @@
       <c r="Q75" t="n">
         <v>3</v>
       </c>
-      <c r="R75" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="S75" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="T75" s="1" t="n">
-        <v>46183</v>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -10233,6 +11777,19 @@
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -10292,14 +11849,20 @@
       <c r="Q76" t="n">
         <v>2</v>
       </c>
-      <c r="R76" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S76" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T76" s="1" t="n">
-        <v>46174</v>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -10363,6 +11926,19 @@
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -10422,14 +11998,20 @@
       <c r="Q77" t="n">
         <v>20</v>
       </c>
-      <c r="R77" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="S77" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="T77" s="1" t="n">
-        <v>46174</v>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -10493,6 +12075,19 @@
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -10554,14 +12149,20 @@
       <c r="Q78" t="n">
         <v>2</v>
       </c>
-      <c r="R78" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="S78" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="T78" s="1" t="n">
-        <v>46174</v>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -10625,6 +12226,19 @@
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -10686,14 +12300,20 @@
       <c r="Q79" t="n">
         <v>2</v>
       </c>
-      <c r="R79" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="S79" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="T79" s="1" t="n">
-        <v>46178</v>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -10757,6 +12377,19 @@
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -10818,14 +12451,20 @@
       <c r="Q80" t="n">
         <v>2</v>
       </c>
-      <c r="R80" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="S80" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="T80" s="1" t="n">
-        <v>46174</v>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -10889,6 +12528,19 @@
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/plan_input_tasks.xlsx
+++ b/output/plan_input_tasks.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AL80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,71 +611,6 @@
           <t>AI特別指定_解析</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>」グローバルコメント解析】</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>参照用・段階2で自動記録</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -731,20 +670,14 @@
       <c r="Q2" t="n">
         <v>4</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
+      <c r="R2" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -808,27 +741,6 @@
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>※二重適用についで</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>配台への反映はメインシート「グローバルコメント」からのみ行ゝれした。このAX〜AY列は読み坖られません。編集しても次回実行まで配台に効しません。原文はメイン欄を参照してください。</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,20 +800,14 @@
       <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+      <c r="R3" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -965,27 +871,6 @@
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>計画基準日時</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,20 +930,14 @@
       <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+      <c r="R4" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1122,27 +1001,6 @@
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>工場休業日</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1202,20 +1060,14 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
+      <c r="R5" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1279,102 +1131,73 @@
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>スキル覝件を無視</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>W5-22</t>
+          <t>Y5-38</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80126</v>
+        <v>79823</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>2000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I6" t="n">
-        <v>63</v>
+        <v>2000</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>63</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>4000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>13011-APR0-1500X 63F-A   X</t>
+          <t>0R040-8Y0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="O6" t="n">
-        <v>1500</v>
+        <v>850</v>
       </c>
       <c r="P6" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1383,18 +1206,18 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>13011-APR0-1500X 63F-A   X</t>
+          <t>50080-AY0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="X6" t="n">
-        <v>1500</v>
+        <v>850</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1410,18 +1233,18 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>検査+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>（―）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>（2026/5/29）</t>
+          <t>（2026/5/28）</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1438,27 +1261,6 @@
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>need人数1固定</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1467,71 +1269,65 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y5-38</t>
+          <t>W6-7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79823</v>
+        <v>80110</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 850X200F-AGA1C</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O7" t="n">
-        <v>850</v>
+        <v>940</v>
       </c>
       <c r="P7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1540,18 +1336,18 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50080-AY0B- 850X200F-AGA1C</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X7" t="n">
-        <v>850</v>
+        <v>940</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1567,18 +1363,18 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>（2026/5/28）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -1595,27 +1391,6 @@
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>配台制限の撤廃</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1624,11 +1399,11 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>W6-7</t>
+          <t>PN06-01</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80110</v>
+        <v>79935</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1637,58 +1412,52 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="J8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FEL3002BY05WDLG-EC</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>25025-JP17- 940X250F-A   Q</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>250</v>
-      </c>
-      <c r="O8" t="n">
-        <v>940</v>
-      </c>
-      <c r="P8" t="n">
-        <v>250</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+      <c r="R8" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1697,18 +1466,18 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>25025-JP17- 940X250F-A   Q</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="X8" t="n">
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1724,18 +1493,18 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>EC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1752,27 +1521,6 @@
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>グローバルOP指定</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1781,11 +1529,11 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PN06-01</t>
+          <t>PN06-02</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79935</v>
+        <v>80058</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1798,26 +1546,26 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1830,22 +1578,16 @@
         <v>100</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1854,7 +1596,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>FEL3002BGB-05WD-1000X100   B</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -1909,27 +1651,6 @@
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>日付×工程フォーム指定</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1938,71 +1659,65 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PN06-02</t>
+          <t>W6-6</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80058</v>
+        <v>80108</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>20020-AP17-1120X300F-A   P</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O10" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2011,18 +1726,18 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   B</t>
+          <t>20020-AP17-1330X300F-A   P</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>1330</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2038,7 +1753,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>EC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2066,27 +1781,6 @@
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>グローバル速度ルール</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2095,71 +1789,65 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W6-6</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80108</v>
+        <v>79821</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>1500</v>
+        <v>2850</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20020-AP17-1120X300F-A   P</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
-        <v>1120</v>
+        <v>316</v>
       </c>
       <c r="P11" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2168,18 +1856,18 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>20020-AP17-1330X300F-A   P</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X11" t="n">
-        <v>1330</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2195,12 +1883,12 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -2223,27 +1911,6 @@
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>未適用メモ(AI)</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2260,16 +1927,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2284,7 +1951,7 @@
         <v>2850</v>
       </c>
       <c r="L12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2303,20 +1970,14 @@
       <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R12" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2352,12 +2013,12 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -2380,27 +2041,6 @@
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>AI覝約</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>（なし）</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2409,91 +2049,85 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79821</v>
+        <v>80080</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>950</v>
+        <v>1750</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>2850</v>
+        <v>600</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O13" t="n">
-        <v>316</v>
+        <v>1550</v>
       </c>
       <c r="P13" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2509,12 +2143,12 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2537,19 +2171,6 @@
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2558,11 +2179,11 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80080</v>
+        <v>80100</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2575,74 +2196,68 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="L14" t="n">
         <v>20</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>250</v>
       </c>
       <c r="O14" t="n">
-        <v>1550</v>
+        <v>1300</v>
       </c>
       <c r="P14" t="n">
         <v>250</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>250</v>
       </c>
       <c r="X14" t="n">
-        <v>1550</v>
+        <v>1300</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2669,7 +2284,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr"/>
@@ -2686,19 +2301,6 @@
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2707,71 +2309,65 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80100</v>
+        <v>79754</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>500</v>
+        <v>1155</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>500</v>
+        <v>1155</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>250</v>
+        <v>2310</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15020-NP17-1300X250F-A   J</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="O15" t="n">
-        <v>1300</v>
+        <v>1080</v>
       </c>
       <c r="P15" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2780,18 +2376,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>15020-AP17-1300X250F-A   P</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="X15" t="n">
-        <v>1300</v>
+        <v>1080</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>EC,巻返し</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2807,12 +2403,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -2835,19 +2431,6 @@
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2864,31 +2447,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1155</v>
+        <v>2310</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1155</v>
+        <v>2310</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
         <v>2310</v>
       </c>
       <c r="L16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2907,20 +2490,14 @@
       <c r="Q16" t="n">
         <v>5</v>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+      <c r="R16" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2956,12 +2533,12 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
@@ -2984,19 +2561,6 @@
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3005,71 +2569,65 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>C6-1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79754</v>
+        <v>80116</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2310</v>
+        <v>1600</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2310</v>
+        <v>1600</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>2310</v>
+        <v>3200</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>0R040-8Y0B- 310X200G-A   C</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O17" t="n">
-        <v>1080</v>
+        <v>820</v>
       </c>
       <c r="P17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3078,18 +2636,18 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="X17" t="n">
-        <v>1080</v>
+        <v>820</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -3105,12 +2663,12 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -3133,19 +2691,6 @@
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3154,91 +2699,85 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C6-1</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80116</v>
+        <v>79996</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>3200</v>
+        <v>6400</v>
       </c>
       <c r="L18" t="n">
         <v>25</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 310X200G-A   C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="P18" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W18" t="n">
         <v>200</v>
       </c>
       <c r="X18" t="n">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3254,7 +2793,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3282,19 +2821,6 @@
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3303,71 +2829,65 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79996</v>
+        <v>80080</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3200</v>
+        <v>1750</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3200</v>
+        <v>1750</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>6400</v>
+        <v>600</v>
       </c>
       <c r="L19" t="n">
         <v>25</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O19" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3376,18 +2896,18 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -3403,7 +2923,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3414,7 +2934,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
@@ -3431,19 +2951,6 @@
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3452,91 +2959,85 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>Y6-1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80080</v>
+        <v>79867</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>600</v>
+        <v>4800</v>
       </c>
       <c r="L20" t="n">
         <v>25</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="O20" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="P20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="X20" t="n">
-        <v>1550</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3552,7 +3053,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3580,19 +3081,6 @@
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3601,71 +3089,65 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Y6-1</t>
+          <t>Y5-39</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79867</v>
+        <v>79825</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>4800</v>
+        <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>200</v>
       </c>
       <c r="O21" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="P21" t="n">
         <v>200</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3674,18 +3156,18 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W21" t="n">
         <v>200</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3701,12 +3183,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -3729,19 +3211,6 @@
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3750,11 +3219,11 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Y5-39</t>
+          <t>Y5-40</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79825</v>
+        <v>79826</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3767,19 +3236,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
@@ -3801,40 +3270,34 @@
       <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R22" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X22" t="n">
         <v>750</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3878,19 +3341,6 @@
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3899,11 +3349,11 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Y5-40</t>
+          <t>Y5-41</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79826</v>
+        <v>79827</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3916,26 +3366,26 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3948,42 +3398,36 @@
         <v>200</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X23" t="n">
         <v>750</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -4010,7 +3454,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr"/>
@@ -4027,19 +3471,6 @@
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4048,71 +3479,65 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Y5-41</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79827</v>
+        <v>79926</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>200</v>
+        <v>3995</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>200</v>
+        <v>4085</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>200</v>
+        <v>3880</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="O24" t="n">
-        <v>740</v>
+        <v>870</v>
       </c>
       <c r="P24" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -4121,18 +3546,18 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="X24" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -4148,18 +3573,18 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr"/>
@@ -4176,19 +3601,6 @@
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4205,31 +3617,31 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3995</v>
+        <v>3880</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4085</v>
+        <v>3895</v>
       </c>
       <c r="J25" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
         <v>3880</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -4248,20 +3660,14 @@
       <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R25" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4297,12 +3703,12 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -4325,19 +3731,6 @@
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4346,91 +3739,85 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>T6-3</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79926</v>
+        <v>80061</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3880</v>
+        <v>2000</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3895</v>
+        <v>2000</v>
       </c>
       <c r="J26" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>3880</v>
+        <v>2000</v>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>30050-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="O26" t="n">
-        <v>870</v>
+        <v>1030</v>
       </c>
       <c r="P26" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>30050-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4446,12 +3833,12 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -4474,19 +3861,6 @@
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4495,11 +3869,11 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T6-3</t>
+          <t>T6-4</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>80061</v>
+        <v>80063</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4512,54 +3886,48 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L27" t="n">
         <v>20</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30050-JG00-1030X200F-ABK0Q</t>
+          <t>30060-JG00-1000X100F-A   Q</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="P27" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4568,14 +3936,14 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>30050-AG00-1030X200F-ABK0C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X27" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -4623,19 +3991,6 @@
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4644,11 +3999,11 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T6-4</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4661,54 +4016,48 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L28" t="n">
         <v>20</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30060-JG00-1000X100F-A   Q</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O28" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4717,18 +4066,18 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4772,19 +4121,6 @@
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4801,31 +4137,31 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>400</v>
       </c>
       <c r="L29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -4844,20 +4180,14 @@
       <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R29" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4893,12 +4223,12 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -4921,19 +4251,6 @@
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4942,71 +4259,65 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80064</v>
+        <v>79994</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O30" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="P30" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5015,18 +4326,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="W30" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X30" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -5042,18 +4353,18 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -5070,19 +4381,6 @@
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5099,12 +4397,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5123,7 +4421,7 @@
         <v>500</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -5142,20 +4440,14 @@
       <c r="Q31" t="n">
         <v>10</v>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+      <c r="R31" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5191,12 +4483,12 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>巻返し+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -5219,19 +4511,6 @@
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5240,91 +4519,85 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>Y6-2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79994</v>
+        <v>79868</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>500</v>
+        <v>5600</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O32" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="P32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>3.3</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -5340,7 +4613,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>巻返し+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5351,7 +4624,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr"/>
@@ -5368,19 +4641,6 @@
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5389,11 +4649,11 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y6-2</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79868</v>
+        <v>80056</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5406,74 +4666,68 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O33" t="n">
-        <v>640</v>
+        <v>900</v>
       </c>
       <c r="P33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X33" t="n">
-        <v>640</v>
+        <v>900</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -5500,7 +4754,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr"/>
@@ -5517,19 +4771,6 @@
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5538,20 +4779,20 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>T6-6</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>80056</v>
+        <v>80094</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5564,65 +4805,59 @@
         <v>200</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>200</v>
       </c>
       <c r="L34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O34" t="n">
-        <v>900</v>
+        <v>740</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>10010-AY00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X34" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -5638,18 +4873,18 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/5/1）</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr"/>
@@ -5666,19 +4901,6 @@
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5687,91 +4909,85 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T6-6</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>80094</v>
+        <v>79605</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N35" t="n">
         <v>200</v>
       </c>
       <c r="O35" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P35" t="n">
         <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026/05/01</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>10010-AY00- 750X200F-AGR0C</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>200</v>
       </c>
       <c r="X35" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -5787,18 +5003,18 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>（2026/5/1）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr"/>
@@ -5815,19 +5031,6 @@
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5836,43 +5039,43 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>Y5-37</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>79605</v>
+        <v>79822</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>1400</v>
+        <v>4000</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5887,29 +5090,23 @@
       <c r="Q36" t="n">
         <v>3</v>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+      <c r="R36" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -5920,7 +5117,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5936,18 +5133,18 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr"/>
@@ -5964,19 +5161,6 @@
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5985,71 +5169,65 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Y5-37</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79822</v>
+        <v>80081</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="L37" t="n">
         <v>25</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>20020-AP17-1410X300F-A   V</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O37" t="n">
-        <v>1000</v>
+        <v>1410</v>
       </c>
       <c r="P37" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6058,18 +5236,18 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>20020-AP17-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -6085,7 +5263,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6113,19 +5291,6 @@
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6134,71 +5299,65 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>T6-2</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>80081</v>
+        <v>79989</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="L38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>20020-AP17-1410X300F-A   V</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O38" t="n">
-        <v>1410</v>
+        <v>740</v>
       </c>
       <c r="P38" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+      <c r="R38" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6207,18 +5366,18 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>20020-AP17-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X38" t="n">
-        <v>1440</v>
+        <v>750</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -6234,18 +5393,18 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr"/>
@@ -6262,19 +5421,6 @@
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6283,91 +5429,85 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T6-2</t>
+          <t>V6-4</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>79989</v>
+        <v>80129</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>15020-BA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="O39" t="n">
-        <v>740</v>
+        <v>1000</v>
       </c>
       <c r="P39" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="Q39" t="n">
         <v>2</v>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R39" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>15040-AA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="X39" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -6383,12 +5523,12 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -6411,19 +5551,6 @@
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6432,11 +5559,11 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>V6-4</t>
+          <t>V6-5</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -6458,7 +5585,7 @@
         <v>150</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>300</v>
@@ -6468,35 +5595,29 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15020-BA00-1000X 75F-ABK0C</t>
+          <t>15020-BA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="O40" t="n">
         <v>1000</v>
       </c>
       <c r="P40" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R40" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6505,11 +5626,11 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>15040-AA00-1000X 75F-ABK0C</t>
+          <t>15040-AA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -6560,19 +5681,6 @@
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6581,11 +5689,11 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>V6-5</t>
+          <t>V6-6</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -6598,54 +5706,48 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="L41" t="n">
         <v>25</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15020-BA00-1000X150F-ABK0C</t>
+          <t>30025-BV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O41" t="n">
         <v>1000</v>
       </c>
       <c r="P41" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6654,11 +5756,11 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>15040-AA00-1000X150F-ABK0C</t>
+          <t>30050-AV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -6709,19 +5811,6 @@
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6730,11 +5819,11 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>V6-6</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>80136</v>
+        <v>80137</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -6747,26 +5836,26 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="L42" t="n">
         <v>25</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>30025-BV90-1000X200F-A   C</t>
+          <t>30025-BS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6781,20 +5870,14 @@
       <c r="Q42" t="n">
         <v>2.5</v>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R42" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6803,7 +5886,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>30050-AV90-1000X200F-A   C</t>
+          <t>30050-AS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -6858,19 +5941,6 @@
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6879,11 +5949,11 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>V6-7</t>
+          <t>Y6-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80137</v>
+        <v>80060</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -6896,26 +5966,26 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="L43" t="n">
         <v>25</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>30025-BS60-1000X200F-A   C</t>
+          <t>30030-BG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6928,31 +5998,25 @@
         <v>200</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>30050-AS60-1000X200F-A   C</t>
+          <t>30060-AG00-1000X200F-ABK0C</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -6990,7 +6054,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr"/>
@@ -7007,19 +6071,6 @@
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7028,71 +6079,65 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y6-11</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>80060</v>
+        <v>79871</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
-        <v>2000</v>
+        <v>6400</v>
       </c>
       <c r="L44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X200F-ABK0C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N44" t="n">
         <v>200</v>
       </c>
       <c r="O44" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="P44" t="n">
         <v>200</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7101,18 +6146,18 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="W44" t="n">
         <v>200</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -7128,18 +6173,18 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr"/>
@@ -7156,19 +6201,6 @@
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7185,12 +6217,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7209,7 +6241,7 @@
         <v>6400</v>
       </c>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7228,20 +6260,14 @@
       <c r="Q45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R45" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7277,12 +6303,12 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -7305,19 +6331,6 @@
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7326,43 +6339,43 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79871</v>
+        <v>79872</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" t="n">
         <v>3200</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J46" t="n">
-        <v>16</v>
-      </c>
-      <c r="K46" t="n">
-        <v>6400</v>
-      </c>
       <c r="L46" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7377,20 +6390,14 @@
       <c r="Q46" t="n">
         <v>4</v>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R46" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7399,7 +6406,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7426,12 +6433,12 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -7454,19 +6461,6 @@
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
-      <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7483,12 +6477,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7507,7 +6501,7 @@
         <v>3200</v>
       </c>
       <c r="L47" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7526,20 +6520,14 @@
       <c r="Q47" t="n">
         <v>4</v>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R47" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7575,12 +6563,12 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -7603,19 +6591,6 @@
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7624,50 +6599,50 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="J48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="L48" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>200</v>
       </c>
       <c r="O48" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="P48" t="n">
         <v>200</v>
@@ -7675,36 +6650,30 @@
       <c r="Q48" t="n">
         <v>4</v>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R48" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>200</v>
       </c>
       <c r="X48" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -7724,12 +6693,12 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>接続+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -7752,19 +6721,6 @@
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7781,12 +6737,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7805,7 +6761,7 @@
         <v>1200</v>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -7824,20 +6780,14 @@
       <c r="Q49" t="n">
         <v>4</v>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R49" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7873,12 +6823,12 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>接続+熱融着機　湖南</t>
+          <t>SEC+SEC機　湖南</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（27）</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -7901,19 +6851,6 @@
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7922,11 +6859,11 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>Y6-6</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79873</v>
+        <v>79874</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -7939,19 +6876,19 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="L50" t="n">
         <v>27</v>
@@ -7973,20 +6910,14 @@
       <c r="Q50" t="n">
         <v>4</v>
       </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R50" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S50" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7995,7 +6926,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -8006,7 +6937,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -8033,7 +6964,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr"/>
@@ -8050,19 +6981,6 @@
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8071,11 +6989,11 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Y6-6</t>
+          <t>Y6-7</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79874</v>
+        <v>79875</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -8088,33 +7006,33 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>200</v>
+        <v>3800</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>200</v>
+        <v>3800</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>400</v>
+        <v>7600</v>
       </c>
       <c r="L51" t="n">
         <v>27</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>200</v>
       </c>
       <c r="O51" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="P51" t="n">
         <v>200</v>
@@ -8122,36 +7040,30 @@
       <c r="Q51" t="n">
         <v>4</v>
       </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R51" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>200</v>
       </c>
       <c r="X51" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -8199,19 +7111,6 @@
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8220,11 +7119,11 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Y6-7</t>
+          <t>Y6-8</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79875</v>
+        <v>79876</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -8237,26 +7136,26 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3800</v>
+        <v>800</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>3800</v>
+        <v>800</v>
       </c>
       <c r="J52" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="L52" t="n">
         <v>27</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8271,20 +7170,14 @@
       <c r="Q52" t="n">
         <v>4</v>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R52" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="S52" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8293,7 +7186,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -8348,19 +7241,6 @@
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr"/>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8369,91 +7249,85 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Y6-8</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79876</v>
+        <v>79927</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>800</v>
+        <v>29400</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>800</v>
+        <v>29400</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="K53" t="n">
-        <v>1600</v>
+        <v>29400</v>
       </c>
       <c r="L53" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O53" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="P53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="R53" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="S53" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X53" t="n">
-        <v>870</v>
+        <v>1050</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -8469,18 +7343,18 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>SEC+SEC機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>（27）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
@@ -8497,19 +7371,6 @@
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8518,11 +7379,11 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79927</v>
+        <v>79987</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -8535,74 +7396,68 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>29400</v>
+        <v>6000</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>29400</v>
+        <v>6000</v>
       </c>
       <c r="J54" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>29400</v>
+        <v>12000</v>
       </c>
       <c r="L54" t="n">
         <v>25</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>300</v>
       </c>
       <c r="O54" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P54" t="n">
         <v>300</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>2026/06/12</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>2026/06/12</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R54" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S54" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T54" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W54" t="n">
         <v>300</v>
       </c>
       <c r="X54" t="n">
-        <v>1050</v>
+        <v>1110</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -8629,7 +7484,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/5）</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr"/>
@@ -8646,19 +7501,6 @@
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8667,20 +7509,20 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>Y6-12</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79987</v>
+        <v>80128</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8693,7 +7535,7 @@
         <v>6000</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
         <v>12000</v>
@@ -8703,35 +7545,29 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O55" t="n">
-        <v>550</v>
+        <v>640</v>
       </c>
       <c r="P55" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R55" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S55" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T55" s="1" t="n">
+        <v>46177</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8740,18 +7576,18 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="X55" t="n">
-        <v>1110</v>
+        <v>640</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -8767,7 +7603,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8778,7 +7614,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>（2026/6/5）</t>
+          <t>（2026/6/4）</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr"/>
@@ -8795,19 +7631,6 @@
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8816,20 +7639,20 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Y6-12</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>80128</v>
+        <v>80065</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8842,45 +7665,39 @@
         <v>6000</v>
       </c>
       <c r="J56" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="L56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O56" t="n">
-        <v>640</v>
+        <v>1440</v>
       </c>
       <c r="P56" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q56" t="n">
         <v>2</v>
       </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
+      <c r="R56" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="S56" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8889,18 +7706,18 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="X56" t="n">
-        <v>640</v>
+        <v>1440</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -8916,18 +7733,18 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>スライス+スライス機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>（2026/6/4）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr"/>
@@ -8944,19 +7761,6 @@
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8973,12 +7777,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8997,7 +7801,7 @@
         <v>6000</v>
       </c>
       <c r="L57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -9016,20 +7820,14 @@
       <c r="Q57" t="n">
         <v>2</v>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+      <c r="R57" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="S57" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T57" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9065,12 +7863,12 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -9093,19 +7891,6 @@
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="inlineStr"/>
-      <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="inlineStr"/>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr"/>
-      <c r="AV57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr"/>
-      <c r="AX57" t="inlineStr"/>
-      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9114,71 +7899,65 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>W6-3</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>80065</v>
+        <v>79985</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="J58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="L58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>300</v>
       </c>
       <c r="O58" t="n">
-        <v>1440</v>
+        <v>550</v>
       </c>
       <c r="P58" t="n">
         <v>300</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R58" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="S58" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T58" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -9187,18 +7966,18 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="W58" t="n">
         <v>300</v>
       </c>
       <c r="X58" t="n">
-        <v>1440</v>
+        <v>1110</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -9214,18 +7993,18 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr"/>
@@ -9242,19 +8021,6 @@
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
-      <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr"/>
-      <c r="AV58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr"/>
-      <c r="AX58" t="inlineStr"/>
-      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9263,15 +8029,15 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>V6-2</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79985</v>
+        <v>79995</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9280,54 +8046,48 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>5400</v>
+        <v>10000</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>5400</v>
+        <v>10000</v>
       </c>
       <c r="J59" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="K59" t="n">
-        <v>10800</v>
+        <v>10000</v>
       </c>
       <c r="L59" t="n">
         <v>25</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="P59" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="R59" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="S59" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="T59" s="1" t="n">
+        <v>46184</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -9336,18 +8096,18 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X59" t="n">
-        <v>1110</v>
+        <v>1000</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -9363,7 +8123,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>分割+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9374,7 +8134,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/11）</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr"/>
@@ -9391,19 +8151,6 @@
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="inlineStr"/>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
-      <c r="AV59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr"/>
-      <c r="AX59" t="inlineStr"/>
-      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9412,15 +8159,15 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>V6-2</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>79995</v>
+        <v>80067</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -9429,54 +8176,48 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="L60" t="n">
         <v>25</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O60" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="P60" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>2026/06/17</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>2026/06/17</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026/06/11</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R60" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="S60" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="T60" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9485,18 +8226,18 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>1440</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -9512,7 +8253,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>分割+スリット機1　湖南</t>
+          <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9523,7 +8264,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>（2026/6/11）</t>
+          <t>（2026/6/9）</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr"/>
@@ -9540,19 +8281,6 @@
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="inlineStr"/>
-      <c r="AR60" t="inlineStr"/>
-      <c r="AS60" t="inlineStr"/>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="inlineStr"/>
-      <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
-      <c r="AX60" t="inlineStr"/>
-      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9569,12 +8297,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9593,7 +8321,7 @@
         <v>6000</v>
       </c>
       <c r="L61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -9612,20 +8340,14 @@
       <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+      <c r="R61" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="S61" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="T61" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9661,12 +8383,12 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>スリット+スリット機1　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -9689,19 +8411,6 @@
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
-      <c r="AR61" t="inlineStr"/>
-      <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="inlineStr"/>
-      <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9718,12 +8427,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9742,7 +8451,7 @@
         <v>6000</v>
       </c>
       <c r="L62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -9761,20 +8470,14 @@
       <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+      <c r="R62" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="S62" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="T62" s="1" t="n">
+        <v>46182</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9810,12 +8513,12 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -9838,19 +8541,6 @@
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="inlineStr"/>
-      <c r="AQ62" t="inlineStr"/>
-      <c r="AR62" t="inlineStr"/>
-      <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr"/>
-      <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9859,50 +8549,50 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>80067</v>
+        <v>80066</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="J63" t="n">
+        <v>30</v>
+      </c>
+      <c r="K63" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L63" t="n">
         <v>20</v>
       </c>
-      <c r="K63" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L63" t="n">
-        <v>10</v>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>300</v>
       </c>
       <c r="O63" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="P63" t="n">
         <v>300</v>
@@ -9910,20 +8600,14 @@
       <c r="Q63" t="n">
         <v>2</v>
       </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
+      <c r="R63" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S63" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T63" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9943,7 +8627,7 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -9959,18 +8643,18 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>EC+EC機　湖南</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（20）</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>（2026/6/9）</t>
+          <t>（2026/6/10）</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr"/>
@@ -9987,19 +8671,6 @@
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="inlineStr"/>
-      <c r="AS63" t="inlineStr"/>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AU63" t="inlineStr"/>
-      <c r="AV63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr"/>
-      <c r="AX63" t="inlineStr"/>
-      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10016,12 +8687,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10040,7 +8711,7 @@
         <v>9000</v>
       </c>
       <c r="L64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -10059,20 +8730,14 @@
       <c r="Q64" t="n">
         <v>2</v>
       </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+      <c r="R64" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S64" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T64" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -10108,12 +8773,12 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>EC+EC機　湖南</t>
+          <t>検査+熱融着機　湖南</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>（20）</t>
+          <t>（10）</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -10136,19 +8801,6 @@
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
-      <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="inlineStr"/>
-      <c r="AR64" t="inlineStr"/>
-      <c r="AS64" t="inlineStr"/>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AU64" t="inlineStr"/>
-      <c r="AV64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr"/>
-      <c r="AX64" t="inlineStr"/>
-      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10157,91 +8809,85 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>W6-5</t>
+          <t>Y5-42</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>80066</v>
+        <v>79828</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>9000</v>
+        <v>1200</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>9000</v>
+        <v>1200</v>
       </c>
       <c r="J65" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>9000</v>
+        <v>1200</v>
       </c>
       <c r="L65" t="n">
         <v>10</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O65" t="n">
-        <v>1440</v>
+        <v>740</v>
       </c>
       <c r="P65" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+      <c r="R65" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S65" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T65" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="W65" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X65" t="n">
-        <v>1440</v>
+        <v>750</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -10257,7 +8903,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>検査+熱融着機　湖南</t>
+          <t>エンボス+エンボス　湖南</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10268,7 +8914,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>（2026/6/10）</t>
+          <t>（2026/6/1）</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr"/>
@@ -10285,112 +8931,95 @@
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr"/>
-      <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="inlineStr"/>
-      <c r="AS65" t="inlineStr"/>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr"/>
-      <c r="AV65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr"/>
-      <c r="AX65" t="inlineStr"/>
-      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Y5-42</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>79828</v>
+        <v>79996</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1200</v>
+        <v>6400</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1200</v>
+        <v>6400</v>
       </c>
       <c r="J66" t="n">
+        <v>32</v>
+      </c>
+      <c r="K66" t="n">
+        <v>6400</v>
+      </c>
+      <c r="L66" t="n">
+        <v>25</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>30030-BG00-1000X100F-A   C</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>100</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P66" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q66" t="n">
         <v>3</v>
       </c>
-      <c r="K66" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L66" t="n">
-        <v>10</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>200</v>
-      </c>
-      <c r="O66" t="n">
-        <v>740</v>
-      </c>
-      <c r="P66" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R66" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S66" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T66" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="W66" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X66" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -10406,18 +9035,18 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>エンボス+エンボス　湖南</t>
+          <t>分割+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>（10）</t>
+          <t>（25）</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>（2026/6/1）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr"/>
@@ -10434,19 +9063,6 @@
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="inlineStr"/>
-      <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="inlineStr"/>
-      <c r="AV66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr"/>
-      <c r="AX66" t="inlineStr"/>
-      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -10457,15 +9073,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>V6-3</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>79996</v>
+        <v>80056</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -10474,54 +9090,46 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>6400</v>
+        <v>200</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>6400</v>
+        <v>200</v>
       </c>
       <c r="J67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>6400</v>
-      </c>
-      <c r="L67" t="n">
-        <v>25</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>50090-BY0B- 900X100F-ABKOC</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P67" t="n">
         <v>100</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="R67" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="T67" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10530,18 +9138,18 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>50090-AY0B- 900X100F-ABKOM</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X67" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>巻返し,スライス</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -10557,18 +9165,18 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>分割+スライス機1　湖南</t>
+          <t>巻返し+スライス機1　湖南</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>（25）</t>
+          <t>（―）</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/6/3）</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr"/>
@@ -10585,19 +9193,6 @@
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
-      <c r="AN67" t="inlineStr"/>
-      <c r="AO67" t="inlineStr"/>
-      <c r="AP67" t="inlineStr"/>
-      <c r="AQ67" t="inlineStr"/>
-      <c r="AR67" t="inlineStr"/>
-      <c r="AS67" t="inlineStr"/>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AU67" t="inlineStr"/>
-      <c r="AV67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr"/>
-      <c r="AX67" t="inlineStr"/>
-      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -10608,11 +9203,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>V6-3</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>80056</v>
+        <v>80100</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -10621,76 +9216,70 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>50090-BY0B- 900X100F-ABKOC</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O68" t="n">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="P68" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R68" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S68" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T68" s="1" t="n">
+        <v>46175</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>50090-AY0B- 900X100F-ABKOM</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="W68" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="X68" t="n">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>巻返し,スライス</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -10706,7 +9295,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>巻返し+スライス機1　湖南</t>
+          <t>巻返し+EC機　湖南</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10717,7 +9306,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>（2026/6/3）</t>
+          <t>（2026/6/2）</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr"/>
@@ -10734,19 +9323,6 @@
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="inlineStr"/>
-      <c r="AO68" t="inlineStr"/>
-      <c r="AP68" t="inlineStr"/>
-      <c r="AQ68" t="inlineStr"/>
-      <c r="AR68" t="inlineStr"/>
-      <c r="AS68" t="inlineStr"/>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AU68" t="inlineStr"/>
-      <c r="AV68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr"/>
-      <c r="AX68" t="inlineStr"/>
-      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -10757,69 +9333,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>W5-22</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>80100</v>
+        <v>80126</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>15020-NP17-1300X250F-A   J</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="O69" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="P69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
+        <v>1.1</v>
+      </c>
+      <c r="R69" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S69" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T69" s="1" t="n">
+        <v>46171</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10828,18 +9398,18 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>15020-AP17-1300X250F-A   P</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="W69" t="n">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="X69" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>EC,巻返し</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -10855,7 +9425,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>巻返し+EC機　湖南</t>
+          <t>検査+スリット機1　湖南</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10866,7 +9436,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>（2026/6/2）</t>
+          <t>（2026/5/29）</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr"/>
@@ -10883,19 +9453,6 @@
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="inlineStr"/>
-      <c r="AO69" t="inlineStr"/>
-      <c r="AP69" t="inlineStr"/>
-      <c r="AQ69" t="inlineStr"/>
-      <c r="AR69" t="inlineStr"/>
-      <c r="AS69" t="inlineStr"/>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AU69" t="inlineStr"/>
-      <c r="AV69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr"/>
-      <c r="AX69" t="inlineStr"/>
-      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -10955,20 +9512,14 @@
       <c r="Q70" t="n">
         <v>2</v>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
+      <c r="R70" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="S70" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="T70" s="1" t="n">
+        <v>46170</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -11032,19 +9583,6 @@
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="inlineStr"/>
-      <c r="AO70" t="inlineStr"/>
-      <c r="AP70" t="inlineStr"/>
-      <c r="AQ70" t="inlineStr"/>
-      <c r="AR70" t="inlineStr"/>
-      <c r="AS70" t="inlineStr"/>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AU70" t="inlineStr"/>
-      <c r="AV70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr"/>
-      <c r="AX70" t="inlineStr"/>
-      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -11104,20 +9642,14 @@
       <c r="Q71" t="n">
         <v>4</v>
       </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R71" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S71" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T71" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -11181,19 +9713,6 @@
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="inlineStr"/>
-      <c r="AO71" t="inlineStr"/>
-      <c r="AP71" t="inlineStr"/>
-      <c r="AQ71" t="inlineStr"/>
-      <c r="AR71" t="inlineStr"/>
-      <c r="AS71" t="inlineStr"/>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AU71" t="inlineStr"/>
-      <c r="AV71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr"/>
-      <c r="AX71" t="inlineStr"/>
-      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -11253,20 +9772,14 @@
       <c r="Q72" t="n">
         <v>2.5</v>
       </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R72" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S72" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T72" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -11330,19 +9843,6 @@
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="inlineStr"/>
-      <c r="AO72" t="inlineStr"/>
-      <c r="AP72" t="inlineStr"/>
-      <c r="AQ72" t="inlineStr"/>
-      <c r="AR72" t="inlineStr"/>
-      <c r="AS72" t="inlineStr"/>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AU72" t="inlineStr"/>
-      <c r="AV72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr"/>
-      <c r="AX72" t="inlineStr"/>
-      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -11402,20 +9902,14 @@
       <c r="Q73" t="n">
         <v>2</v>
       </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R73" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S73" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T73" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -11479,19 +9973,6 @@
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="inlineStr"/>
-      <c r="AO73" t="inlineStr"/>
-      <c r="AP73" t="inlineStr"/>
-      <c r="AQ73" t="inlineStr"/>
-      <c r="AR73" t="inlineStr"/>
-      <c r="AS73" t="inlineStr"/>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AU73" t="inlineStr"/>
-      <c r="AV73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr"/>
-      <c r="AX73" t="inlineStr"/>
-      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -11551,20 +10032,14 @@
       <c r="Q74" t="n">
         <v>3</v>
       </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R74" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S74" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="T74" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11628,19 +10103,6 @@
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
-      <c r="AN74" t="inlineStr"/>
-      <c r="AO74" t="inlineStr"/>
-      <c r="AP74" t="inlineStr"/>
-      <c r="AQ74" t="inlineStr"/>
-      <c r="AR74" t="inlineStr"/>
-      <c r="AS74" t="inlineStr"/>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AU74" t="inlineStr"/>
-      <c r="AV74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr"/>
-      <c r="AX74" t="inlineStr"/>
-      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -11700,20 +10162,14 @@
       <c r="Q75" t="n">
         <v>3</v>
       </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>2026/06/10</t>
-        </is>
+      <c r="R75" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="S75" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T75" s="1" t="n">
+        <v>46183</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11777,19 +10233,6 @@
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr"/>
-      <c r="AO75" t="inlineStr"/>
-      <c r="AP75" t="inlineStr"/>
-      <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="inlineStr"/>
-      <c r="AS75" t="inlineStr"/>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AU75" t="inlineStr"/>
-      <c r="AV75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr"/>
-      <c r="AX75" t="inlineStr"/>
-      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -11849,20 +10292,14 @@
       <c r="Q76" t="n">
         <v>2</v>
       </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R76" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S76" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T76" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -11926,19 +10363,6 @@
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="inlineStr"/>
-      <c r="AO76" t="inlineStr"/>
-      <c r="AP76" t="inlineStr"/>
-      <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="inlineStr"/>
-      <c r="AS76" t="inlineStr"/>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AU76" t="inlineStr"/>
-      <c r="AV76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr"/>
-      <c r="AX76" t="inlineStr"/>
-      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -11998,20 +10422,14 @@
       <c r="Q77" t="n">
         <v>20</v>
       </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R77" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="S77" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="T77" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -12075,19 +10493,6 @@
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr"/>
-      <c r="AO77" t="inlineStr"/>
-      <c r="AP77" t="inlineStr"/>
-      <c r="AQ77" t="inlineStr"/>
-      <c r="AR77" t="inlineStr"/>
-      <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AU77" t="inlineStr"/>
-      <c r="AV77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr"/>
-      <c r="AX77" t="inlineStr"/>
-      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -12149,20 +10554,14 @@
       <c r="Q78" t="n">
         <v>2</v>
       </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R78" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="T78" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -12226,19 +10625,6 @@
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
-      <c r="AN78" t="inlineStr"/>
-      <c r="AO78" t="inlineStr"/>
-      <c r="AP78" t="inlineStr"/>
-      <c r="AQ78" t="inlineStr"/>
-      <c r="AR78" t="inlineStr"/>
-      <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AU78" t="inlineStr"/>
-      <c r="AV78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr"/>
-      <c r="AX78" t="inlineStr"/>
-      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -12300,20 +10686,14 @@
       <c r="Q79" t="n">
         <v>2</v>
       </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
+      <c r="R79" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="T79" s="1" t="n">
+        <v>46178</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -12377,19 +10757,6 @@
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
-      <c r="AN79" t="inlineStr"/>
-      <c r="AO79" t="inlineStr"/>
-      <c r="AP79" t="inlineStr"/>
-      <c r="AQ79" t="inlineStr"/>
-      <c r="AR79" t="inlineStr"/>
-      <c r="AS79" t="inlineStr"/>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr"/>
-      <c r="AV79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr"/>
-      <c r="AX79" t="inlineStr"/>
-      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -12451,20 +10818,14 @@
       <c r="Q80" t="n">
         <v>2</v>
       </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
+      <c r="R80" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="T80" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12528,19 +10889,6 @@
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr"/>
-      <c r="AO80" t="inlineStr"/>
-      <c r="AP80" t="inlineStr"/>
-      <c r="AQ80" t="inlineStr"/>
-      <c r="AR80" t="inlineStr"/>
-      <c r="AS80" t="inlineStr"/>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AU80" t="inlineStr"/>
-      <c r="AV80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr"/>
-      <c r="AX80" t="inlineStr"/>
-      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
